--- a/data/entry_signals_tw.xlsx
+++ b/data/entry_signals_tw.xlsx
@@ -1881,90 +1881,90 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>136.92326733</v>
+        <v>2163</v>
       </c>
       <c r="C33" t="n">
-        <v>209.37295785</v>
+        <v>4698.75</v>
       </c>
       <c r="D33" t="n">
-        <v>169</v>
+        <v>3285</v>
       </c>
       <c r="E33" t="n">
-        <v>132.935211</v>
+        <v>2100</v>
       </c>
       <c r="F33" t="n">
-        <v>199.402817</v>
+        <v>4475</v>
       </c>
       <c r="G33" t="n">
-        <v>209.37</v>
+        <v>4698.75</v>
       </c>
       <c r="H33" t="n">
-        <v>136.92</v>
+        <v>2163</v>
       </c>
       <c r="I33" t="n">
-        <v>155.04</v>
+        <v>2796.94</v>
       </c>
       <c r="J33" t="n">
-        <v>23.9</v>
+        <v>43</v>
       </c>
       <c r="K33" t="n">
-        <v>-19</v>
+        <v>-34.2</v>
       </c>
       <c r="L33" t="n">
         <v>1.26</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2163</v>
+        <v>136.92326733</v>
       </c>
       <c r="C34" t="n">
-        <v>4698.75</v>
+        <v>209.37295785</v>
       </c>
       <c r="D34" t="n">
-        <v>3285</v>
+        <v>169</v>
       </c>
       <c r="E34" t="n">
-        <v>2100</v>
+        <v>132.935211</v>
       </c>
       <c r="F34" t="n">
-        <v>4475</v>
+        <v>199.402817</v>
       </c>
       <c r="G34" t="n">
-        <v>4698.75</v>
+        <v>209.37</v>
       </c>
       <c r="H34" t="n">
-        <v>2163</v>
+        <v>136.92</v>
       </c>
       <c r="I34" t="n">
-        <v>2796.94</v>
+        <v>155.04</v>
       </c>
       <c r="J34" t="n">
-        <v>43</v>
+        <v>23.9</v>
       </c>
       <c r="K34" t="n">
-        <v>-34.2</v>
+        <v>-19</v>
       </c>
       <c r="L34" t="n">
         <v>1.26</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
@@ -2421,90 +2421,90 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>276.555</v>
+        <v>107.635</v>
       </c>
       <c r="C45" t="n">
-        <v>459.9</v>
+        <v>127.575</v>
       </c>
       <c r="D45" t="n">
-        <v>372</v>
+        <v>118</v>
       </c>
       <c r="E45" t="n">
-        <v>268.5</v>
+        <v>104.5</v>
       </c>
       <c r="F45" t="n">
-        <v>438</v>
+        <v>121.5</v>
       </c>
       <c r="G45" t="n">
-        <v>459.9</v>
+        <v>127.58</v>
       </c>
       <c r="H45" t="n">
-        <v>276.56</v>
+        <v>107.64</v>
       </c>
       <c r="I45" t="n">
-        <v>322.39</v>
+        <v>112.62</v>
       </c>
       <c r="J45" t="n">
-        <v>23.6</v>
+        <v>8.1</v>
       </c>
       <c r="K45" t="n">
-        <v>-25.7</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L45" t="n">
         <v>0.92</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>107.635</v>
+        <v>276.555</v>
       </c>
       <c r="C46" t="n">
-        <v>127.575</v>
+        <v>459.9</v>
       </c>
       <c r="D46" t="n">
-        <v>118</v>
+        <v>372</v>
       </c>
       <c r="E46" t="n">
-        <v>104.5</v>
+        <v>268.5</v>
       </c>
       <c r="F46" t="n">
-        <v>121.5</v>
+        <v>438</v>
       </c>
       <c r="G46" t="n">
-        <v>127.58</v>
+        <v>459.9</v>
       </c>
       <c r="H46" t="n">
-        <v>107.64</v>
+        <v>276.56</v>
       </c>
       <c r="I46" t="n">
-        <v>112.62</v>
+        <v>322.39</v>
       </c>
       <c r="J46" t="n">
-        <v>8.1</v>
+        <v>23.6</v>
       </c>
       <c r="K46" t="n">
-        <v>-8.800000000000001</v>
+        <v>-25.7</v>
       </c>
       <c r="L46" t="n">
         <v>0.92</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
@@ -4491,38 +4491,38 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1575.9</v>
+        <v>576.76065297</v>
       </c>
       <c r="C91" t="n">
-        <v>6347.25</v>
+        <v>1764</v>
       </c>
       <c r="D91" t="n">
-        <v>5535</v>
+        <v>1555</v>
       </c>
       <c r="E91" t="n">
-        <v>1530</v>
+        <v>559.961799</v>
       </c>
       <c r="F91" t="n">
-        <v>6045</v>
+        <v>1680</v>
       </c>
       <c r="G91" t="n">
-        <v>6347.25</v>
+        <v>1764</v>
       </c>
       <c r="H91" t="n">
-        <v>1575.9</v>
+        <v>576.76</v>
       </c>
       <c r="I91" t="n">
-        <v>2768.74</v>
+        <v>873.5700000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>14.7</v>
+        <v>13.4</v>
       </c>
       <c r="K91" t="n">
-        <v>-71.5</v>
+        <v>-62.9</v>
       </c>
       <c r="L91" t="n">
         <v>0.21</v>
@@ -4536,38 +4536,38 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>576.76065297</v>
+        <v>1575.9</v>
       </c>
       <c r="C92" t="n">
-        <v>1764</v>
+        <v>6347.25</v>
       </c>
       <c r="D92" t="n">
-        <v>1555</v>
+        <v>5535</v>
       </c>
       <c r="E92" t="n">
-        <v>559.961799</v>
+        <v>1530</v>
       </c>
       <c r="F92" t="n">
-        <v>1680</v>
+        <v>6045</v>
       </c>
       <c r="G92" t="n">
-        <v>1764</v>
+        <v>6347.25</v>
       </c>
       <c r="H92" t="n">
-        <v>576.76</v>
+        <v>1575.9</v>
       </c>
       <c r="I92" t="n">
-        <v>873.5700000000001</v>
+        <v>2768.74</v>
       </c>
       <c r="J92" t="n">
-        <v>13.4</v>
+        <v>14.7</v>
       </c>
       <c r="K92" t="n">
-        <v>-62.9</v>
+        <v>-71.5</v>
       </c>
       <c r="L92" t="n">
         <v>0.21</v>
@@ -5157,7 +5157,7 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
+          <t>🚨 已破止損(SL 失守, 重新評估支撐)</t>
         </is>
       </c>
     </row>

--- a/data/entry_signals_tw.xlsx
+++ b/data/entry_signals_tw.xlsx
@@ -496,7 +496,7 @@
         <v>1170.75</v>
       </c>
       <c r="D2" t="n">
-        <v>757</v>
+        <v>773</v>
       </c>
       <c r="E2" t="n">
         <v>731</v>
@@ -514,13 +514,13 @@
         <v>857.38</v>
       </c>
       <c r="J2" t="n">
-        <v>54.7</v>
+        <v>51.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5</v>
+        <v>-2.6</v>
       </c>
       <c r="L2" t="n">
-        <v>101.66</v>
+        <v>19.82</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -531,41 +531,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.805</v>
+        <v>71.07000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>67.935</v>
+        <v>111.0765831</v>
       </c>
       <c r="D3" t="n">
-        <v>45.55</v>
+        <v>76.2</v>
       </c>
       <c r="E3" t="n">
-        <v>43.5</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>64.7</v>
+        <v>105.787222</v>
       </c>
       <c r="G3" t="n">
-        <v>67.94</v>
+        <v>111.08</v>
       </c>
       <c r="H3" t="n">
-        <v>44.8</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>50.59</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>49.1</v>
+        <v>45.8</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.6</v>
+        <v>-6.7</v>
       </c>
       <c r="L3" t="n">
-        <v>30.05</v>
+        <v>6.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -576,41 +576,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71.07000000000001</v>
+        <v>44.805</v>
       </c>
       <c r="C4" t="n">
-        <v>111.0765831</v>
+        <v>67.935</v>
       </c>
       <c r="D4" t="n">
-        <v>73.59999999999999</v>
+        <v>47.85</v>
       </c>
       <c r="E4" t="n">
-        <v>69</v>
+        <v>43.5</v>
       </c>
       <c r="F4" t="n">
-        <v>105.787222</v>
+        <v>64.7</v>
       </c>
       <c r="G4" t="n">
-        <v>111.08</v>
+        <v>67.94</v>
       </c>
       <c r="H4" t="n">
-        <v>71.06999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="I4" t="n">
-        <v>81.06999999999999</v>
+        <v>50.59</v>
       </c>
       <c r="J4" t="n">
-        <v>50.9</v>
+        <v>42</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.4</v>
+        <v>-6.4</v>
       </c>
       <c r="L4" t="n">
-        <v>14.81</v>
+        <v>6.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -621,41 +621,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141.22429189</v>
+        <v>89.404</v>
       </c>
       <c r="C5" t="n">
-        <v>153.4643019</v>
+        <v>124.425</v>
       </c>
       <c r="D5" t="n">
-        <v>142</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>137.110963</v>
+        <v>86.8</v>
       </c>
       <c r="F5" t="n">
-        <v>146.156478</v>
+        <v>118.5</v>
       </c>
       <c r="G5" t="n">
-        <v>153.46</v>
+        <v>124.43</v>
       </c>
       <c r="H5" t="n">
-        <v>141.22</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>144.28</v>
+        <v>98.16</v>
       </c>
       <c r="J5" t="n">
-        <v>8.1</v>
+        <v>31.8</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5</v>
+        <v>-5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>14.78</v>
+        <v>6.01</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -666,41 +666,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>89.404</v>
+        <v>22.866</v>
       </c>
       <c r="C6" t="n">
-        <v>124.425</v>
+        <v>33.81861420000001</v>
       </c>
       <c r="D6" t="n">
-        <v>92.90000000000001</v>
+        <v>24.45</v>
       </c>
       <c r="E6" t="n">
-        <v>86.8</v>
+        <v>22.2</v>
       </c>
       <c r="F6" t="n">
-        <v>118.5</v>
+        <v>32.208204</v>
       </c>
       <c r="G6" t="n">
-        <v>124.43</v>
+        <v>33.82</v>
       </c>
       <c r="H6" t="n">
-        <v>89.40000000000001</v>
+        <v>22.87</v>
       </c>
       <c r="I6" t="n">
-        <v>98.16</v>
+        <v>25.6</v>
       </c>
       <c r="J6" t="n">
-        <v>33.9</v>
+        <v>38.3</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.8</v>
+        <v>-6.5</v>
       </c>
       <c r="L6" t="n">
-        <v>9.02</v>
+        <v>5.91</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>55.23</v>
       </c>
       <c r="D7" t="n">
-        <v>40.75</v>
+        <v>41.7</v>
       </c>
       <c r="E7" t="n">
         <v>37.8</v>
@@ -739,13 +739,13 @@
         <v>43.01</v>
       </c>
       <c r="J7" t="n">
-        <v>35.5</v>
+        <v>32.4</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.5</v>
+        <v>-6.6</v>
       </c>
       <c r="L7" t="n">
-        <v>7.97</v>
+        <v>4.89</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -756,41 +756,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.866</v>
+        <v>20.806</v>
       </c>
       <c r="C8" t="n">
-        <v>33.81861420000001</v>
+        <v>32.445</v>
       </c>
       <c r="D8" t="n">
-        <v>24.3</v>
+        <v>23.4</v>
       </c>
       <c r="E8" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="F8" t="n">
-        <v>32.208204</v>
+        <v>30.9</v>
       </c>
       <c r="G8" t="n">
-        <v>33.82</v>
+        <v>32.45</v>
       </c>
       <c r="H8" t="n">
-        <v>22.87</v>
+        <v>20.81</v>
       </c>
       <c r="I8" t="n">
-        <v>25.6</v>
+        <v>23.72</v>
       </c>
       <c r="J8" t="n">
-        <v>39.2</v>
+        <v>38.7</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.9</v>
+        <v>-11.1</v>
       </c>
       <c r="L8" t="n">
-        <v>6.64</v>
+        <v>3.49</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -801,266 +801,266 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.806</v>
+        <v>94.863</v>
       </c>
       <c r="C9" t="n">
-        <v>32.445</v>
+        <v>124.13135595</v>
       </c>
       <c r="D9" t="n">
-        <v>22.5</v>
+        <v>102.5</v>
       </c>
       <c r="E9" t="n">
-        <v>20.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>30.9</v>
+        <v>118.220339</v>
       </c>
       <c r="G9" t="n">
-        <v>32.45</v>
+        <v>124.13</v>
       </c>
       <c r="H9" t="n">
-        <v>20.81</v>
+        <v>94.86</v>
       </c>
       <c r="I9" t="n">
-        <v>23.72</v>
+        <v>102.18</v>
       </c>
       <c r="J9" t="n">
-        <v>44.2</v>
+        <v>21.1</v>
       </c>
       <c r="K9" t="n">
         <v>-7.5</v>
       </c>
       <c r="L9" t="n">
-        <v>5.87</v>
+        <v>2.83</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94.863</v>
+        <v>101.36665072</v>
       </c>
       <c r="C10" t="n">
-        <v>124.13135595</v>
+        <v>122.8038357</v>
       </c>
       <c r="D10" t="n">
-        <v>99.2</v>
+        <v>107</v>
       </c>
       <c r="E10" t="n">
-        <v>92.09999999999999</v>
+        <v>98.414224</v>
       </c>
       <c r="F10" t="n">
-        <v>118.220339</v>
+        <v>116.956034</v>
       </c>
       <c r="G10" t="n">
-        <v>124.13</v>
+        <v>122.8</v>
       </c>
       <c r="H10" t="n">
-        <v>94.86</v>
+        <v>101.37</v>
       </c>
       <c r="I10" t="n">
-        <v>102.18</v>
+        <v>106.73</v>
       </c>
       <c r="J10" t="n">
-        <v>25.1</v>
+        <v>14.8</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.4</v>
+        <v>-5.3</v>
       </c>
       <c r="L10" t="n">
-        <v>5.75</v>
+        <v>2.81</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>101.36665072</v>
+        <v>135.96</v>
       </c>
       <c r="C11" t="n">
-        <v>122.8038357</v>
+        <v>154.35</v>
       </c>
       <c r="D11" t="n">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="E11" t="n">
-        <v>98.414224</v>
+        <v>132</v>
       </c>
       <c r="F11" t="n">
-        <v>116.956034</v>
+        <v>147</v>
       </c>
       <c r="G11" t="n">
-        <v>122.8</v>
+        <v>154.35</v>
       </c>
       <c r="H11" t="n">
-        <v>101.37</v>
+        <v>135.96</v>
       </c>
       <c r="I11" t="n">
-        <v>106.73</v>
+        <v>140.56</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.5</v>
+        <v>-3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>4.9</v>
+        <v>2.65</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>153.80987013</v>
+        <v>37.78805496</v>
       </c>
       <c r="C12" t="n">
-        <v>192.6356628</v>
+        <v>45.24471735</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>39.85</v>
       </c>
       <c r="E12" t="n">
-        <v>149.329971</v>
+        <v>36.687432</v>
       </c>
       <c r="F12" t="n">
-        <v>183.462536</v>
+        <v>43.090207</v>
       </c>
       <c r="G12" t="n">
-        <v>192.64</v>
+        <v>45.24</v>
       </c>
       <c r="H12" t="n">
-        <v>153.81</v>
+        <v>37.79</v>
       </c>
       <c r="I12" t="n">
-        <v>163.52</v>
+        <v>39.65</v>
       </c>
       <c r="J12" t="n">
-        <v>19.6</v>
+        <v>13.5</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.5</v>
+        <v>-5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>4.4</v>
+        <v>2.62</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1236</v>
+        <v>891.03583299</v>
       </c>
       <c r="C13" t="n">
-        <v>2667</v>
+        <v>1354.7205</v>
       </c>
       <c r="D13" t="n">
-        <v>1575</v>
+        <v>1020</v>
       </c>
       <c r="E13" t="n">
-        <v>1200</v>
+        <v>865.083333</v>
       </c>
       <c r="F13" t="n">
-        <v>2540</v>
+        <v>1290.21</v>
       </c>
       <c r="G13" t="n">
-        <v>2667</v>
+        <v>1354.72</v>
       </c>
       <c r="H13" t="n">
-        <v>1236</v>
+        <v>891.04</v>
       </c>
       <c r="I13" t="n">
-        <v>1593.75</v>
+        <v>1006.96</v>
       </c>
       <c r="J13" t="n">
-        <v>69.3</v>
+        <v>32.8</v>
       </c>
       <c r="K13" t="n">
-        <v>-21.5</v>
+        <v>-12.6</v>
       </c>
       <c r="L13" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>891.03583299</v>
+        <v>1236</v>
       </c>
       <c r="C14" t="n">
-        <v>1354.7205</v>
+        <v>2667</v>
       </c>
       <c r="D14" t="n">
-        <v>1010</v>
+        <v>1640</v>
       </c>
       <c r="E14" t="n">
-        <v>865.083333</v>
+        <v>1200</v>
       </c>
       <c r="F14" t="n">
-        <v>1290.21</v>
+        <v>2540</v>
       </c>
       <c r="G14" t="n">
-        <v>1354.72</v>
+        <v>2667</v>
       </c>
       <c r="H14" t="n">
-        <v>891.04</v>
+        <v>1236</v>
       </c>
       <c r="I14" t="n">
-        <v>1006.96</v>
+        <v>1593.75</v>
       </c>
       <c r="J14" t="n">
-        <v>34.1</v>
+        <v>62.6</v>
       </c>
       <c r="K14" t="n">
-        <v>-11.8</v>
+        <v>-24.6</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1071,41 +1071,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>209.605</v>
+        <v>2369</v>
       </c>
       <c r="C15" t="n">
-        <v>262.5</v>
+        <v>5969.25</v>
       </c>
       <c r="D15" t="n">
-        <v>223.5</v>
+        <v>3420</v>
       </c>
       <c r="E15" t="n">
-        <v>203.5</v>
+        <v>2300</v>
       </c>
       <c r="F15" t="n">
-        <v>250</v>
+        <v>5685</v>
       </c>
       <c r="G15" t="n">
-        <v>262.5</v>
+        <v>5969.25</v>
       </c>
       <c r="H15" t="n">
-        <v>209.61</v>
+        <v>2369</v>
       </c>
       <c r="I15" t="n">
-        <v>222.83</v>
+        <v>3269.06</v>
       </c>
       <c r="J15" t="n">
-        <v>17.4</v>
+        <v>74.5</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.2</v>
+        <v>-30.7</v>
       </c>
       <c r="L15" t="n">
-        <v>2.81</v>
+        <v>2.43</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1116,41 +1116,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>250.805</v>
+        <v>66.8203539</v>
       </c>
       <c r="C16" t="n">
-        <v>486.675</v>
+        <v>142.9118481</v>
       </c>
       <c r="D16" t="n">
-        <v>316.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>243.5</v>
+        <v>64.87412999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>463.5</v>
+        <v>136.106522</v>
       </c>
       <c r="G16" t="n">
-        <v>486.68</v>
+        <v>142.91</v>
       </c>
       <c r="H16" t="n">
-        <v>250.81</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>309.77</v>
+        <v>85.84</v>
       </c>
       <c r="J16" t="n">
-        <v>53.8</v>
+        <v>58.6</v>
       </c>
       <c r="K16" t="n">
-        <v>-20.8</v>
+        <v>-25.8</v>
       </c>
       <c r="L16" t="n">
-        <v>2.59</v>
+        <v>2.27</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1161,41 +1161,41 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>37.5955047</v>
+        <v>141.22429189</v>
       </c>
       <c r="C17" t="n">
-        <v>45.24471735</v>
+        <v>155.4</v>
       </c>
       <c r="D17" t="n">
-        <v>39.75</v>
+        <v>146.5</v>
       </c>
       <c r="E17" t="n">
-        <v>36.50049</v>
+        <v>137.110963</v>
       </c>
       <c r="F17" t="n">
-        <v>43.090207</v>
+        <v>148</v>
       </c>
       <c r="G17" t="n">
-        <v>45.24</v>
+        <v>155.4</v>
       </c>
       <c r="H17" t="n">
-        <v>37.6</v>
+        <v>141.22</v>
       </c>
       <c r="I17" t="n">
-        <v>39.51</v>
+        <v>144.77</v>
       </c>
       <c r="J17" t="n">
-        <v>13.8</v>
+        <v>6.1</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.4</v>
+        <v>-3.6</v>
       </c>
       <c r="L17" t="n">
-        <v>2.55</v>
+        <v>1.69</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1206,176 +1206,176 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2369</v>
+        <v>270.89</v>
       </c>
       <c r="C18" t="n">
-        <v>5969.25</v>
+        <v>800.1</v>
       </c>
       <c r="D18" t="n">
-        <v>3400</v>
+        <v>468.5</v>
       </c>
       <c r="E18" t="n">
-        <v>2300</v>
+        <v>263</v>
       </c>
       <c r="F18" t="n">
-        <v>5685</v>
+        <v>762</v>
       </c>
       <c r="G18" t="n">
-        <v>5969.25</v>
+        <v>800.1</v>
       </c>
       <c r="H18" t="n">
-        <v>2369</v>
+        <v>270.89</v>
       </c>
       <c r="I18" t="n">
-        <v>3269.06</v>
+        <v>403.19</v>
       </c>
       <c r="J18" t="n">
-        <v>75.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="K18" t="n">
-        <v>-30.3</v>
+        <v>-42.2</v>
       </c>
       <c r="L18" t="n">
-        <v>2.49</v>
+        <v>1.68</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>134.93</v>
+        <v>156.045</v>
       </c>
       <c r="C19" t="n">
-        <v>154.35</v>
+        <v>369.6</v>
       </c>
       <c r="D19" t="n">
-        <v>141.5</v>
+        <v>236</v>
       </c>
       <c r="E19" t="n">
-        <v>131</v>
+        <v>151.5</v>
       </c>
       <c r="F19" t="n">
-        <v>147</v>
+        <v>352</v>
       </c>
       <c r="G19" t="n">
-        <v>154.35</v>
+        <v>369.6</v>
       </c>
       <c r="H19" t="n">
-        <v>134.93</v>
+        <v>156.05</v>
       </c>
       <c r="I19" t="n">
-        <v>139.78</v>
+        <v>209.43</v>
       </c>
       <c r="J19" t="n">
-        <v>9.1</v>
+        <v>56.6</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.6</v>
+        <v>-33.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>270.89</v>
+        <v>153.80987013</v>
       </c>
       <c r="C20" t="n">
-        <v>800.1</v>
+        <v>192.6356628</v>
       </c>
       <c r="D20" t="n">
-        <v>450.5</v>
+        <v>168.5</v>
       </c>
       <c r="E20" t="n">
-        <v>263</v>
+        <v>149.329971</v>
       </c>
       <c r="F20" t="n">
-        <v>762</v>
+        <v>183.462536</v>
       </c>
       <c r="G20" t="n">
-        <v>800.1</v>
+        <v>192.64</v>
       </c>
       <c r="H20" t="n">
-        <v>270.89</v>
+        <v>153.81</v>
       </c>
       <c r="I20" t="n">
-        <v>403.19</v>
+        <v>163.52</v>
       </c>
       <c r="J20" t="n">
-        <v>77.59999999999999</v>
+        <v>14.3</v>
       </c>
       <c r="K20" t="n">
-        <v>-39.9</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>64.67146078</v>
+        <v>126.175</v>
       </c>
       <c r="C21" t="n">
-        <v>142.9118481</v>
+        <v>211.05</v>
       </c>
       <c r="D21" t="n">
-        <v>91.3</v>
+        <v>159</v>
       </c>
       <c r="E21" t="n">
-        <v>62.787826</v>
+        <v>122.5</v>
       </c>
       <c r="F21" t="n">
-        <v>136.106522</v>
+        <v>201</v>
       </c>
       <c r="G21" t="n">
-        <v>142.91</v>
+        <v>211.05</v>
       </c>
       <c r="H21" t="n">
-        <v>64.67</v>
+        <v>126.17</v>
       </c>
       <c r="I21" t="n">
-        <v>84.23</v>
+        <v>147.39</v>
       </c>
       <c r="J21" t="n">
-        <v>56.5</v>
+        <v>32.7</v>
       </c>
       <c r="K21" t="n">
-        <v>-29.2</v>
+        <v>-20.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1386,41 +1386,41 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>703.31864508</v>
+        <v>187.54150699</v>
       </c>
       <c r="C22" t="n">
-        <v>1826.16</v>
+        <v>320.16794775</v>
       </c>
       <c r="D22" t="n">
-        <v>1095</v>
+        <v>240.5</v>
       </c>
       <c r="E22" t="n">
-        <v>682.833636</v>
+        <v>182.079133</v>
       </c>
       <c r="F22" t="n">
-        <v>1739.2</v>
+        <v>304.921855</v>
       </c>
       <c r="G22" t="n">
-        <v>1826.16</v>
+        <v>320.17</v>
       </c>
       <c r="H22" t="n">
-        <v>703.3200000000001</v>
+        <v>187.54</v>
       </c>
       <c r="I22" t="n">
-        <v>984.03</v>
+        <v>220.7</v>
       </c>
       <c r="J22" t="n">
-        <v>66.8</v>
+        <v>33.1</v>
       </c>
       <c r="K22" t="n">
-        <v>-35.8</v>
+        <v>-22</v>
       </c>
       <c r="L22" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1431,86 +1431,86 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>126.175</v>
+        <v>209.605</v>
       </c>
       <c r="C23" t="n">
-        <v>208.95</v>
+        <v>262.5</v>
       </c>
       <c r="D23" t="n">
-        <v>155.5</v>
+        <v>231</v>
       </c>
       <c r="E23" t="n">
-        <v>122.5</v>
+        <v>203.5</v>
       </c>
       <c r="F23" t="n">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="G23" t="n">
-        <v>208.95</v>
+        <v>262.5</v>
       </c>
       <c r="H23" t="n">
-        <v>126.17</v>
+        <v>209.61</v>
       </c>
       <c r="I23" t="n">
-        <v>146.87</v>
+        <v>222.83</v>
       </c>
       <c r="J23" t="n">
-        <v>34.4</v>
+        <v>13.6</v>
       </c>
       <c r="K23" t="n">
-        <v>-18.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>56.032</v>
+        <v>68.90700000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>85.26000000000001</v>
+        <v>150.675</v>
       </c>
       <c r="D24" t="n">
-        <v>66.7</v>
+        <v>102.5</v>
       </c>
       <c r="E24" t="n">
-        <v>54.4</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>81.2</v>
+        <v>143.5</v>
       </c>
       <c r="G24" t="n">
-        <v>85.26000000000001</v>
+        <v>150.68</v>
       </c>
       <c r="H24" t="n">
-        <v>56.03</v>
+        <v>68.91</v>
       </c>
       <c r="I24" t="n">
-        <v>63.34</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>27.8</v>
+        <v>47</v>
       </c>
       <c r="K24" t="n">
-        <v>-16</v>
+        <v>-32.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1521,41 +1521,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>68.90700000000001</v>
+        <v>98.88</v>
       </c>
       <c r="C25" t="n">
-        <v>150.675</v>
+        <v>156.975</v>
       </c>
       <c r="D25" t="n">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="E25" t="n">
-        <v>66.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="F25" t="n">
-        <v>143.5</v>
+        <v>149.5</v>
       </c>
       <c r="G25" t="n">
-        <v>150.68</v>
+        <v>156.97</v>
       </c>
       <c r="H25" t="n">
-        <v>68.91</v>
+        <v>98.88</v>
       </c>
       <c r="I25" t="n">
-        <v>89.34999999999999</v>
+        <v>113.4</v>
       </c>
       <c r="J25" t="n">
-        <v>50.7</v>
+        <v>27.6</v>
       </c>
       <c r="K25" t="n">
-        <v>-31.1</v>
+        <v>-19.6</v>
       </c>
       <c r="L25" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1566,41 +1566,41 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>126.175</v>
+        <v>56.032</v>
       </c>
       <c r="C26" t="n">
-        <v>211.05</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>159.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>122.5</v>
+        <v>54.4</v>
       </c>
       <c r="F26" t="n">
-        <v>201</v>
+        <v>81.2</v>
       </c>
       <c r="G26" t="n">
-        <v>211.05</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>126.17</v>
+        <v>56.03</v>
       </c>
       <c r="I26" t="n">
-        <v>147.39</v>
+        <v>63.34</v>
       </c>
       <c r="J26" t="n">
-        <v>32.3</v>
+        <v>24.6</v>
       </c>
       <c r="K26" t="n">
-        <v>-20.9</v>
+        <v>-18.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1611,86 +1611,86 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>177.16</v>
+        <v>250.805</v>
       </c>
       <c r="C27" t="n">
-        <v>205.8</v>
+        <v>486.675</v>
       </c>
       <c r="D27" t="n">
-        <v>188.5</v>
+        <v>351</v>
       </c>
       <c r="E27" t="n">
-        <v>172</v>
+        <v>243.5</v>
       </c>
       <c r="F27" t="n">
-        <v>196</v>
+        <v>463.5</v>
       </c>
       <c r="G27" t="n">
-        <v>205.8</v>
+        <v>486.68</v>
       </c>
       <c r="H27" t="n">
-        <v>177.16</v>
+        <v>250.81</v>
       </c>
       <c r="I27" t="n">
-        <v>184.32</v>
+        <v>309.77</v>
       </c>
       <c r="J27" t="n">
-        <v>9.199999999999999</v>
+        <v>38.7</v>
       </c>
       <c r="K27" t="n">
-        <v>-6</v>
+        <v>-28.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>193.125</v>
+        <v>126.175</v>
       </c>
       <c r="C28" t="n">
-        <v>329.7</v>
+        <v>208.95</v>
       </c>
       <c r="D28" t="n">
-        <v>248</v>
+        <v>162</v>
       </c>
       <c r="E28" t="n">
-        <v>187.5</v>
+        <v>122.5</v>
       </c>
       <c r="F28" t="n">
-        <v>314</v>
+        <v>199</v>
       </c>
       <c r="G28" t="n">
-        <v>329.7</v>
+        <v>208.95</v>
       </c>
       <c r="H28" t="n">
-        <v>193.12</v>
+        <v>126.17</v>
       </c>
       <c r="I28" t="n">
-        <v>227.27</v>
+        <v>146.87</v>
       </c>
       <c r="J28" t="n">
-        <v>32.9</v>
+        <v>29</v>
       </c>
       <c r="K28" t="n">
         <v>-22.1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1701,41 +1701,41 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>122.04276875</v>
+        <v>106.605</v>
       </c>
       <c r="C29" t="n">
-        <v>180.779025</v>
+        <v>192.15</v>
       </c>
       <c r="D29" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E29" t="n">
-        <v>118.488125</v>
+        <v>103.5</v>
       </c>
       <c r="F29" t="n">
-        <v>172.1705</v>
+        <v>183</v>
       </c>
       <c r="G29" t="n">
-        <v>180.78</v>
+        <v>192.15</v>
       </c>
       <c r="H29" t="n">
-        <v>122.04</v>
+        <v>106.61</v>
       </c>
       <c r="I29" t="n">
-        <v>136.73</v>
+        <v>127.99</v>
       </c>
       <c r="J29" t="n">
-        <v>23.8</v>
+        <v>33.4</v>
       </c>
       <c r="K29" t="n">
-        <v>-16.4</v>
+        <v>-26</v>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -1746,221 +1746,221 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>156.045</v>
+        <v>107.635</v>
       </c>
       <c r="C30" t="n">
-        <v>369.6</v>
+        <v>127.575</v>
       </c>
       <c r="D30" t="n">
-        <v>243.5</v>
+        <v>116.5</v>
       </c>
       <c r="E30" t="n">
-        <v>151.5</v>
+        <v>104.5</v>
       </c>
       <c r="F30" t="n">
-        <v>352</v>
+        <v>121.5</v>
       </c>
       <c r="G30" t="n">
-        <v>369.6</v>
+        <v>127.58</v>
       </c>
       <c r="H30" t="n">
-        <v>156.05</v>
+        <v>107.64</v>
       </c>
       <c r="I30" t="n">
-        <v>209.43</v>
+        <v>112.62</v>
       </c>
       <c r="J30" t="n">
-        <v>51.8</v>
+        <v>9.5</v>
       </c>
       <c r="K30" t="n">
-        <v>-35.9</v>
+        <v>-7.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>98.57100000000001</v>
+        <v>170.11119397</v>
       </c>
       <c r="C31" t="n">
-        <v>153.3</v>
+        <v>197.6116716</v>
       </c>
       <c r="D31" t="n">
-        <v>122</v>
+        <v>182.5</v>
       </c>
       <c r="E31" t="n">
-        <v>95.7</v>
+        <v>165.156499</v>
       </c>
       <c r="F31" t="n">
-        <v>146</v>
+        <v>188.201592</v>
       </c>
       <c r="G31" t="n">
-        <v>153.3</v>
+        <v>197.61</v>
       </c>
       <c r="H31" t="n">
-        <v>98.56999999999999</v>
+        <v>170.11</v>
       </c>
       <c r="I31" t="n">
-        <v>112.25</v>
+        <v>176.99</v>
       </c>
       <c r="J31" t="n">
-        <v>25.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-19.2</v>
+        <v>-6.8</v>
       </c>
       <c r="L31" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>106.09</v>
+        <v>2163</v>
       </c>
       <c r="C32" t="n">
-        <v>192.15</v>
+        <v>4698.75</v>
       </c>
       <c r="D32" t="n">
-        <v>143.5</v>
+        <v>3320</v>
       </c>
       <c r="E32" t="n">
-        <v>103</v>
+        <v>2100</v>
       </c>
       <c r="F32" t="n">
-        <v>183</v>
+        <v>4475</v>
       </c>
       <c r="G32" t="n">
-        <v>192.15</v>
+        <v>4698.75</v>
       </c>
       <c r="H32" t="n">
-        <v>106.09</v>
+        <v>2163</v>
       </c>
       <c r="I32" t="n">
-        <v>127.6</v>
+        <v>2796.94</v>
       </c>
       <c r="J32" t="n">
-        <v>33.9</v>
+        <v>41.5</v>
       </c>
       <c r="K32" t="n">
-        <v>-26.1</v>
+        <v>-34.8</v>
       </c>
       <c r="L32" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2163</v>
+        <v>122.04276875</v>
       </c>
       <c r="C33" t="n">
-        <v>4698.75</v>
+        <v>180.779025</v>
       </c>
       <c r="D33" t="n">
-        <v>3285</v>
+        <v>149</v>
       </c>
       <c r="E33" t="n">
-        <v>2100</v>
+        <v>118.488125</v>
       </c>
       <c r="F33" t="n">
-        <v>4475</v>
+        <v>172.1705</v>
       </c>
       <c r="G33" t="n">
-        <v>4698.75</v>
+        <v>180.78</v>
       </c>
       <c r="H33" t="n">
-        <v>2163</v>
+        <v>122.04</v>
       </c>
       <c r="I33" t="n">
-        <v>2796.94</v>
+        <v>136.73</v>
       </c>
       <c r="J33" t="n">
-        <v>43</v>
+        <v>21.3</v>
       </c>
       <c r="K33" t="n">
-        <v>-34.2</v>
+        <v>-18.1</v>
       </c>
       <c r="L33" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>136.92326733</v>
+        <v>146.775</v>
       </c>
       <c r="C34" t="n">
-        <v>209.37295785</v>
+        <v>211.05</v>
       </c>
       <c r="D34" t="n">
-        <v>169</v>
+        <v>176.5</v>
       </c>
       <c r="E34" t="n">
-        <v>132.935211</v>
+        <v>142.5</v>
       </c>
       <c r="F34" t="n">
-        <v>199.402817</v>
+        <v>201</v>
       </c>
       <c r="G34" t="n">
-        <v>209.37</v>
+        <v>211.05</v>
       </c>
       <c r="H34" t="n">
-        <v>136.92</v>
+        <v>146.78</v>
       </c>
       <c r="I34" t="n">
-        <v>155.04</v>
+        <v>162.84</v>
       </c>
       <c r="J34" t="n">
-        <v>23.9</v>
+        <v>19.6</v>
       </c>
       <c r="K34" t="n">
-        <v>-19</v>
+        <v>-16.8</v>
       </c>
       <c r="L34" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -1971,86 +1971,86 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>101.64987909</v>
+        <v>98.57100000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>278.03973015</v>
+        <v>153.3</v>
       </c>
       <c r="D35" t="n">
-        <v>180</v>
+        <v>124</v>
       </c>
       <c r="E35" t="n">
-        <v>98.68920300000001</v>
+        <v>95.7</v>
       </c>
       <c r="F35" t="n">
-        <v>264.799743</v>
+        <v>146</v>
       </c>
       <c r="G35" t="n">
-        <v>278.04</v>
+        <v>153.3</v>
       </c>
       <c r="H35" t="n">
-        <v>101.65</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>145.75</v>
+        <v>112.25</v>
       </c>
       <c r="J35" t="n">
-        <v>54.5</v>
+        <v>23.6</v>
       </c>
       <c r="K35" t="n">
-        <v>-43.5</v>
+        <v>-20.5</v>
       </c>
       <c r="L35" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>90.74299999999999</v>
+        <v>93.28990881</v>
       </c>
       <c r="C36" t="n">
-        <v>119.175</v>
+        <v>114.975</v>
       </c>
       <c r="D36" t="n">
-        <v>103.5</v>
+        <v>104</v>
       </c>
       <c r="E36" t="n">
-        <v>88.09999999999999</v>
+        <v>90.572727</v>
       </c>
       <c r="F36" t="n">
-        <v>113.5</v>
+        <v>109.5</v>
       </c>
       <c r="G36" t="n">
-        <v>119.18</v>
+        <v>114.98</v>
       </c>
       <c r="H36" t="n">
-        <v>90.73999999999999</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>97.84999999999999</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>15.1</v>
+        <v>10.6</v>
       </c>
       <c r="K36" t="n">
-        <v>-12.3</v>
+        <v>-10.3</v>
       </c>
       <c r="L36" t="n">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2061,221 +2061,221 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>93.28990881</v>
+        <v>90.74299999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>114.975</v>
+        <v>119.175</v>
       </c>
       <c r="D37" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E37" t="n">
-        <v>90.572727</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>109.5</v>
+        <v>113.5</v>
       </c>
       <c r="G37" t="n">
-        <v>114.98</v>
+        <v>119.18</v>
       </c>
       <c r="H37" t="n">
-        <v>93.29000000000001</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>98.70999999999999</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>11.6</v>
+        <v>13.5</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.4</v>
+        <v>-13.6</v>
       </c>
       <c r="L37" t="n">
-        <v>1.23</v>
+        <v>0.99</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>98.88</v>
+        <v>127.72</v>
       </c>
       <c r="C38" t="n">
-        <v>156.975</v>
+        <v>223.125</v>
       </c>
       <c r="D38" t="n">
-        <v>125.5</v>
+        <v>177</v>
       </c>
       <c r="E38" t="n">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="F38" t="n">
-        <v>149.5</v>
+        <v>212.5</v>
       </c>
       <c r="G38" t="n">
-        <v>156.97</v>
+        <v>223.12</v>
       </c>
       <c r="H38" t="n">
-        <v>98.88</v>
+        <v>127.72</v>
       </c>
       <c r="I38" t="n">
-        <v>113.4</v>
+        <v>151.57</v>
       </c>
       <c r="J38" t="n">
-        <v>25.1</v>
+        <v>26.1</v>
       </c>
       <c r="K38" t="n">
-        <v>-21.2</v>
+        <v>-27.8</v>
       </c>
       <c r="L38" t="n">
-        <v>1.18</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>146.775</v>
+        <v>624.1800000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>211.05</v>
+        <v>3470.25</v>
       </c>
       <c r="D39" t="n">
-        <v>177</v>
+        <v>2100</v>
       </c>
       <c r="E39" t="n">
-        <v>142.5</v>
+        <v>606</v>
       </c>
       <c r="F39" t="n">
-        <v>201</v>
+        <v>3305</v>
       </c>
       <c r="G39" t="n">
-        <v>211.05</v>
+        <v>3470.25</v>
       </c>
       <c r="H39" t="n">
-        <v>146.78</v>
+        <v>624.1799999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>162.84</v>
+        <v>1335.7</v>
       </c>
       <c r="J39" t="n">
-        <v>19.2</v>
+        <v>65.3</v>
       </c>
       <c r="K39" t="n">
-        <v>-17.1</v>
+        <v>-70.3</v>
       </c>
       <c r="L39" t="n">
-        <v>1.13</v>
+        <v>0.93</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>127.72</v>
+        <v>101.64987909</v>
       </c>
       <c r="C40" t="n">
-        <v>223.125</v>
+        <v>278.03973015</v>
       </c>
       <c r="D40" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="E40" t="n">
-        <v>124</v>
+        <v>98.68920300000001</v>
       </c>
       <c r="F40" t="n">
-        <v>212.5</v>
+        <v>264.799743</v>
       </c>
       <c r="G40" t="n">
-        <v>223.12</v>
+        <v>278.04</v>
       </c>
       <c r="H40" t="n">
-        <v>127.72</v>
+        <v>101.65</v>
       </c>
       <c r="I40" t="n">
-        <v>151.57</v>
+        <v>145.75</v>
       </c>
       <c r="J40" t="n">
-        <v>29</v>
+        <v>44.1</v>
       </c>
       <c r="K40" t="n">
-        <v>-26.2</v>
+        <v>-47.3</v>
       </c>
       <c r="L40" t="n">
-        <v>1.11</v>
+        <v>0.93</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>624.1800000000001</v>
+        <v>39.7065</v>
       </c>
       <c r="C41" t="n">
-        <v>3470.25</v>
+        <v>93.03</v>
       </c>
       <c r="D41" t="n">
-        <v>1980</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>606</v>
+        <v>38.55</v>
       </c>
       <c r="F41" t="n">
-        <v>3305</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>3470.25</v>
+        <v>93.03</v>
       </c>
       <c r="H41" t="n">
-        <v>624.1799999999999</v>
+        <v>39.71</v>
       </c>
       <c r="I41" t="n">
-        <v>1335.7</v>
+        <v>53.04</v>
       </c>
       <c r="J41" t="n">
-        <v>75.3</v>
+        <v>37.6</v>
       </c>
       <c r="K41" t="n">
-        <v>-68.5</v>
+        <v>-41.3</v>
       </c>
       <c r="L41" t="n">
-        <v>1.1</v>
+        <v>0.91</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2286,86 +2286,86 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>113.3</v>
+        <v>703.31864508</v>
       </c>
       <c r="C42" t="n">
-        <v>128.625</v>
+        <v>1826.16</v>
       </c>
       <c r="D42" t="n">
-        <v>121</v>
+        <v>1300</v>
       </c>
       <c r="E42" t="n">
-        <v>110</v>
+        <v>682.833636</v>
       </c>
       <c r="F42" t="n">
-        <v>122.5</v>
+        <v>1739.2</v>
       </c>
       <c r="G42" t="n">
-        <v>128.62</v>
+        <v>1826.16</v>
       </c>
       <c r="H42" t="n">
-        <v>113.3</v>
+        <v>703.3200000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>117.13</v>
+        <v>984.03</v>
       </c>
       <c r="J42" t="n">
-        <v>6.3</v>
+        <v>40.5</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.4</v>
+        <v>-45.9</v>
       </c>
       <c r="L42" t="n">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>252.15184757</v>
+        <v>276.555</v>
       </c>
       <c r="C43" t="n">
-        <v>541.8000000000001</v>
+        <v>459.9</v>
       </c>
       <c r="D43" t="n">
-        <v>398.5</v>
+        <v>377</v>
       </c>
       <c r="E43" t="n">
-        <v>244.807619</v>
+        <v>268.5</v>
       </c>
       <c r="F43" t="n">
-        <v>516</v>
+        <v>438</v>
       </c>
       <c r="G43" t="n">
-        <v>541.8</v>
+        <v>459.9</v>
       </c>
       <c r="H43" t="n">
-        <v>252.15</v>
+        <v>276.56</v>
       </c>
       <c r="I43" t="n">
-        <v>324.56</v>
+        <v>322.39</v>
       </c>
       <c r="J43" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>-36.7</v>
+        <v>-26.6</v>
       </c>
       <c r="L43" t="n">
-        <v>0.98</v>
+        <v>0.83</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -2376,41 +2376,41 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>39.7065</v>
+        <v>252.15184757</v>
       </c>
       <c r="C44" t="n">
-        <v>93.03</v>
+        <v>541.8000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>66.90000000000001</v>
+        <v>411.5</v>
       </c>
       <c r="E44" t="n">
-        <v>38.55</v>
+        <v>244.807619</v>
       </c>
       <c r="F44" t="n">
-        <v>88.59999999999999</v>
+        <v>516</v>
       </c>
       <c r="G44" t="n">
-        <v>93.03</v>
+        <v>541.8</v>
       </c>
       <c r="H44" t="n">
-        <v>39.71</v>
+        <v>252.15</v>
       </c>
       <c r="I44" t="n">
-        <v>53.04</v>
+        <v>324.56</v>
       </c>
       <c r="J44" t="n">
-        <v>39.1</v>
+        <v>31.7</v>
       </c>
       <c r="K44" t="n">
-        <v>-40.6</v>
+        <v>-38.7</v>
       </c>
       <c r="L44" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -2421,86 +2421,86 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>107.635</v>
+        <v>368.225</v>
       </c>
       <c r="C45" t="n">
-        <v>127.575</v>
+        <v>1564.5</v>
       </c>
       <c r="D45" t="n">
-        <v>118</v>
+        <v>1030</v>
       </c>
       <c r="E45" t="n">
-        <v>104.5</v>
+        <v>357.5</v>
       </c>
       <c r="F45" t="n">
-        <v>121.5</v>
+        <v>1490</v>
       </c>
       <c r="G45" t="n">
-        <v>127.58</v>
+        <v>1564.5</v>
       </c>
       <c r="H45" t="n">
-        <v>107.64</v>
+        <v>368.23</v>
       </c>
       <c r="I45" t="n">
-        <v>112.62</v>
+        <v>667.29</v>
       </c>
       <c r="J45" t="n">
-        <v>8.1</v>
+        <v>51.9</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.800000000000001</v>
+        <v>-64.2</v>
       </c>
       <c r="L45" t="n">
-        <v>0.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>276.555</v>
+        <v>387.66964797</v>
       </c>
       <c r="C46" t="n">
-        <v>459.9</v>
+        <v>835.8000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>372</v>
+        <v>636</v>
       </c>
       <c r="E46" t="n">
-        <v>268.5</v>
+        <v>376.378299</v>
       </c>
       <c r="F46" t="n">
-        <v>438</v>
+        <v>796</v>
       </c>
       <c r="G46" t="n">
-        <v>459.9</v>
+        <v>835.8</v>
       </c>
       <c r="H46" t="n">
-        <v>276.56</v>
+        <v>387.67</v>
       </c>
       <c r="I46" t="n">
-        <v>322.39</v>
+        <v>499.7</v>
       </c>
       <c r="J46" t="n">
-        <v>23.6</v>
+        <v>31.4</v>
       </c>
       <c r="K46" t="n">
-        <v>-25.7</v>
+        <v>-39</v>
       </c>
       <c r="L46" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -2511,45 +2511,45 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>113.85245492</v>
+        <v>136.92326733</v>
       </c>
       <c r="C47" t="n">
-        <v>196.35</v>
+        <v>209.37295785</v>
       </c>
       <c r="D47" t="n">
-        <v>158.5</v>
+        <v>177.5</v>
       </c>
       <c r="E47" t="n">
-        <v>110.536364</v>
+        <v>132.935211</v>
       </c>
       <c r="F47" t="n">
-        <v>187</v>
+        <v>199.402817</v>
       </c>
       <c r="G47" t="n">
-        <v>196.35</v>
+        <v>209.37</v>
       </c>
       <c r="H47" t="n">
-        <v>113.85</v>
+        <v>136.92</v>
       </c>
       <c r="I47" t="n">
-        <v>134.48</v>
+        <v>155.04</v>
       </c>
       <c r="J47" t="n">
-        <v>23.9</v>
+        <v>18</v>
       </c>
       <c r="K47" t="n">
-        <v>-28.2</v>
+        <v>-22.9</v>
       </c>
       <c r="L47" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
         <v>1651.86</v>
       </c>
       <c r="D48" t="n">
-        <v>1295</v>
+        <v>1305</v>
       </c>
       <c r="E48" t="n">
         <v>818.261887</v>
@@ -2584,13 +2584,13 @@
         <v>1045.07</v>
       </c>
       <c r="J48" t="n">
-        <v>27.6</v>
+        <v>26.6</v>
       </c>
       <c r="K48" t="n">
-        <v>-34.9</v>
+        <v>-35.4</v>
       </c>
       <c r="L48" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -2601,131 +2601,131 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2554.4</v>
+        <v>30.8485</v>
       </c>
       <c r="C49" t="n">
-        <v>5922</v>
+        <v>37.3275</v>
       </c>
       <c r="D49" t="n">
-        <v>4450</v>
+        <v>34.55</v>
       </c>
       <c r="E49" t="n">
-        <v>2480</v>
+        <v>29.95</v>
       </c>
       <c r="F49" t="n">
-        <v>5640</v>
+        <v>35.55</v>
       </c>
       <c r="G49" t="n">
-        <v>5922</v>
+        <v>37.33</v>
       </c>
       <c r="H49" t="n">
-        <v>2554.4</v>
+        <v>30.85</v>
       </c>
       <c r="I49" t="n">
-        <v>3396.3</v>
+        <v>32.47</v>
       </c>
       <c r="J49" t="n">
-        <v>33.1</v>
+        <v>8</v>
       </c>
       <c r="K49" t="n">
-        <v>-42.6</v>
+        <v>-10.7</v>
       </c>
       <c r="L49" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>30.8485</v>
+        <v>294.13217351</v>
       </c>
       <c r="C50" t="n">
-        <v>37.3275</v>
+        <v>556.1286129</v>
       </c>
       <c r="D50" t="n">
-        <v>34.5</v>
+        <v>445</v>
       </c>
       <c r="E50" t="n">
-        <v>29.95</v>
+        <v>285.565217</v>
       </c>
       <c r="F50" t="n">
-        <v>35.55</v>
+        <v>529.646298</v>
       </c>
       <c r="G50" t="n">
-        <v>37.33</v>
+        <v>556.13</v>
       </c>
       <c r="H50" t="n">
-        <v>30.85</v>
+        <v>294.13</v>
       </c>
       <c r="I50" t="n">
-        <v>32.47</v>
+        <v>359.63</v>
       </c>
       <c r="J50" t="n">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="K50" t="n">
-        <v>-10.6</v>
+        <v>-33.9</v>
       </c>
       <c r="L50" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>387.66964797</v>
+        <v>143.685</v>
       </c>
       <c r="C51" t="n">
-        <v>835.8000000000001</v>
+        <v>275.1</v>
       </c>
       <c r="D51" t="n">
-        <v>641</v>
+        <v>219</v>
       </c>
       <c r="E51" t="n">
-        <v>376.378299</v>
+        <v>139.5</v>
       </c>
       <c r="F51" t="n">
-        <v>796</v>
+        <v>262</v>
       </c>
       <c r="G51" t="n">
-        <v>835.8</v>
+        <v>275.1</v>
       </c>
       <c r="H51" t="n">
-        <v>387.67</v>
+        <v>143.69</v>
       </c>
       <c r="I51" t="n">
-        <v>499.7</v>
+        <v>176.54</v>
       </c>
       <c r="J51" t="n">
-        <v>30.4</v>
+        <v>25.6</v>
       </c>
       <c r="K51" t="n">
-        <v>-39.5</v>
+        <v>-34.4</v>
       </c>
       <c r="L51" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -2736,86 +2736,86 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>968.2</v>
+        <v>690.1</v>
       </c>
       <c r="C52" t="n">
-        <v>1680</v>
+        <v>874.6500000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>1375</v>
+        <v>797</v>
       </c>
       <c r="E52" t="n">
-        <v>940</v>
+        <v>670</v>
       </c>
       <c r="F52" t="n">
-        <v>1600</v>
+        <v>833</v>
       </c>
       <c r="G52" t="n">
-        <v>1680</v>
+        <v>874.65</v>
       </c>
       <c r="H52" t="n">
-        <v>968.2</v>
+        <v>690.1</v>
       </c>
       <c r="I52" t="n">
-        <v>1146.15</v>
+        <v>736.24</v>
       </c>
       <c r="J52" t="n">
-        <v>22.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-29.6</v>
+        <v>-13.4</v>
       </c>
       <c r="L52" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>294.13217351</v>
+        <v>451.14</v>
       </c>
       <c r="C53" t="n">
-        <v>556.1286129</v>
+        <v>1018.5</v>
       </c>
       <c r="D53" t="n">
-        <v>443.5</v>
+        <v>783</v>
       </c>
       <c r="E53" t="n">
-        <v>285.565217</v>
+        <v>438</v>
       </c>
       <c r="F53" t="n">
-        <v>529.646298</v>
+        <v>970</v>
       </c>
       <c r="G53" t="n">
-        <v>556.13</v>
+        <v>1018.5</v>
       </c>
       <c r="H53" t="n">
-        <v>294.13</v>
+        <v>451.14</v>
       </c>
       <c r="I53" t="n">
-        <v>359.63</v>
+        <v>592.98</v>
       </c>
       <c r="J53" t="n">
-        <v>25.4</v>
+        <v>30.1</v>
       </c>
       <c r="K53" t="n">
-        <v>-33.7</v>
+        <v>-42.4</v>
       </c>
       <c r="L53" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -2826,41 +2826,41 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>143.685</v>
+        <v>174.585</v>
       </c>
       <c r="C54" t="n">
-        <v>275.1</v>
+        <v>282.975</v>
       </c>
       <c r="D54" t="n">
-        <v>219.5</v>
+        <v>238</v>
       </c>
       <c r="E54" t="n">
-        <v>139.5</v>
+        <v>169.5</v>
       </c>
       <c r="F54" t="n">
-        <v>262</v>
+        <v>269.5</v>
       </c>
       <c r="G54" t="n">
-        <v>275.1</v>
+        <v>282.98</v>
       </c>
       <c r="H54" t="n">
-        <v>143.69</v>
+        <v>174.59</v>
       </c>
       <c r="I54" t="n">
-        <v>176.54</v>
+        <v>201.68</v>
       </c>
       <c r="J54" t="n">
-        <v>25.3</v>
+        <v>18.9</v>
       </c>
       <c r="K54" t="n">
-        <v>-34.5</v>
+        <v>-26.6</v>
       </c>
       <c r="L54" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -2871,41 +2871,41 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>368.225</v>
+        <v>2199.05</v>
       </c>
       <c r="C55" t="n">
-        <v>1564.5</v>
+        <v>5628</v>
       </c>
       <c r="D55" t="n">
-        <v>1065</v>
+        <v>4230</v>
       </c>
       <c r="E55" t="n">
-        <v>357.5</v>
+        <v>2135</v>
       </c>
       <c r="F55" t="n">
-        <v>1490</v>
+        <v>5360</v>
       </c>
       <c r="G55" t="n">
-        <v>1564.5</v>
+        <v>5628</v>
       </c>
       <c r="H55" t="n">
-        <v>368.23</v>
+        <v>2199.05</v>
       </c>
       <c r="I55" t="n">
-        <v>667.29</v>
+        <v>3056.29</v>
       </c>
       <c r="J55" t="n">
-        <v>46.9</v>
+        <v>33</v>
       </c>
       <c r="K55" t="n">
-        <v>-65.40000000000001</v>
+        <v>-48</v>
       </c>
       <c r="L55" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -2916,41 +2916,41 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>992.8782458600001</v>
+        <v>86.31399999999999</v>
       </c>
       <c r="C56" t="n">
-        <v>2700.13103115</v>
+        <v>245.175</v>
       </c>
       <c r="D56" t="n">
-        <v>1990</v>
+        <v>184.5</v>
       </c>
       <c r="E56" t="n">
-        <v>963.959462</v>
+        <v>83.8</v>
       </c>
       <c r="F56" t="n">
-        <v>2571.553363</v>
+        <v>233.5</v>
       </c>
       <c r="G56" t="n">
-        <v>2700.13</v>
+        <v>245.18</v>
       </c>
       <c r="H56" t="n">
-        <v>992.88</v>
+        <v>86.31</v>
       </c>
       <c r="I56" t="n">
-        <v>1419.69</v>
+        <v>126.03</v>
       </c>
       <c r="J56" t="n">
-        <v>35.7</v>
+        <v>32.9</v>
       </c>
       <c r="K56" t="n">
-        <v>-50.1</v>
+        <v>-53.2</v>
       </c>
       <c r="L56" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -2961,41 +2961,41 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>606.49914566</v>
+        <v>2554.4</v>
       </c>
       <c r="C57" t="n">
-        <v>1647.3453759</v>
+        <v>5922</v>
       </c>
       <c r="D57" t="n">
-        <v>1220</v>
+        <v>4650</v>
       </c>
       <c r="E57" t="n">
-        <v>588.834122</v>
+        <v>2480</v>
       </c>
       <c r="F57" t="n">
-        <v>1568.900358</v>
+        <v>5640</v>
       </c>
       <c r="G57" t="n">
-        <v>1647.35</v>
+        <v>5922</v>
       </c>
       <c r="H57" t="n">
-        <v>606.5</v>
+        <v>2554.4</v>
       </c>
       <c r="I57" t="n">
-        <v>866.71</v>
+        <v>3396.3</v>
       </c>
       <c r="J57" t="n">
-        <v>35</v>
+        <v>27.4</v>
       </c>
       <c r="K57" t="n">
-        <v>-50.3</v>
+        <v>-45.1</v>
       </c>
       <c r="L57" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -3006,86 +3006,86 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1071.2</v>
+        <v>113.3</v>
       </c>
       <c r="C58" t="n">
-        <v>1743</v>
+        <v>129.675</v>
       </c>
       <c r="D58" t="n">
-        <v>1470</v>
+        <v>123.5</v>
       </c>
       <c r="E58" t="n">
-        <v>1040</v>
+        <v>110</v>
       </c>
       <c r="F58" t="n">
-        <v>1660</v>
+        <v>123.5</v>
       </c>
       <c r="G58" t="n">
-        <v>1743</v>
+        <v>129.68</v>
       </c>
       <c r="H58" t="n">
-        <v>1071.2</v>
+        <v>113.3</v>
       </c>
       <c r="I58" t="n">
-        <v>1239.15</v>
+        <v>117.39</v>
       </c>
       <c r="J58" t="n">
-        <v>18.6</v>
+        <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>-27.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>172.525</v>
+        <v>1012.34644684</v>
       </c>
       <c r="C59" t="n">
-        <v>282.975</v>
+        <v>2700.13103115</v>
       </c>
       <c r="D59" t="n">
-        <v>238.5</v>
+        <v>2075</v>
       </c>
       <c r="E59" t="n">
-        <v>167.5</v>
+        <v>982.860628</v>
       </c>
       <c r="F59" t="n">
-        <v>269.5</v>
+        <v>2571.553363</v>
       </c>
       <c r="G59" t="n">
-        <v>282.98</v>
+        <v>2700.13</v>
       </c>
       <c r="H59" t="n">
-        <v>172.53</v>
+        <v>1012.35</v>
       </c>
       <c r="I59" t="n">
-        <v>200.14</v>
+        <v>1434.29</v>
       </c>
       <c r="J59" t="n">
-        <v>18.6</v>
+        <v>30.1</v>
       </c>
       <c r="K59" t="n">
-        <v>-27.7</v>
+        <v>-51.2</v>
       </c>
       <c r="L59" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -3096,41 +3096,41 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>100.38161743</v>
+        <v>204.455</v>
       </c>
       <c r="C60" t="n">
-        <v>347.47028925</v>
+        <v>530.25</v>
       </c>
       <c r="D60" t="n">
-        <v>249</v>
+        <v>409.5</v>
       </c>
       <c r="E60" t="n">
-        <v>97.457881</v>
+        <v>198.5</v>
       </c>
       <c r="F60" t="n">
-        <v>330.924085</v>
+        <v>505</v>
       </c>
       <c r="G60" t="n">
-        <v>347.47</v>
+        <v>530.25</v>
       </c>
       <c r="H60" t="n">
-        <v>100.38</v>
+        <v>204.46</v>
       </c>
       <c r="I60" t="n">
-        <v>162.15</v>
+        <v>285.9</v>
       </c>
       <c r="J60" t="n">
-        <v>39.5</v>
+        <v>29.5</v>
       </c>
       <c r="K60" t="n">
-        <v>-59.7</v>
+        <v>-50.1</v>
       </c>
       <c r="L60" t="n">
-        <v>0.66</v>
+        <v>0.59</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -3141,86 +3141,86 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>181.795</v>
+        <v>102.81265536</v>
       </c>
       <c r="C61" t="n">
-        <v>262.5</v>
+        <v>347.47028925</v>
       </c>
       <c r="D61" t="n">
-        <v>230.5</v>
+        <v>258</v>
       </c>
       <c r="E61" t="n">
-        <v>176.5</v>
+        <v>99.818112</v>
       </c>
       <c r="F61" t="n">
-        <v>250</v>
+        <v>330.924085</v>
       </c>
       <c r="G61" t="n">
-        <v>262.5</v>
+        <v>347.47</v>
       </c>
       <c r="H61" t="n">
-        <v>181.8</v>
+        <v>102.81</v>
       </c>
       <c r="I61" t="n">
-        <v>201.97</v>
+        <v>163.98</v>
       </c>
       <c r="J61" t="n">
-        <v>13.9</v>
+        <v>34.7</v>
       </c>
       <c r="K61" t="n">
-        <v>-21.1</v>
+        <v>-60.2</v>
       </c>
       <c r="L61" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>316.725</v>
+        <v>40.38815194</v>
       </c>
       <c r="C62" t="n">
-        <v>627.9</v>
+        <v>60.31306155000001</v>
       </c>
       <c r="D62" t="n">
-        <v>506</v>
+        <v>53.3</v>
       </c>
       <c r="E62" t="n">
-        <v>307.5</v>
+        <v>39.211798</v>
       </c>
       <c r="F62" t="n">
-        <v>598</v>
+        <v>57.441011</v>
       </c>
       <c r="G62" t="n">
-        <v>627.9</v>
+        <v>60.31</v>
       </c>
       <c r="H62" t="n">
-        <v>316.73</v>
+        <v>40.39</v>
       </c>
       <c r="I62" t="n">
-        <v>394.52</v>
+        <v>45.37</v>
       </c>
       <c r="J62" t="n">
-        <v>24.1</v>
+        <v>13.2</v>
       </c>
       <c r="K62" t="n">
-        <v>-37.4</v>
+        <v>-24.2</v>
       </c>
       <c r="L62" t="n">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -3231,41 +3231,41 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>115.875</v>
+        <v>317.755</v>
       </c>
       <c r="C63" t="n">
-        <v>168.525</v>
+        <v>627.9</v>
       </c>
       <c r="D63" t="n">
-        <v>148.5</v>
+        <v>520</v>
       </c>
       <c r="E63" t="n">
-        <v>112.5</v>
+        <v>308.5</v>
       </c>
       <c r="F63" t="n">
-        <v>160.5</v>
+        <v>598</v>
       </c>
       <c r="G63" t="n">
-        <v>168.53</v>
+        <v>627.9</v>
       </c>
       <c r="H63" t="n">
-        <v>115.88</v>
+        <v>317.75</v>
       </c>
       <c r="I63" t="n">
-        <v>129.04</v>
+        <v>395.29</v>
       </c>
       <c r="J63" t="n">
-        <v>13.5</v>
+        <v>20.8</v>
       </c>
       <c r="K63" t="n">
-        <v>-22</v>
+        <v>-38.9</v>
       </c>
       <c r="L63" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -3276,41 +3276,41 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2199.05</v>
+        <v>181.795</v>
       </c>
       <c r="C64" t="n">
-        <v>5628</v>
+        <v>262.5</v>
       </c>
       <c r="D64" t="n">
-        <v>4330</v>
+        <v>235</v>
       </c>
       <c r="E64" t="n">
-        <v>2135</v>
+        <v>176.5</v>
       </c>
       <c r="F64" t="n">
-        <v>5360</v>
+        <v>250</v>
       </c>
       <c r="G64" t="n">
-        <v>5628</v>
+        <v>262.5</v>
       </c>
       <c r="H64" t="n">
-        <v>2199.05</v>
+        <v>181.8</v>
       </c>
       <c r="I64" t="n">
-        <v>3056.29</v>
+        <v>201.97</v>
       </c>
       <c r="J64" t="n">
-        <v>30</v>
+        <v>11.7</v>
       </c>
       <c r="K64" t="n">
-        <v>-49.2</v>
+        <v>-22.6</v>
       </c>
       <c r="L64" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -3321,41 +3321,41 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>40.38815194</v>
+        <v>113.85245492</v>
       </c>
       <c r="C65" t="n">
-        <v>60.31306155000001</v>
+        <v>196.35</v>
       </c>
       <c r="D65" t="n">
-        <v>53.2</v>
+        <v>168</v>
       </c>
       <c r="E65" t="n">
-        <v>39.211798</v>
+        <v>110.536364</v>
       </c>
       <c r="F65" t="n">
-        <v>57.441011</v>
+        <v>187</v>
       </c>
       <c r="G65" t="n">
-        <v>60.31</v>
+        <v>196.35</v>
       </c>
       <c r="H65" t="n">
-        <v>40.39</v>
+        <v>113.85</v>
       </c>
       <c r="I65" t="n">
-        <v>45.37</v>
+        <v>134.48</v>
       </c>
       <c r="J65" t="n">
-        <v>13.4</v>
+        <v>16.9</v>
       </c>
       <c r="K65" t="n">
-        <v>-24.1</v>
+        <v>-32.2</v>
       </c>
       <c r="L65" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -3366,41 +3366,41 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3293.32097618</v>
+        <v>971.2900000000001</v>
       </c>
       <c r="C66" t="n">
-        <v>6000.22536855</v>
+        <v>1680</v>
       </c>
       <c r="D66" t="n">
-        <v>5035</v>
+        <v>1440</v>
       </c>
       <c r="E66" t="n">
-        <v>3197.399006</v>
+        <v>943</v>
       </c>
       <c r="F66" t="n">
-        <v>5714.500351</v>
+        <v>1600</v>
       </c>
       <c r="G66" t="n">
-        <v>6000.23</v>
+        <v>1680</v>
       </c>
       <c r="H66" t="n">
-        <v>3293.32</v>
+        <v>971.29</v>
       </c>
       <c r="I66" t="n">
-        <v>3970.05</v>
+        <v>1148.47</v>
       </c>
       <c r="J66" t="n">
-        <v>19.2</v>
+        <v>16.7</v>
       </c>
       <c r="K66" t="n">
-        <v>-34.6</v>
+        <v>-32.5</v>
       </c>
       <c r="L66" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -3411,86 +3411,86 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>156.56</v>
+        <v>61.32276701</v>
       </c>
       <c r="C67" t="n">
-        <v>213.3067608</v>
+        <v>103.53</v>
       </c>
       <c r="D67" t="n">
-        <v>193.5</v>
+        <v>89.3</v>
       </c>
       <c r="E67" t="n">
-        <v>152</v>
+        <v>59.536667</v>
       </c>
       <c r="F67" t="n">
-        <v>203.149296</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>213.31</v>
+        <v>103.53</v>
       </c>
       <c r="H67" t="n">
-        <v>156.56</v>
+        <v>61.32</v>
       </c>
       <c r="I67" t="n">
-        <v>170.75</v>
+        <v>71.87</v>
       </c>
       <c r="J67" t="n">
-        <v>10.2</v>
+        <v>15.9</v>
       </c>
       <c r="K67" t="n">
-        <v>-19.1</v>
+        <v>-31.3</v>
       </c>
       <c r="L67" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2837.65</v>
+        <v>606.49914566</v>
       </c>
       <c r="C68" t="n">
-        <v>12064.5</v>
+        <v>1647.3453759</v>
       </c>
       <c r="D68" t="n">
-        <v>8890</v>
+        <v>1305</v>
       </c>
       <c r="E68" t="n">
-        <v>2755</v>
+        <v>588.834122</v>
       </c>
       <c r="F68" t="n">
-        <v>11490</v>
+        <v>1568.900358</v>
       </c>
       <c r="G68" t="n">
-        <v>12064.5</v>
+        <v>1647.35</v>
       </c>
       <c r="H68" t="n">
-        <v>2837.65</v>
+        <v>606.5</v>
       </c>
       <c r="I68" t="n">
-        <v>5144.36</v>
+        <v>866.71</v>
       </c>
       <c r="J68" t="n">
-        <v>35.7</v>
+        <v>26.2</v>
       </c>
       <c r="K68" t="n">
-        <v>-68.09999999999999</v>
+        <v>-53.5</v>
       </c>
       <c r="L68" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -3501,41 +3501,41 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>84.12256788000001</v>
+        <v>578.80953618</v>
       </c>
       <c r="C69" t="n">
-        <v>245.175</v>
+        <v>1764</v>
       </c>
       <c r="D69" t="n">
-        <v>190</v>
+        <v>1380</v>
       </c>
       <c r="E69" t="n">
-        <v>81.67239600000001</v>
+        <v>561.951006</v>
       </c>
       <c r="F69" t="n">
-        <v>233.5</v>
+        <v>1680</v>
       </c>
       <c r="G69" t="n">
-        <v>245.18</v>
+        <v>1764</v>
       </c>
       <c r="H69" t="n">
-        <v>84.12</v>
+        <v>578.8099999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>124.39</v>
+        <v>875.11</v>
       </c>
       <c r="J69" t="n">
-        <v>29</v>
+        <v>27.8</v>
       </c>
       <c r="K69" t="n">
-        <v>-55.7</v>
+        <v>-58.1</v>
       </c>
       <c r="L69" t="n">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -3546,41 +3546,41 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>60.26215232</v>
+        <v>925.3533287</v>
       </c>
       <c r="C70" t="n">
-        <v>103.53</v>
+        <v>2910.13596825</v>
       </c>
       <c r="D70" t="n">
-        <v>89.09999999999999</v>
+        <v>2265</v>
       </c>
       <c r="E70" t="n">
-        <v>58.506944</v>
+        <v>898.40129</v>
       </c>
       <c r="F70" t="n">
-        <v>98.59999999999999</v>
+        <v>2771.558065</v>
       </c>
       <c r="G70" t="n">
-        <v>103.53</v>
+        <v>2910.14</v>
       </c>
       <c r="H70" t="n">
-        <v>60.26</v>
+        <v>925.35</v>
       </c>
       <c r="I70" t="n">
-        <v>71.08</v>
+        <v>1421.55</v>
       </c>
       <c r="J70" t="n">
-        <v>16.2</v>
+        <v>28.5</v>
       </c>
       <c r="K70" t="n">
-        <v>-32.4</v>
+        <v>-59.1</v>
       </c>
       <c r="L70" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -3591,41 +3591,41 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>451.14</v>
+        <v>1071.2</v>
       </c>
       <c r="C71" t="n">
-        <v>1018.5</v>
+        <v>1743</v>
       </c>
       <c r="D71" t="n">
-        <v>829</v>
+        <v>1530</v>
       </c>
       <c r="E71" t="n">
-        <v>438</v>
+        <v>1040</v>
       </c>
       <c r="F71" t="n">
-        <v>970</v>
+        <v>1660</v>
       </c>
       <c r="G71" t="n">
-        <v>1018.5</v>
+        <v>1743</v>
       </c>
       <c r="H71" t="n">
-        <v>451.14</v>
+        <v>1071.2</v>
       </c>
       <c r="I71" t="n">
-        <v>592.98</v>
+        <v>1239.15</v>
       </c>
       <c r="J71" t="n">
-        <v>22.9</v>
+        <v>13.9</v>
       </c>
       <c r="K71" t="n">
-        <v>-45.6</v>
+        <v>-30</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -3636,41 +3636,41 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>196.73</v>
+        <v>2194.20362855</v>
       </c>
       <c r="C72" t="n">
-        <v>530.25</v>
+        <v>6219.16666665</v>
       </c>
       <c r="D72" t="n">
-        <v>421</v>
+        <v>5040</v>
       </c>
       <c r="E72" t="n">
-        <v>191</v>
+        <v>2130.294785</v>
       </c>
       <c r="F72" t="n">
-        <v>505</v>
+        <v>5923.015873</v>
       </c>
       <c r="G72" t="n">
-        <v>530.25</v>
+        <v>6219.17</v>
       </c>
       <c r="H72" t="n">
-        <v>196.73</v>
+        <v>2194.2</v>
       </c>
       <c r="I72" t="n">
-        <v>280.11</v>
+        <v>3200.44</v>
       </c>
       <c r="J72" t="n">
-        <v>26</v>
+        <v>23.4</v>
       </c>
       <c r="K72" t="n">
-        <v>-53.3</v>
+        <v>-56.5</v>
       </c>
       <c r="L72" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>642.6</v>
       </c>
       <c r="D73" t="n">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="E73" t="n">
         <v>236.525526</v>
@@ -3709,13 +3709,13 @@
         <v>343.37</v>
       </c>
       <c r="J73" t="n">
-        <v>25.5</v>
+        <v>21.2</v>
       </c>
       <c r="K73" t="n">
-        <v>-52.4</v>
+        <v>-54</v>
       </c>
       <c r="L73" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -3726,86 +3726,86 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>690.1</v>
+        <v>312.09</v>
       </c>
       <c r="C74" t="n">
-        <v>874.6500000000001</v>
+        <v>1060.5</v>
       </c>
       <c r="D74" t="n">
-        <v>819</v>
+        <v>851</v>
       </c>
       <c r="E74" t="n">
-        <v>670</v>
+        <v>303</v>
       </c>
       <c r="F74" t="n">
-        <v>833</v>
+        <v>1010</v>
       </c>
       <c r="G74" t="n">
-        <v>874.65</v>
+        <v>1060.5</v>
       </c>
       <c r="H74" t="n">
-        <v>690.1</v>
+        <v>312.09</v>
       </c>
       <c r="I74" t="n">
-        <v>736.24</v>
+        <v>499.19</v>
       </c>
       <c r="J74" t="n">
-        <v>6.8</v>
+        <v>24.6</v>
       </c>
       <c r="K74" t="n">
-        <v>-15.7</v>
+        <v>-63.3</v>
       </c>
       <c r="L74" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>792.5763613900001</v>
+        <v>156.56</v>
       </c>
       <c r="C75" t="n">
-        <v>2910.13596825</v>
+        <v>213.3067608</v>
       </c>
       <c r="D75" t="n">
-        <v>2270</v>
+        <v>197.5</v>
       </c>
       <c r="E75" t="n">
-        <v>769.491613</v>
+        <v>152</v>
       </c>
       <c r="F75" t="n">
-        <v>2771.558065</v>
+        <v>203.149296</v>
       </c>
       <c r="G75" t="n">
-        <v>2910.14</v>
+        <v>213.31</v>
       </c>
       <c r="H75" t="n">
-        <v>792.58</v>
+        <v>156.56</v>
       </c>
       <c r="I75" t="n">
-        <v>1321.97</v>
+        <v>170.75</v>
       </c>
       <c r="J75" t="n">
-        <v>28.2</v>
+        <v>8</v>
       </c>
       <c r="K75" t="n">
-        <v>-65.09999999999999</v>
+        <v>-20.7</v>
       </c>
       <c r="L75" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -3816,41 +3816,41 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>39.72351972</v>
+        <v>33.1145</v>
       </c>
       <c r="C76" t="n">
-        <v>88.515</v>
+        <v>47.9325</v>
       </c>
       <c r="D76" t="n">
-        <v>74.3</v>
+        <v>43.85</v>
       </c>
       <c r="E76" t="n">
-        <v>38.566524</v>
+        <v>32.15</v>
       </c>
       <c r="F76" t="n">
-        <v>84.3</v>
+        <v>45.65</v>
       </c>
       <c r="G76" t="n">
-        <v>88.52</v>
+        <v>47.93</v>
       </c>
       <c r="H76" t="n">
-        <v>39.72</v>
+        <v>33.11</v>
       </c>
       <c r="I76" t="n">
-        <v>51.92</v>
+        <v>36.82</v>
       </c>
       <c r="J76" t="n">
-        <v>19.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-46.5</v>
+        <v>-24.5</v>
       </c>
       <c r="L76" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -3861,41 +3861,41 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1302.95</v>
+        <v>306.94</v>
       </c>
       <c r="C77" t="n">
-        <v>3160.5</v>
+        <v>616.35</v>
       </c>
       <c r="D77" t="n">
-        <v>2620</v>
+        <v>531</v>
       </c>
       <c r="E77" t="n">
-        <v>1265</v>
+        <v>298</v>
       </c>
       <c r="F77" t="n">
-        <v>3010</v>
+        <v>587</v>
       </c>
       <c r="G77" t="n">
-        <v>3160.5</v>
+        <v>616.35</v>
       </c>
       <c r="H77" t="n">
-        <v>1302.95</v>
+        <v>306.94</v>
       </c>
       <c r="I77" t="n">
-        <v>1767.34</v>
+        <v>384.29</v>
       </c>
       <c r="J77" t="n">
-        <v>20.6</v>
+        <v>16.1</v>
       </c>
       <c r="K77" t="n">
-        <v>-50.3</v>
+        <v>-42.2</v>
       </c>
       <c r="L77" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -3906,41 +3906,41 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2194.20362855</v>
+        <v>1457.45</v>
       </c>
       <c r="C78" t="n">
-        <v>6219.16666665</v>
+        <v>5218.5</v>
       </c>
       <c r="D78" t="n">
-        <v>5045</v>
+        <v>4195</v>
       </c>
       <c r="E78" t="n">
-        <v>2130.294785</v>
+        <v>1415</v>
       </c>
       <c r="F78" t="n">
-        <v>5923.015873</v>
+        <v>4970</v>
       </c>
       <c r="G78" t="n">
-        <v>6219.17</v>
+        <v>5218.5</v>
       </c>
       <c r="H78" t="n">
-        <v>2194.2</v>
+        <v>1457.45</v>
       </c>
       <c r="I78" t="n">
-        <v>3200.44</v>
+        <v>2397.71</v>
       </c>
       <c r="J78" t="n">
-        <v>23.3</v>
+        <v>24.4</v>
       </c>
       <c r="K78" t="n">
-        <v>-56.5</v>
+        <v>-65.3</v>
       </c>
       <c r="L78" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -3951,38 +3951,38 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>7264.04618369</v>
+        <v>3293.32097618</v>
       </c>
       <c r="C79" t="n">
-        <v>20778.1652799</v>
+        <v>6000.22536855</v>
       </c>
       <c r="D79" t="n">
-        <v>17145</v>
+        <v>5265</v>
       </c>
       <c r="E79" t="n">
-        <v>7052.472023</v>
+        <v>3197.399006</v>
       </c>
       <c r="F79" t="n">
-        <v>19788.728838</v>
+        <v>5714.500351</v>
       </c>
       <c r="G79" t="n">
-        <v>20778.17</v>
+        <v>6000.23</v>
       </c>
       <c r="H79" t="n">
-        <v>7264.05</v>
+        <v>3293.32</v>
       </c>
       <c r="I79" t="n">
-        <v>10642.58</v>
+        <v>3970.05</v>
       </c>
       <c r="J79" t="n">
-        <v>21.2</v>
+        <v>14</v>
       </c>
       <c r="K79" t="n">
-        <v>-57.6</v>
+        <v>-37.4</v>
       </c>
       <c r="L79" t="n">
         <v>0.37</v>
@@ -3996,41 +3996,41 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>33.1145</v>
+        <v>7351.19423237</v>
       </c>
       <c r="C80" t="n">
-        <v>47.9325</v>
+        <v>20778.1652799</v>
       </c>
       <c r="D80" t="n">
-        <v>43.9</v>
+        <v>17265</v>
       </c>
       <c r="E80" t="n">
-        <v>32.15</v>
+        <v>7137.081779</v>
       </c>
       <c r="F80" t="n">
-        <v>45.65</v>
+        <v>19788.728838</v>
       </c>
       <c r="G80" t="n">
-        <v>47.93</v>
+        <v>20778.17</v>
       </c>
       <c r="H80" t="n">
-        <v>33.11</v>
+        <v>7351.19</v>
       </c>
       <c r="I80" t="n">
-        <v>36.82</v>
+        <v>10707.94</v>
       </c>
       <c r="J80" t="n">
-        <v>9.199999999999999</v>
+        <v>20.3</v>
       </c>
       <c r="K80" t="n">
-        <v>-24.6</v>
+        <v>-57.4</v>
       </c>
       <c r="L80" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -4041,41 +4041,41 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>299.73</v>
+        <v>115.875</v>
       </c>
       <c r="C81" t="n">
-        <v>616.35</v>
+        <v>168.525</v>
       </c>
       <c r="D81" t="n">
-        <v>533</v>
+        <v>155</v>
       </c>
       <c r="E81" t="n">
-        <v>291</v>
+        <v>112.5</v>
       </c>
       <c r="F81" t="n">
-        <v>587</v>
+        <v>160.5</v>
       </c>
       <c r="G81" t="n">
-        <v>616.35</v>
+        <v>168.53</v>
       </c>
       <c r="H81" t="n">
-        <v>299.73</v>
+        <v>115.88</v>
       </c>
       <c r="I81" t="n">
-        <v>378.88</v>
+        <v>129.04</v>
       </c>
       <c r="J81" t="n">
-        <v>15.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-43.8</v>
+        <v>-25.2</v>
       </c>
       <c r="L81" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -4086,41 +4086,41 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1454.99488479</v>
+        <v>3182.7</v>
       </c>
       <c r="C82" t="n">
-        <v>5218.5</v>
+        <v>12064.5</v>
       </c>
       <c r="D82" t="n">
-        <v>4335</v>
+        <v>9900</v>
       </c>
       <c r="E82" t="n">
-        <v>1412.616393</v>
+        <v>3090</v>
       </c>
       <c r="F82" t="n">
-        <v>4970</v>
+        <v>11490</v>
       </c>
       <c r="G82" t="n">
-        <v>5218.5</v>
+        <v>12064.5</v>
       </c>
       <c r="H82" t="n">
-        <v>1454.99</v>
+        <v>3182.7</v>
       </c>
       <c r="I82" t="n">
-        <v>2395.87</v>
+        <v>5403.15</v>
       </c>
       <c r="J82" t="n">
-        <v>20.4</v>
+        <v>21.9</v>
       </c>
       <c r="K82" t="n">
-        <v>-66.40000000000001</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -4131,131 +4131,131 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>282.735</v>
+        <v>65.405</v>
       </c>
       <c r="C83" t="n">
-        <v>565.95</v>
+        <v>85.05</v>
       </c>
       <c r="D83" t="n">
-        <v>503</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E83" t="n">
-        <v>274.5</v>
+        <v>63.5</v>
       </c>
       <c r="F83" t="n">
-        <v>539</v>
+        <v>81</v>
       </c>
       <c r="G83" t="n">
-        <v>565.95</v>
+        <v>85.05</v>
       </c>
       <c r="H83" t="n">
-        <v>282.74</v>
+        <v>65.41</v>
       </c>
       <c r="I83" t="n">
-        <v>353.54</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="K83" t="n">
-        <v>-43.8</v>
+        <v>-18.7</v>
       </c>
       <c r="L83" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>64.99300000000001</v>
+        <v>38.59008918000001</v>
       </c>
       <c r="C84" t="n">
-        <v>83.47500000000001</v>
+        <v>85.98940350000001</v>
       </c>
       <c r="D84" t="n">
-        <v>79.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="E84" t="n">
-        <v>63.1</v>
+        <v>37.466106</v>
       </c>
       <c r="F84" t="n">
-        <v>79.5</v>
+        <v>81.89467</v>
       </c>
       <c r="G84" t="n">
-        <v>83.48</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>64.98999999999999</v>
+        <v>38.59</v>
       </c>
       <c r="I84" t="n">
-        <v>69.61</v>
+        <v>50.44</v>
       </c>
       <c r="J84" t="n">
-        <v>5.1</v>
+        <v>14.7</v>
       </c>
       <c r="K84" t="n">
-        <v>-18.1</v>
+        <v>-48.5</v>
       </c>
       <c r="L84" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>104.545</v>
+        <v>1694.58551877</v>
       </c>
       <c r="C85" t="n">
-        <v>512.4</v>
+        <v>2661.75</v>
       </c>
       <c r="D85" t="n">
-        <v>425</v>
+        <v>2445</v>
       </c>
       <c r="E85" t="n">
-        <v>101.5</v>
+        <v>1645.228659</v>
       </c>
       <c r="F85" t="n">
-        <v>488</v>
+        <v>2535</v>
       </c>
       <c r="G85" t="n">
-        <v>512.4</v>
+        <v>2661.75</v>
       </c>
       <c r="H85" t="n">
-        <v>104.55</v>
+        <v>1694.59</v>
       </c>
       <c r="I85" t="n">
-        <v>206.51</v>
+        <v>1936.38</v>
       </c>
       <c r="J85" t="n">
-        <v>20.6</v>
+        <v>8.9</v>
       </c>
       <c r="K85" t="n">
-        <v>-75.40000000000001</v>
+        <v>-30.7</v>
       </c>
       <c r="L85" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -4266,41 +4266,41 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>142.655</v>
+        <v>239.81384837</v>
       </c>
       <c r="C86" t="n">
-        <v>403.725</v>
+        <v>1281</v>
       </c>
       <c r="D86" t="n">
-        <v>348</v>
+        <v>1045</v>
       </c>
       <c r="E86" t="n">
-        <v>138.5</v>
+        <v>232.828979</v>
       </c>
       <c r="F86" t="n">
-        <v>384.5</v>
+        <v>1220</v>
       </c>
       <c r="G86" t="n">
-        <v>403.73</v>
+        <v>1281</v>
       </c>
       <c r="H86" t="n">
-        <v>142.66</v>
+        <v>239.81</v>
       </c>
       <c r="I86" t="n">
-        <v>207.92</v>
+        <v>500.11</v>
       </c>
       <c r="J86" t="n">
-        <v>16</v>
+        <v>22.6</v>
       </c>
       <c r="K86" t="n">
-        <v>-59</v>
+        <v>-77.09999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -4311,41 +4311,41 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>312.09</v>
+        <v>104.545</v>
       </c>
       <c r="C87" t="n">
-        <v>1060.5</v>
+        <v>512.4</v>
       </c>
       <c r="D87" t="n">
-        <v>905</v>
+        <v>425</v>
       </c>
       <c r="E87" t="n">
-        <v>303</v>
+        <v>101.5</v>
       </c>
       <c r="F87" t="n">
-        <v>1010</v>
+        <v>488</v>
       </c>
       <c r="G87" t="n">
-        <v>1060.5</v>
+        <v>512.4</v>
       </c>
       <c r="H87" t="n">
-        <v>312.09</v>
+        <v>104.55</v>
       </c>
       <c r="I87" t="n">
-        <v>499.19</v>
+        <v>206.51</v>
       </c>
       <c r="J87" t="n">
-        <v>17.2</v>
+        <v>20.6</v>
       </c>
       <c r="K87" t="n">
-        <v>-65.5</v>
+        <v>-75.40000000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -4356,41 +4356,41 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>491.825</v>
+        <v>1302.95</v>
       </c>
       <c r="C88" t="n">
-        <v>1020.6</v>
+        <v>3160.5</v>
       </c>
       <c r="D88" t="n">
-        <v>912</v>
+        <v>2760</v>
       </c>
       <c r="E88" t="n">
-        <v>477.5</v>
+        <v>1265</v>
       </c>
       <c r="F88" t="n">
-        <v>972</v>
+        <v>3010</v>
       </c>
       <c r="G88" t="n">
-        <v>1020.6</v>
+        <v>3160.5</v>
       </c>
       <c r="H88" t="n">
-        <v>491.82</v>
+        <v>1302.95</v>
       </c>
       <c r="I88" t="n">
-        <v>624.02</v>
+        <v>1767.34</v>
       </c>
       <c r="J88" t="n">
-        <v>11.9</v>
+        <v>14.5</v>
       </c>
       <c r="K88" t="n">
-        <v>-46.1</v>
+        <v>-52.8</v>
       </c>
       <c r="L88" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -4401,41 +4401,41 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>450.62400914</v>
+        <v>397.58</v>
       </c>
       <c r="C89" t="n">
-        <v>2016</v>
+        <v>829.5</v>
       </c>
       <c r="D89" t="n">
-        <v>1690</v>
+        <v>756</v>
       </c>
       <c r="E89" t="n">
-        <v>437.499038</v>
+        <v>386</v>
       </c>
       <c r="F89" t="n">
-        <v>1920</v>
+        <v>790</v>
       </c>
       <c r="G89" t="n">
-        <v>2016</v>
+        <v>829.5</v>
       </c>
       <c r="H89" t="n">
-        <v>450.62</v>
+        <v>397.58</v>
       </c>
       <c r="I89" t="n">
-        <v>841.97</v>
+        <v>505.56</v>
       </c>
       <c r="J89" t="n">
-        <v>19.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K89" t="n">
-        <v>-73.3</v>
+        <v>-47.4</v>
       </c>
       <c r="L89" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -4446,41 +4446,41 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>74.366</v>
+        <v>282.735</v>
       </c>
       <c r="C90" t="n">
-        <v>141.75</v>
+        <v>565.95</v>
       </c>
       <c r="D90" t="n">
-        <v>128.5</v>
+        <v>521</v>
       </c>
       <c r="E90" t="n">
-        <v>72.2</v>
+        <v>274.5</v>
       </c>
       <c r="F90" t="n">
-        <v>135</v>
+        <v>539</v>
       </c>
       <c r="G90" t="n">
-        <v>141.75</v>
+        <v>565.95</v>
       </c>
       <c r="H90" t="n">
-        <v>74.37</v>
+        <v>282.74</v>
       </c>
       <c r="I90" t="n">
-        <v>91.20999999999999</v>
+        <v>353.54</v>
       </c>
       <c r="J90" t="n">
-        <v>10.3</v>
+        <v>8.6</v>
       </c>
       <c r="K90" t="n">
-        <v>-42.1</v>
+        <v>-45.7</v>
       </c>
       <c r="L90" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -4491,41 +4491,41 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>576.76065297</v>
+        <v>491.825</v>
       </c>
       <c r="C91" t="n">
-        <v>1764</v>
+        <v>1036.35</v>
       </c>
       <c r="D91" t="n">
-        <v>1555</v>
+        <v>948</v>
       </c>
       <c r="E91" t="n">
-        <v>559.961799</v>
+        <v>477.5</v>
       </c>
       <c r="F91" t="n">
-        <v>1680</v>
+        <v>987</v>
       </c>
       <c r="G91" t="n">
-        <v>1764</v>
+        <v>1036.35</v>
       </c>
       <c r="H91" t="n">
-        <v>576.76</v>
+        <v>491.82</v>
       </c>
       <c r="I91" t="n">
-        <v>873.5700000000001</v>
+        <v>627.96</v>
       </c>
       <c r="J91" t="n">
-        <v>13.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K91" t="n">
-        <v>-62.9</v>
+        <v>-48.1</v>
       </c>
       <c r="L91" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -4536,41 +4536,41 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1575.9</v>
+        <v>266.90718673</v>
       </c>
       <c r="C92" t="n">
-        <v>6347.25</v>
+        <v>758.5219929</v>
       </c>
       <c r="D92" t="n">
-        <v>5535</v>
+        <v>682</v>
       </c>
       <c r="E92" t="n">
-        <v>1530</v>
+        <v>259.133191</v>
       </c>
       <c r="F92" t="n">
-        <v>6045</v>
+        <v>722.401898</v>
       </c>
       <c r="G92" t="n">
-        <v>6347.25</v>
+        <v>758.52</v>
       </c>
       <c r="H92" t="n">
-        <v>1575.9</v>
+        <v>266.91</v>
       </c>
       <c r="I92" t="n">
-        <v>2768.74</v>
+        <v>389.81</v>
       </c>
       <c r="J92" t="n">
-        <v>14.7</v>
+        <v>11.2</v>
       </c>
       <c r="K92" t="n">
-        <v>-71.5</v>
+        <v>-60.9</v>
       </c>
       <c r="L92" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -4581,41 +4581,41 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2085.75</v>
+        <v>74.366</v>
       </c>
       <c r="C93" t="n">
-        <v>7612.5</v>
+        <v>142.8</v>
       </c>
       <c r="D93" t="n">
-        <v>6695</v>
+        <v>133</v>
       </c>
       <c r="E93" t="n">
-        <v>2025</v>
+        <v>72.2</v>
       </c>
       <c r="F93" t="n">
-        <v>7250</v>
+        <v>136</v>
       </c>
       <c r="G93" t="n">
-        <v>7612.5</v>
+        <v>142.8</v>
       </c>
       <c r="H93" t="n">
-        <v>2085.75</v>
+        <v>74.37</v>
       </c>
       <c r="I93" t="n">
-        <v>3467.44</v>
+        <v>91.47</v>
       </c>
       <c r="J93" t="n">
-        <v>13.7</v>
+        <v>7.4</v>
       </c>
       <c r="K93" t="n">
-        <v>-68.8</v>
+        <v>-44.1</v>
       </c>
       <c r="L93" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -4626,41 +4626,41 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>11.021</v>
+        <v>450.62400914</v>
       </c>
       <c r="C94" t="n">
-        <v>43.05</v>
+        <v>2016</v>
       </c>
       <c r="D94" t="n">
-        <v>38</v>
+        <v>1790</v>
       </c>
       <c r="E94" t="n">
-        <v>10.7</v>
+        <v>437.499038</v>
       </c>
       <c r="F94" t="n">
-        <v>41</v>
+        <v>1920</v>
       </c>
       <c r="G94" t="n">
-        <v>43.05</v>
+        <v>2016</v>
       </c>
       <c r="H94" t="n">
-        <v>11.02</v>
+        <v>450.62</v>
       </c>
       <c r="I94" t="n">
-        <v>19.03</v>
+        <v>841.97</v>
       </c>
       <c r="J94" t="n">
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
       <c r="K94" t="n">
-        <v>-71</v>
+        <v>-74.8</v>
       </c>
       <c r="L94" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -4671,41 +4671,41 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>397.58</v>
+        <v>404.275</v>
       </c>
       <c r="C95" t="n">
-        <v>829.5</v>
+        <v>772.8000000000001</v>
       </c>
       <c r="D95" t="n">
-        <v>763</v>
+        <v>721</v>
       </c>
       <c r="E95" t="n">
-        <v>386</v>
+        <v>392.5</v>
       </c>
       <c r="F95" t="n">
-        <v>790</v>
+        <v>736</v>
       </c>
       <c r="G95" t="n">
-        <v>829.5</v>
+        <v>772.8</v>
       </c>
       <c r="H95" t="n">
-        <v>397.58</v>
+        <v>404.28</v>
       </c>
       <c r="I95" t="n">
-        <v>505.56</v>
+        <v>496.41</v>
       </c>
       <c r="J95" t="n">
-        <v>8.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="K95" t="n">
-        <v>-47.9</v>
+        <v>-43.9</v>
       </c>
       <c r="L95" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -4716,41 +4716,41 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>255.95657075</v>
+        <v>11.5875</v>
       </c>
       <c r="C96" t="n">
-        <v>627.9</v>
+        <v>43.05</v>
       </c>
       <c r="D96" t="n">
-        <v>571</v>
+        <v>38.8</v>
       </c>
       <c r="E96" t="n">
-        <v>248.501525</v>
+        <v>11.25</v>
       </c>
       <c r="F96" t="n">
-        <v>598</v>
+        <v>41</v>
       </c>
       <c r="G96" t="n">
-        <v>627.9</v>
+        <v>43.05</v>
       </c>
       <c r="H96" t="n">
-        <v>255.96</v>
+        <v>11.59</v>
       </c>
       <c r="I96" t="n">
-        <v>348.94</v>
+        <v>19.45</v>
       </c>
       <c r="J96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K96" t="n">
-        <v>-55.2</v>
+        <v>-70.09999999999999</v>
       </c>
       <c r="L96" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -4765,37 +4765,37 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>145.745</v>
+        <v>147.29</v>
       </c>
       <c r="C97" t="n">
-        <v>214.2</v>
+        <v>227.325</v>
       </c>
       <c r="D97" t="n">
-        <v>204</v>
+        <v>216.5</v>
       </c>
       <c r="E97" t="n">
-        <v>141.5</v>
+        <v>143</v>
       </c>
       <c r="F97" t="n">
-        <v>204</v>
+        <v>216.5</v>
       </c>
       <c r="G97" t="n">
-        <v>214.2</v>
+        <v>227.33</v>
       </c>
       <c r="H97" t="n">
-        <v>145.75</v>
+        <v>147.29</v>
       </c>
       <c r="I97" t="n">
-        <v>162.86</v>
+        <v>167.3</v>
       </c>
       <c r="J97" t="n">
         <v>5</v>
       </c>
       <c r="K97" t="n">
-        <v>-28.6</v>
+        <v>-32</v>
       </c>
       <c r="L97" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -4806,41 +4806,41 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1581.95445742</v>
+        <v>1122.7</v>
       </c>
       <c r="C98" t="n">
-        <v>2661.75</v>
+        <v>2940</v>
       </c>
       <c r="D98" t="n">
-        <v>2505</v>
+        <v>2735</v>
       </c>
       <c r="E98" t="n">
-        <v>1535.878114</v>
+        <v>1090</v>
       </c>
       <c r="F98" t="n">
-        <v>2535</v>
+        <v>2800</v>
       </c>
       <c r="G98" t="n">
-        <v>2661.75</v>
+        <v>2940</v>
       </c>
       <c r="H98" t="n">
-        <v>1581.95</v>
+        <v>1122.7</v>
       </c>
       <c r="I98" t="n">
-        <v>1851.9</v>
+        <v>1577.03</v>
       </c>
       <c r="J98" t="n">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="K98" t="n">
-        <v>-36.8</v>
+        <v>-59</v>
       </c>
       <c r="L98" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -4851,41 +4851,41 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>235.21187635</v>
+        <v>255.95657075</v>
       </c>
       <c r="C99" t="n">
-        <v>1281</v>
+        <v>627.9</v>
       </c>
       <c r="D99" t="n">
-        <v>1140</v>
+        <v>588</v>
       </c>
       <c r="E99" t="n">
-        <v>228.361045</v>
+        <v>248.501525</v>
       </c>
       <c r="F99" t="n">
-        <v>1220</v>
+        <v>598</v>
       </c>
       <c r="G99" t="n">
-        <v>1281</v>
+        <v>627.9</v>
       </c>
       <c r="H99" t="n">
-        <v>235.21</v>
+        <v>255.96</v>
       </c>
       <c r="I99" t="n">
-        <v>496.66</v>
+        <v>348.94</v>
       </c>
       <c r="J99" t="n">
-        <v>12.4</v>
+        <v>6.8</v>
       </c>
       <c r="K99" t="n">
-        <v>-79.40000000000001</v>
+        <v>-56.5</v>
       </c>
       <c r="L99" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -4896,41 +4896,41 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>404.275</v>
+        <v>512.4250000000001</v>
       </c>
       <c r="C100" t="n">
-        <v>723.45</v>
+        <v>1501.5</v>
       </c>
       <c r="D100" t="n">
-        <v>682</v>
+        <v>1395</v>
       </c>
       <c r="E100" t="n">
-        <v>392.5</v>
+        <v>497.5</v>
       </c>
       <c r="F100" t="n">
-        <v>689</v>
+        <v>1430</v>
       </c>
       <c r="G100" t="n">
-        <v>723.45</v>
+        <v>1501.5</v>
       </c>
       <c r="H100" t="n">
-        <v>404.28</v>
+        <v>512.4299999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>484.07</v>
+        <v>759.6900000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="K100" t="n">
-        <v>-40.7</v>
+        <v>-63.3</v>
       </c>
       <c r="L100" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -4941,41 +4941,41 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1122.7</v>
+        <v>2961.25</v>
       </c>
       <c r="C101" t="n">
-        <v>2856</v>
+        <v>8557.5</v>
       </c>
       <c r="D101" t="n">
-        <v>2660</v>
+        <v>8000</v>
       </c>
       <c r="E101" t="n">
-        <v>1090</v>
+        <v>2875</v>
       </c>
       <c r="F101" t="n">
-        <v>2720</v>
+        <v>8150</v>
       </c>
       <c r="G101" t="n">
-        <v>2856</v>
+        <v>8557.5</v>
       </c>
       <c r="H101" t="n">
-        <v>1122.7</v>
+        <v>2961.25</v>
       </c>
       <c r="I101" t="n">
-        <v>1556.03</v>
+        <v>4360.31</v>
       </c>
       <c r="J101" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="K101" t="n">
-        <v>-57.8</v>
+        <v>-63</v>
       </c>
       <c r="L101" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -4986,41 +4986,41 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2961.25</v>
+        <v>139.8182976</v>
       </c>
       <c r="C102" t="n">
-        <v>8268.75</v>
+        <v>395.69690475</v>
       </c>
       <c r="D102" t="n">
-        <v>7655</v>
+        <v>372.5</v>
       </c>
       <c r="E102" t="n">
-        <v>2875</v>
+        <v>135.74592</v>
       </c>
       <c r="F102" t="n">
-        <v>7875</v>
+        <v>376.854195</v>
       </c>
       <c r="G102" t="n">
-        <v>8268.75</v>
+        <v>395.7</v>
       </c>
       <c r="H102" t="n">
-        <v>2961.25</v>
+        <v>139.82</v>
       </c>
       <c r="I102" t="n">
-        <v>4288.12</v>
+        <v>203.79</v>
       </c>
       <c r="J102" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="K102" t="n">
-        <v>-61.3</v>
+        <v>-62.5</v>
       </c>
       <c r="L102" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -5031,41 +5031,41 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>484.1</v>
+        <v>2085.75</v>
       </c>
       <c r="C103" t="n">
-        <v>1475.25</v>
+        <v>7770</v>
       </c>
       <c r="D103" t="n">
-        <v>1360</v>
+        <v>7380</v>
       </c>
       <c r="E103" t="n">
-        <v>470</v>
+        <v>2025</v>
       </c>
       <c r="F103" t="n">
-        <v>1405</v>
+        <v>7400</v>
       </c>
       <c r="G103" t="n">
-        <v>1475.25</v>
+        <v>7770</v>
       </c>
       <c r="H103" t="n">
-        <v>484.1</v>
+        <v>2085.75</v>
       </c>
       <c r="I103" t="n">
-        <v>731.89</v>
+        <v>3506.81</v>
       </c>
       <c r="J103" t="n">
-        <v>8.5</v>
+        <v>5.3</v>
       </c>
       <c r="K103" t="n">
-        <v>-64.40000000000001</v>
+        <v>-71.7</v>
       </c>
       <c r="L103" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -5076,41 +5076,41 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>257.5</v>
+        <v>1575.9</v>
       </c>
       <c r="C104" t="n">
-        <v>753.9</v>
+        <v>6384</v>
       </c>
       <c r="D104" t="n">
-        <v>703</v>
+        <v>6080</v>
       </c>
       <c r="E104" t="n">
-        <v>250</v>
+        <v>1530</v>
       </c>
       <c r="F104" t="n">
-        <v>718</v>
+        <v>6080</v>
       </c>
       <c r="G104" t="n">
-        <v>753.9</v>
+        <v>6384</v>
       </c>
       <c r="H104" t="n">
-        <v>257.5</v>
+        <v>1575.9</v>
       </c>
       <c r="I104" t="n">
-        <v>381.6</v>
+        <v>2777.93</v>
       </c>
       <c r="J104" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="K104" t="n">
-        <v>-63.4</v>
+        <v>-74.09999999999999</v>
       </c>
       <c r="L104" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -5125,16 +5125,16 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>115.875</v>
+        <v>112.785</v>
       </c>
       <c r="C105" t="n">
         <v>163.24184205</v>
       </c>
       <c r="D105" t="n">
-        <v>114</v>
+        <v>112.5</v>
       </c>
       <c r="E105" t="n">
-        <v>112.5</v>
+        <v>109.5</v>
       </c>
       <c r="F105" t="n">
         <v>155.468421</v>
@@ -5143,16 +5143,16 @@
         <v>163.24</v>
       </c>
       <c r="H105" t="n">
-        <v>115.88</v>
+        <v>112.78</v>
       </c>
       <c r="I105" t="n">
-        <v>127.72</v>
+        <v>125.4</v>
       </c>
       <c r="J105" t="n">
-        <v>43.2</v>
+        <v>45.1</v>
       </c>
       <c r="K105" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">

--- a/data/entry_signals_tw.xlsx
+++ b/data/entry_signals_tw.xlsx
@@ -486,41 +486,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>752.9300000000001</v>
+        <v>44.805</v>
       </c>
       <c r="C2" t="n">
-        <v>1170.75</v>
+        <v>65.205</v>
       </c>
       <c r="D2" t="n">
-        <v>773</v>
+        <v>45.6</v>
       </c>
       <c r="E2" t="n">
-        <v>731</v>
+        <v>43.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1115</v>
+        <v>62.1</v>
       </c>
       <c r="G2" t="n">
-        <v>1170.75</v>
+        <v>65.2</v>
       </c>
       <c r="H2" t="n">
-        <v>752.9299999999999</v>
+        <v>44.8</v>
       </c>
       <c r="I2" t="n">
-        <v>857.38</v>
+        <v>49.91</v>
       </c>
       <c r="J2" t="n">
-        <v>51.5</v>
+        <v>43</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.6</v>
+        <v>-1.7</v>
       </c>
       <c r="L2" t="n">
-        <v>19.82</v>
+        <v>24.66</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -531,41 +531,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71.07000000000001</v>
+        <v>891.03583299</v>
       </c>
       <c r="C3" t="n">
-        <v>111.0765831</v>
+        <v>1354.7205</v>
       </c>
       <c r="D3" t="n">
-        <v>76.2</v>
+        <v>920</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>865.083333</v>
       </c>
       <c r="F3" t="n">
-        <v>105.787222</v>
+        <v>1290.21</v>
       </c>
       <c r="G3" t="n">
-        <v>111.08</v>
+        <v>1354.72</v>
       </c>
       <c r="H3" t="n">
-        <v>71.06999999999999</v>
+        <v>891.04</v>
       </c>
       <c r="I3" t="n">
-        <v>81.06999999999999</v>
+        <v>1006.96</v>
       </c>
       <c r="J3" t="n">
-        <v>45.8</v>
+        <v>47.3</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.7</v>
+        <v>-3.1</v>
       </c>
       <c r="L3" t="n">
-        <v>6.8</v>
+        <v>15.01</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -576,41 +576,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.805</v>
+        <v>22.866</v>
       </c>
       <c r="C4" t="n">
-        <v>67.935</v>
+        <v>33.81861420000001</v>
       </c>
       <c r="D4" t="n">
-        <v>47.85</v>
+        <v>23.6</v>
       </c>
       <c r="E4" t="n">
-        <v>43.5</v>
+        <v>22.2</v>
       </c>
       <c r="F4" t="n">
-        <v>64.7</v>
+        <v>32.208204</v>
       </c>
       <c r="G4" t="n">
-        <v>67.94</v>
+        <v>33.82</v>
       </c>
       <c r="H4" t="n">
-        <v>44.8</v>
+        <v>22.87</v>
       </c>
       <c r="I4" t="n">
-        <v>50.59</v>
+        <v>25.6</v>
       </c>
       <c r="J4" t="n">
-        <v>42</v>
+        <v>43.3</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.4</v>
+        <v>-3.1</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6</v>
+        <v>13.92</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -621,41 +621,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>89.404</v>
+        <v>71.07000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>124.425</v>
+        <v>111.0765831</v>
       </c>
       <c r="D5" t="n">
-        <v>94.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>86.8</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
-        <v>118.5</v>
+        <v>105.787222</v>
       </c>
       <c r="G5" t="n">
-        <v>124.43</v>
+        <v>111.08</v>
       </c>
       <c r="H5" t="n">
-        <v>89.40000000000001</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>98.16</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>31.8</v>
+        <v>50.3</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.3</v>
+        <v>-3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>6.01</v>
+        <v>13.14</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -666,41 +666,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.866</v>
+        <v>89.404</v>
       </c>
       <c r="C6" t="n">
-        <v>33.81861420000001</v>
+        <v>124.425</v>
       </c>
       <c r="D6" t="n">
-        <v>24.45</v>
+        <v>92.2</v>
       </c>
       <c r="E6" t="n">
-        <v>22.2</v>
+        <v>86.8</v>
       </c>
       <c r="F6" t="n">
-        <v>32.208204</v>
+        <v>118.5</v>
       </c>
       <c r="G6" t="n">
-        <v>33.82</v>
+        <v>124.43</v>
       </c>
       <c r="H6" t="n">
-        <v>22.87</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>25.6</v>
+        <v>98.16</v>
       </c>
       <c r="J6" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>-6.5</v>
+        <v>-3</v>
       </c>
       <c r="L6" t="n">
-        <v>5.91</v>
+        <v>11.53</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -711,41 +711,41 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38.934</v>
+        <v>38.36570677</v>
       </c>
       <c r="C7" t="n">
-        <v>55.23</v>
+        <v>45.24471735</v>
       </c>
       <c r="D7" t="n">
-        <v>41.7</v>
+        <v>39.25</v>
       </c>
       <c r="E7" t="n">
-        <v>37.8</v>
+        <v>37.248259</v>
       </c>
       <c r="F7" t="n">
-        <v>52.6</v>
+        <v>43.090207</v>
       </c>
       <c r="G7" t="n">
-        <v>55.23</v>
+        <v>45.24</v>
       </c>
       <c r="H7" t="n">
-        <v>38.93</v>
+        <v>38.37</v>
       </c>
       <c r="I7" t="n">
-        <v>43.01</v>
+        <v>40.09</v>
       </c>
       <c r="J7" t="n">
-        <v>32.4</v>
+        <v>15.3</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.6</v>
+        <v>-2.3</v>
       </c>
       <c r="L7" t="n">
-        <v>4.89</v>
+        <v>6.78</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -756,41 +756,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20.806</v>
+        <v>130.8919571</v>
       </c>
       <c r="C8" t="n">
-        <v>32.445</v>
+        <v>148.5964515</v>
       </c>
       <c r="D8" t="n">
-        <v>23.4</v>
+        <v>133.5</v>
       </c>
       <c r="E8" t="n">
-        <v>20.2</v>
+        <v>127.07957</v>
       </c>
       <c r="F8" t="n">
-        <v>30.9</v>
+        <v>141.52043</v>
       </c>
       <c r="G8" t="n">
-        <v>32.45</v>
+        <v>148.6</v>
       </c>
       <c r="H8" t="n">
-        <v>20.81</v>
+        <v>130.89</v>
       </c>
       <c r="I8" t="n">
-        <v>23.72</v>
+        <v>135.32</v>
       </c>
       <c r="J8" t="n">
-        <v>38.7</v>
+        <v>11.3</v>
       </c>
       <c r="K8" t="n">
-        <v>-11.1</v>
+        <v>-2</v>
       </c>
       <c r="L8" t="n">
-        <v>3.49</v>
+        <v>5.79</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -801,401 +801,401 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94.863</v>
+        <v>1236</v>
       </c>
       <c r="C9" t="n">
-        <v>124.13135595</v>
+        <v>2667</v>
       </c>
       <c r="D9" t="n">
-        <v>102.5</v>
+        <v>1480</v>
       </c>
       <c r="E9" t="n">
-        <v>92.09999999999999</v>
+        <v>1200</v>
       </c>
       <c r="F9" t="n">
-        <v>118.220339</v>
+        <v>2540</v>
       </c>
       <c r="G9" t="n">
-        <v>124.13</v>
+        <v>2667</v>
       </c>
       <c r="H9" t="n">
-        <v>94.86</v>
+        <v>1236</v>
       </c>
       <c r="I9" t="n">
-        <v>102.18</v>
+        <v>1593.75</v>
       </c>
       <c r="J9" t="n">
-        <v>21.1</v>
+        <v>80.2</v>
       </c>
       <c r="K9" t="n">
-        <v>-7.5</v>
+        <v>-16.5</v>
       </c>
       <c r="L9" t="n">
-        <v>2.83</v>
+        <v>4.86</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101.36665072</v>
+        <v>69.99253039</v>
       </c>
       <c r="C10" t="n">
-        <v>122.8038357</v>
+        <v>142.9118481</v>
       </c>
       <c r="D10" t="n">
-        <v>107</v>
+        <v>82.8</v>
       </c>
       <c r="E10" t="n">
-        <v>98.414224</v>
+        <v>67.953913</v>
       </c>
       <c r="F10" t="n">
-        <v>116.956034</v>
+        <v>136.106522</v>
       </c>
       <c r="G10" t="n">
-        <v>122.8</v>
+        <v>142.91</v>
       </c>
       <c r="H10" t="n">
-        <v>101.37</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>106.73</v>
+        <v>88.22</v>
       </c>
       <c r="J10" t="n">
-        <v>14.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.3</v>
+        <v>-15.5</v>
       </c>
       <c r="L10" t="n">
-        <v>2.81</v>
+        <v>4.69</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>135.96</v>
+        <v>141.71465429</v>
       </c>
       <c r="C11" t="n">
-        <v>154.35</v>
+        <v>161.7</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>145.5</v>
       </c>
       <c r="E11" t="n">
-        <v>132</v>
+        <v>137.587043</v>
       </c>
       <c r="F11" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G11" t="n">
-        <v>154.35</v>
+        <v>161.7</v>
       </c>
       <c r="H11" t="n">
-        <v>135.96</v>
+        <v>141.71</v>
       </c>
       <c r="I11" t="n">
-        <v>140.56</v>
+        <v>146.71</v>
       </c>
       <c r="J11" t="n">
-        <v>9.5</v>
+        <v>11.1</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.6</v>
+        <v>-2.6</v>
       </c>
       <c r="L11" t="n">
-        <v>2.65</v>
+        <v>4.28</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37.78805496</v>
+        <v>19.58896127</v>
       </c>
       <c r="C12" t="n">
-        <v>45.24471735</v>
+        <v>30.5471418</v>
       </c>
       <c r="D12" t="n">
-        <v>39.85</v>
+        <v>21.8</v>
       </c>
       <c r="E12" t="n">
-        <v>36.687432</v>
+        <v>19.018409</v>
       </c>
       <c r="F12" t="n">
-        <v>43.090207</v>
+        <v>29.092516</v>
       </c>
       <c r="G12" t="n">
-        <v>45.24</v>
+        <v>30.55</v>
       </c>
       <c r="H12" t="n">
-        <v>37.79</v>
+        <v>19.59</v>
       </c>
       <c r="I12" t="n">
-        <v>39.65</v>
+        <v>22.33</v>
       </c>
       <c r="J12" t="n">
-        <v>13.5</v>
+        <v>40.1</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.2</v>
+        <v>-10.1</v>
       </c>
       <c r="L12" t="n">
-        <v>2.62</v>
+        <v>3.96</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>891.03583299</v>
+        <v>170.11119397</v>
       </c>
       <c r="C13" t="n">
-        <v>1354.7205</v>
+        <v>197.6116716</v>
       </c>
       <c r="D13" t="n">
-        <v>1020</v>
+        <v>176</v>
       </c>
       <c r="E13" t="n">
-        <v>865.083333</v>
+        <v>165.156499</v>
       </c>
       <c r="F13" t="n">
-        <v>1290.21</v>
+        <v>188.201592</v>
       </c>
       <c r="G13" t="n">
-        <v>1354.72</v>
+        <v>197.61</v>
       </c>
       <c r="H13" t="n">
-        <v>891.04</v>
+        <v>170.11</v>
       </c>
       <c r="I13" t="n">
-        <v>1006.96</v>
+        <v>176.99</v>
       </c>
       <c r="J13" t="n">
-        <v>32.8</v>
+        <v>12.3</v>
       </c>
       <c r="K13" t="n">
-        <v>-12.6</v>
+        <v>-3.3</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>3.67</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1236</v>
+        <v>2335.80629197</v>
       </c>
       <c r="C14" t="n">
-        <v>2667</v>
+        <v>4673.55212625</v>
       </c>
       <c r="D14" t="n">
-        <v>1640</v>
+        <v>2855</v>
       </c>
       <c r="E14" t="n">
-        <v>1200</v>
+        <v>2267.773099</v>
       </c>
       <c r="F14" t="n">
-        <v>2540</v>
+        <v>4451.002025</v>
       </c>
       <c r="G14" t="n">
-        <v>2667</v>
+        <v>4673.55</v>
       </c>
       <c r="H14" t="n">
-        <v>1236</v>
+        <v>2335.81</v>
       </c>
       <c r="I14" t="n">
-        <v>1593.75</v>
+        <v>2920.24</v>
       </c>
       <c r="J14" t="n">
-        <v>62.6</v>
+        <v>63.7</v>
       </c>
       <c r="K14" t="n">
-        <v>-24.6</v>
+        <v>-18.2</v>
       </c>
       <c r="L14" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2369</v>
+        <v>56.032</v>
       </c>
       <c r="C15" t="n">
-        <v>5969.25</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>3420</v>
+        <v>62.6</v>
       </c>
       <c r="E15" t="n">
-        <v>2300</v>
+        <v>54.4</v>
       </c>
       <c r="F15" t="n">
-        <v>5685</v>
+        <v>81.2</v>
       </c>
       <c r="G15" t="n">
-        <v>5969.25</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>2369</v>
+        <v>56.03</v>
       </c>
       <c r="I15" t="n">
-        <v>3269.06</v>
+        <v>63.34</v>
       </c>
       <c r="J15" t="n">
-        <v>74.5</v>
+        <v>36.2</v>
       </c>
       <c r="K15" t="n">
-        <v>-30.7</v>
+        <v>-10.5</v>
       </c>
       <c r="L15" t="n">
-        <v>2.43</v>
+        <v>3.45</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>66.8203539</v>
+        <v>2369</v>
       </c>
       <c r="C16" t="n">
-        <v>142.9118481</v>
+        <v>5969.25</v>
       </c>
       <c r="D16" t="n">
-        <v>90.09999999999999</v>
+        <v>3205</v>
       </c>
       <c r="E16" t="n">
-        <v>64.87412999999999</v>
+        <v>2300</v>
       </c>
       <c r="F16" t="n">
-        <v>136.106522</v>
+        <v>5685</v>
       </c>
       <c r="G16" t="n">
-        <v>142.91</v>
+        <v>5969.25</v>
       </c>
       <c r="H16" t="n">
-        <v>66.81999999999999</v>
+        <v>2369</v>
       </c>
       <c r="I16" t="n">
-        <v>85.84</v>
+        <v>3269.06</v>
       </c>
       <c r="J16" t="n">
-        <v>58.6</v>
+        <v>86.2</v>
       </c>
       <c r="K16" t="n">
-        <v>-25.8</v>
+        <v>-26.1</v>
       </c>
       <c r="L16" t="n">
-        <v>2.27</v>
+        <v>3.31</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>141.22429189</v>
+        <v>94.863</v>
       </c>
       <c r="C17" t="n">
-        <v>155.4</v>
+        <v>124.13135595</v>
       </c>
       <c r="D17" t="n">
-        <v>146.5</v>
+        <v>103</v>
       </c>
       <c r="E17" t="n">
-        <v>137.110963</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>148</v>
+        <v>118.220339</v>
       </c>
       <c r="G17" t="n">
-        <v>155.4</v>
+        <v>124.13</v>
       </c>
       <c r="H17" t="n">
-        <v>141.22</v>
+        <v>94.86</v>
       </c>
       <c r="I17" t="n">
-        <v>144.77</v>
+        <v>102.18</v>
       </c>
       <c r="J17" t="n">
-        <v>6.1</v>
+        <v>20.5</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.6</v>
+        <v>-7.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.69</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1206,131 +1206,131 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>270.89</v>
+        <v>87.38638965</v>
       </c>
       <c r="C18" t="n">
-        <v>800.1</v>
+        <v>114.7666821</v>
       </c>
       <c r="D18" t="n">
-        <v>468.5</v>
+        <v>95</v>
       </c>
       <c r="E18" t="n">
-        <v>263</v>
+        <v>84.841155</v>
       </c>
       <c r="F18" t="n">
-        <v>762</v>
+        <v>109.301602</v>
       </c>
       <c r="G18" t="n">
-        <v>800.1</v>
+        <v>114.77</v>
       </c>
       <c r="H18" t="n">
-        <v>270.89</v>
+        <v>87.39</v>
       </c>
       <c r="I18" t="n">
-        <v>403.19</v>
+        <v>94.23</v>
       </c>
       <c r="J18" t="n">
-        <v>70.8</v>
+        <v>20.8</v>
       </c>
       <c r="K18" t="n">
-        <v>-42.2</v>
+        <v>-8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>156.045</v>
+        <v>121.71221909</v>
       </c>
       <c r="C19" t="n">
-        <v>369.6</v>
+        <v>203.58520875</v>
       </c>
       <c r="D19" t="n">
-        <v>236</v>
+        <v>144.5</v>
       </c>
       <c r="E19" t="n">
-        <v>151.5</v>
+        <v>118.167203</v>
       </c>
       <c r="F19" t="n">
-        <v>352</v>
+        <v>193.890675</v>
       </c>
       <c r="G19" t="n">
-        <v>369.6</v>
+        <v>203.59</v>
       </c>
       <c r="H19" t="n">
-        <v>156.05</v>
+        <v>121.71</v>
       </c>
       <c r="I19" t="n">
-        <v>209.43</v>
+        <v>142.18</v>
       </c>
       <c r="J19" t="n">
-        <v>56.6</v>
+        <v>40.9</v>
       </c>
       <c r="K19" t="n">
-        <v>-33.9</v>
+        <v>-15.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>2.59</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>153.80987013</v>
+        <v>103.12004547</v>
       </c>
       <c r="C20" t="n">
-        <v>192.6356628</v>
+        <v>122.22362355</v>
       </c>
       <c r="D20" t="n">
-        <v>168.5</v>
+        <v>108.5</v>
       </c>
       <c r="E20" t="n">
-        <v>149.329971</v>
+        <v>100.116549</v>
       </c>
       <c r="F20" t="n">
-        <v>183.462536</v>
+        <v>116.403451</v>
       </c>
       <c r="G20" t="n">
-        <v>192.64</v>
+        <v>122.22</v>
       </c>
       <c r="H20" t="n">
-        <v>153.81</v>
+        <v>103.12</v>
       </c>
       <c r="I20" t="n">
-        <v>163.52</v>
+        <v>107.9</v>
       </c>
       <c r="J20" t="n">
-        <v>14.3</v>
+        <v>12.6</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.699999999999999</v>
+        <v>-5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.64</v>
+        <v>2.55</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1341,176 +1341,176 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>126.175</v>
+        <v>101.36665072</v>
       </c>
       <c r="C21" t="n">
-        <v>211.05</v>
+        <v>122.8038357</v>
       </c>
       <c r="D21" t="n">
-        <v>159</v>
+        <v>107.5</v>
       </c>
       <c r="E21" t="n">
-        <v>122.5</v>
+        <v>98.414224</v>
       </c>
       <c r="F21" t="n">
-        <v>201</v>
+        <v>116.956034</v>
       </c>
       <c r="G21" t="n">
-        <v>211.05</v>
+        <v>122.8</v>
       </c>
       <c r="H21" t="n">
-        <v>126.17</v>
+        <v>101.37</v>
       </c>
       <c r="I21" t="n">
-        <v>147.39</v>
+        <v>106.73</v>
       </c>
       <c r="J21" t="n">
-        <v>32.7</v>
+        <v>14.2</v>
       </c>
       <c r="K21" t="n">
-        <v>-20.6</v>
+        <v>-5.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.59</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>187.54150699</v>
+        <v>95.97727254000002</v>
       </c>
       <c r="C22" t="n">
-        <v>320.16794775</v>
+        <v>114.975</v>
       </c>
       <c r="D22" t="n">
-        <v>240.5</v>
+        <v>101.5</v>
       </c>
       <c r="E22" t="n">
-        <v>182.079133</v>
+        <v>93.18181800000001</v>
       </c>
       <c r="F22" t="n">
-        <v>304.921855</v>
+        <v>109.5</v>
       </c>
       <c r="G22" t="n">
-        <v>320.17</v>
+        <v>114.98</v>
       </c>
       <c r="H22" t="n">
-        <v>187.54</v>
+        <v>95.98</v>
       </c>
       <c r="I22" t="n">
-        <v>220.7</v>
+        <v>100.73</v>
       </c>
       <c r="J22" t="n">
-        <v>33.1</v>
+        <v>13.3</v>
       </c>
       <c r="K22" t="n">
-        <v>-22</v>
+        <v>-5.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>2.44</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>209.605</v>
+        <v>270.89</v>
       </c>
       <c r="C23" t="n">
-        <v>262.5</v>
+        <v>800.1</v>
       </c>
       <c r="D23" t="n">
-        <v>231</v>
+        <v>432.5</v>
       </c>
       <c r="E23" t="n">
-        <v>203.5</v>
+        <v>263</v>
       </c>
       <c r="F23" t="n">
-        <v>250</v>
+        <v>762</v>
       </c>
       <c r="G23" t="n">
-        <v>262.5</v>
+        <v>800.1</v>
       </c>
       <c r="H23" t="n">
-        <v>209.61</v>
+        <v>270.89</v>
       </c>
       <c r="I23" t="n">
-        <v>222.83</v>
+        <v>403.19</v>
       </c>
       <c r="J23" t="n">
-        <v>13.6</v>
+        <v>85</v>
       </c>
       <c r="K23" t="n">
-        <v>-9.300000000000001</v>
+        <v>-37.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.47</v>
+        <v>2.27</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>68.90700000000001</v>
+        <v>703.31864508</v>
       </c>
       <c r="C24" t="n">
-        <v>150.675</v>
+        <v>1826.16</v>
       </c>
       <c r="D24" t="n">
-        <v>102.5</v>
+        <v>1055</v>
       </c>
       <c r="E24" t="n">
-        <v>66.90000000000001</v>
+        <v>682.833636</v>
       </c>
       <c r="F24" t="n">
-        <v>143.5</v>
+        <v>1739.2</v>
       </c>
       <c r="G24" t="n">
-        <v>150.68</v>
+        <v>1826.16</v>
       </c>
       <c r="H24" t="n">
-        <v>68.91</v>
+        <v>703.3200000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>89.34999999999999</v>
+        <v>984.03</v>
       </c>
       <c r="J24" t="n">
-        <v>47</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-32.8</v>
+        <v>-33.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.43</v>
+        <v>2.19</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1521,41 +1521,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>98.88</v>
+        <v>250.805</v>
       </c>
       <c r="C25" t="n">
-        <v>156.975</v>
+        <v>486.675</v>
       </c>
       <c r="D25" t="n">
-        <v>123</v>
+        <v>325.5</v>
       </c>
       <c r="E25" t="n">
-        <v>96</v>
+        <v>243.5</v>
       </c>
       <c r="F25" t="n">
-        <v>149.5</v>
+        <v>463.5</v>
       </c>
       <c r="G25" t="n">
-        <v>156.97</v>
+        <v>486.68</v>
       </c>
       <c r="H25" t="n">
-        <v>98.88</v>
+        <v>250.81</v>
       </c>
       <c r="I25" t="n">
-        <v>113.4</v>
+        <v>309.77</v>
       </c>
       <c r="J25" t="n">
-        <v>27.6</v>
+        <v>49.5</v>
       </c>
       <c r="K25" t="n">
-        <v>-19.6</v>
+        <v>-22.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.41</v>
+        <v>2.16</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1566,86 +1566,86 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>56.032</v>
+        <v>153.80987013</v>
       </c>
       <c r="C26" t="n">
-        <v>85.26000000000001</v>
+        <v>192.6356628</v>
       </c>
       <c r="D26" t="n">
-        <v>68.40000000000001</v>
+        <v>166.5</v>
       </c>
       <c r="E26" t="n">
-        <v>54.4</v>
+        <v>149.329971</v>
       </c>
       <c r="F26" t="n">
-        <v>81.2</v>
+        <v>183.462536</v>
       </c>
       <c r="G26" t="n">
-        <v>85.26000000000001</v>
+        <v>192.64</v>
       </c>
       <c r="H26" t="n">
-        <v>56.03</v>
+        <v>153.81</v>
       </c>
       <c r="I26" t="n">
-        <v>63.34</v>
+        <v>163.52</v>
       </c>
       <c r="J26" t="n">
-        <v>24.6</v>
+        <v>15.7</v>
       </c>
       <c r="K26" t="n">
-        <v>-18.1</v>
+        <v>-7.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.36</v>
+        <v>2.06</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>250.805</v>
+        <v>106.605</v>
       </c>
       <c r="C27" t="n">
-        <v>486.675</v>
+        <v>192.15</v>
       </c>
       <c r="D27" t="n">
-        <v>351</v>
+        <v>136</v>
       </c>
       <c r="E27" t="n">
-        <v>243.5</v>
+        <v>103.5</v>
       </c>
       <c r="F27" t="n">
-        <v>463.5</v>
+        <v>183</v>
       </c>
       <c r="G27" t="n">
-        <v>486.68</v>
+        <v>192.15</v>
       </c>
       <c r="H27" t="n">
-        <v>250.81</v>
+        <v>106.61</v>
       </c>
       <c r="I27" t="n">
-        <v>309.77</v>
+        <v>127.99</v>
       </c>
       <c r="J27" t="n">
-        <v>38.7</v>
+        <v>41.3</v>
       </c>
       <c r="K27" t="n">
-        <v>-28.5</v>
+        <v>-21.6</v>
       </c>
       <c r="L27" t="n">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1656,86 +1656,86 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>126.175</v>
+        <v>122.04276875</v>
       </c>
       <c r="C28" t="n">
-        <v>208.95</v>
+        <v>180.779025</v>
       </c>
       <c r="D28" t="n">
-        <v>162</v>
+        <v>142.5</v>
       </c>
       <c r="E28" t="n">
-        <v>122.5</v>
+        <v>118.488125</v>
       </c>
       <c r="F28" t="n">
-        <v>199</v>
+        <v>172.1705</v>
       </c>
       <c r="G28" t="n">
-        <v>208.95</v>
+        <v>180.78</v>
       </c>
       <c r="H28" t="n">
-        <v>126.17</v>
+        <v>122.04</v>
       </c>
       <c r="I28" t="n">
-        <v>146.87</v>
+        <v>136.73</v>
       </c>
       <c r="J28" t="n">
-        <v>29</v>
+        <v>26.9</v>
       </c>
       <c r="K28" t="n">
-        <v>-22.1</v>
+        <v>-14.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.31</v>
+        <v>1.87</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>106.605</v>
+        <v>157.59</v>
       </c>
       <c r="C29" t="n">
-        <v>192.15</v>
+        <v>369.6</v>
       </c>
       <c r="D29" t="n">
-        <v>144</v>
+        <v>232</v>
       </c>
       <c r="E29" t="n">
-        <v>103.5</v>
+        <v>153</v>
       </c>
       <c r="F29" t="n">
-        <v>183</v>
+        <v>352</v>
       </c>
       <c r="G29" t="n">
-        <v>192.15</v>
+        <v>369.6</v>
       </c>
       <c r="H29" t="n">
-        <v>106.61</v>
+        <v>157.59</v>
       </c>
       <c r="I29" t="n">
-        <v>127.99</v>
+        <v>210.59</v>
       </c>
       <c r="J29" t="n">
-        <v>33.4</v>
+        <v>59.3</v>
       </c>
       <c r="K29" t="n">
-        <v>-26</v>
+        <v>-32.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -1746,176 +1746,176 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>107.635</v>
+        <v>68.90700000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>127.575</v>
+        <v>150.675</v>
       </c>
       <c r="D30" t="n">
-        <v>116.5</v>
+        <v>97.8</v>
       </c>
       <c r="E30" t="n">
-        <v>104.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>121.5</v>
+        <v>143.5</v>
       </c>
       <c r="G30" t="n">
-        <v>127.58</v>
+        <v>150.68</v>
       </c>
       <c r="H30" t="n">
-        <v>107.64</v>
+        <v>68.91</v>
       </c>
       <c r="I30" t="n">
-        <v>112.62</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>9.5</v>
+        <v>54.1</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.6</v>
+        <v>-29.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>170.11119397</v>
+        <v>103</v>
       </c>
       <c r="C31" t="n">
-        <v>197.6116716</v>
+        <v>156.975</v>
       </c>
       <c r="D31" t="n">
-        <v>182.5</v>
+        <v>122.5</v>
       </c>
       <c r="E31" t="n">
-        <v>165.156499</v>
+        <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>188.201592</v>
+        <v>149.5</v>
       </c>
       <c r="G31" t="n">
-        <v>197.61</v>
+        <v>156.97</v>
       </c>
       <c r="H31" t="n">
-        <v>170.11</v>
+        <v>103</v>
       </c>
       <c r="I31" t="n">
-        <v>176.99</v>
+        <v>116.49</v>
       </c>
       <c r="J31" t="n">
-        <v>8.300000000000001</v>
+        <v>28.1</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.8</v>
+        <v>-15.9</v>
       </c>
       <c r="L31" t="n">
-        <v>1.22</v>
+        <v>1.77</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2163</v>
+        <v>187.54150699</v>
       </c>
       <c r="C32" t="n">
-        <v>4698.75</v>
+        <v>320.16794775</v>
       </c>
       <c r="D32" t="n">
-        <v>3320</v>
+        <v>237.5</v>
       </c>
       <c r="E32" t="n">
-        <v>2100</v>
+        <v>182.079133</v>
       </c>
       <c r="F32" t="n">
-        <v>4475</v>
+        <v>304.921855</v>
       </c>
       <c r="G32" t="n">
-        <v>4698.75</v>
+        <v>320.17</v>
       </c>
       <c r="H32" t="n">
-        <v>2163</v>
+        <v>187.54</v>
       </c>
       <c r="I32" t="n">
-        <v>2796.94</v>
+        <v>220.7</v>
       </c>
       <c r="J32" t="n">
-        <v>41.5</v>
+        <v>34.8</v>
       </c>
       <c r="K32" t="n">
-        <v>-34.8</v>
+        <v>-21</v>
       </c>
       <c r="L32" t="n">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>122.04276875</v>
+        <v>183.34</v>
       </c>
       <c r="C33" t="n">
-        <v>180.779025</v>
+        <v>282.975</v>
       </c>
       <c r="D33" t="n">
-        <v>149</v>
+        <v>221.5</v>
       </c>
       <c r="E33" t="n">
-        <v>118.488125</v>
+        <v>178</v>
       </c>
       <c r="F33" t="n">
-        <v>172.1705</v>
+        <v>269.5</v>
       </c>
       <c r="G33" t="n">
-        <v>180.78</v>
+        <v>282.98</v>
       </c>
       <c r="H33" t="n">
-        <v>122.04</v>
+        <v>183.34</v>
       </c>
       <c r="I33" t="n">
-        <v>136.73</v>
+        <v>208.25</v>
       </c>
       <c r="J33" t="n">
-        <v>21.3</v>
+        <v>27.8</v>
       </c>
       <c r="K33" t="n">
-        <v>-18.1</v>
+        <v>-17.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -1926,41 +1926,41 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>146.775</v>
+        <v>126.175</v>
       </c>
       <c r="C34" t="n">
-        <v>211.05</v>
+        <v>208.95</v>
       </c>
       <c r="D34" t="n">
-        <v>176.5</v>
+        <v>158</v>
       </c>
       <c r="E34" t="n">
-        <v>142.5</v>
+        <v>122.5</v>
       </c>
       <c r="F34" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G34" t="n">
-        <v>211.05</v>
+        <v>208.95</v>
       </c>
       <c r="H34" t="n">
-        <v>146.78</v>
+        <v>126.17</v>
       </c>
       <c r="I34" t="n">
-        <v>162.84</v>
+        <v>146.87</v>
       </c>
       <c r="J34" t="n">
-        <v>19.6</v>
+        <v>32.2</v>
       </c>
       <c r="K34" t="n">
-        <v>-16.8</v>
+        <v>-20.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -1971,41 +1971,41 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>98.57100000000001</v>
+        <v>842.8097436100001</v>
       </c>
       <c r="C35" t="n">
-        <v>153.3</v>
+        <v>1651.86</v>
       </c>
       <c r="D35" t="n">
-        <v>124</v>
+        <v>1175</v>
       </c>
       <c r="E35" t="n">
-        <v>95.7</v>
+        <v>818.261887</v>
       </c>
       <c r="F35" t="n">
-        <v>146</v>
+        <v>1573.2</v>
       </c>
       <c r="G35" t="n">
-        <v>153.3</v>
+        <v>1651.86</v>
       </c>
       <c r="H35" t="n">
-        <v>98.56999999999999</v>
+        <v>842.8099999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>112.25</v>
+        <v>1045.07</v>
       </c>
       <c r="J35" t="n">
-        <v>23.6</v>
+        <v>40.6</v>
       </c>
       <c r="K35" t="n">
-        <v>-20.5</v>
+        <v>-28.3</v>
       </c>
       <c r="L35" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2016,41 +2016,41 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>93.28990881</v>
+        <v>294.13217351</v>
       </c>
       <c r="C36" t="n">
-        <v>114.975</v>
+        <v>556.1286129</v>
       </c>
       <c r="D36" t="n">
-        <v>104</v>
+        <v>403.5</v>
       </c>
       <c r="E36" t="n">
-        <v>90.572727</v>
+        <v>285.565217</v>
       </c>
       <c r="F36" t="n">
-        <v>109.5</v>
+        <v>529.646298</v>
       </c>
       <c r="G36" t="n">
-        <v>114.98</v>
+        <v>556.13</v>
       </c>
       <c r="H36" t="n">
-        <v>93.29000000000001</v>
+        <v>294.13</v>
       </c>
       <c r="I36" t="n">
-        <v>98.70999999999999</v>
+        <v>359.63</v>
       </c>
       <c r="J36" t="n">
-        <v>10.6</v>
+        <v>37.8</v>
       </c>
       <c r="K36" t="n">
-        <v>-10.3</v>
+        <v>-27.1</v>
       </c>
       <c r="L36" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2061,41 +2061,41 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>90.74299999999999</v>
+        <v>127.72</v>
       </c>
       <c r="C37" t="n">
-        <v>119.175</v>
+        <v>223.125</v>
       </c>
       <c r="D37" t="n">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="E37" t="n">
-        <v>88.09999999999999</v>
+        <v>124</v>
       </c>
       <c r="F37" t="n">
-        <v>113.5</v>
+        <v>212.5</v>
       </c>
       <c r="G37" t="n">
-        <v>119.18</v>
+        <v>223.12</v>
       </c>
       <c r="H37" t="n">
-        <v>90.73999999999999</v>
+        <v>127.72</v>
       </c>
       <c r="I37" t="n">
-        <v>97.84999999999999</v>
+        <v>151.57</v>
       </c>
       <c r="J37" t="n">
-        <v>13.5</v>
+        <v>32.8</v>
       </c>
       <c r="K37" t="n">
-        <v>-13.6</v>
+        <v>-24</v>
       </c>
       <c r="L37" t="n">
-        <v>0.99</v>
+        <v>1.37</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2106,176 +2106,176 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>127.72</v>
+        <v>141.64001431</v>
       </c>
       <c r="C38" t="n">
-        <v>223.125</v>
+        <v>203.6663265</v>
       </c>
       <c r="D38" t="n">
-        <v>177</v>
+        <v>168.5</v>
       </c>
       <c r="E38" t="n">
-        <v>124</v>
+        <v>137.514577</v>
       </c>
       <c r="F38" t="n">
-        <v>212.5</v>
+        <v>193.96793</v>
       </c>
       <c r="G38" t="n">
-        <v>223.12</v>
+        <v>203.67</v>
       </c>
       <c r="H38" t="n">
-        <v>127.72</v>
+        <v>141.64</v>
       </c>
       <c r="I38" t="n">
-        <v>151.57</v>
+        <v>157.15</v>
       </c>
       <c r="J38" t="n">
-        <v>26.1</v>
+        <v>20.9</v>
       </c>
       <c r="K38" t="n">
-        <v>-27.8</v>
+        <v>-15.9</v>
       </c>
       <c r="L38" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.31</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>624.1800000000001</v>
+        <v>971.2900000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>3470.25</v>
+        <v>1680</v>
       </c>
       <c r="D39" t="n">
-        <v>2100</v>
+        <v>1280</v>
       </c>
       <c r="E39" t="n">
-        <v>606</v>
+        <v>943</v>
       </c>
       <c r="F39" t="n">
-        <v>3305</v>
+        <v>1600</v>
       </c>
       <c r="G39" t="n">
-        <v>3470.25</v>
+        <v>1680</v>
       </c>
       <c r="H39" t="n">
-        <v>624.1799999999999</v>
+        <v>971.29</v>
       </c>
       <c r="I39" t="n">
-        <v>1335.7</v>
+        <v>1148.47</v>
       </c>
       <c r="J39" t="n">
-        <v>65.3</v>
+        <v>31.2</v>
       </c>
       <c r="K39" t="n">
-        <v>-70.3</v>
+        <v>-24.1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.93</v>
+        <v>1.3</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>101.64987909</v>
+        <v>98.57100000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>278.03973015</v>
+        <v>153.3</v>
       </c>
       <c r="D40" t="n">
-        <v>193</v>
+        <v>122.5</v>
       </c>
       <c r="E40" t="n">
-        <v>98.68920300000001</v>
+        <v>95.7</v>
       </c>
       <c r="F40" t="n">
-        <v>264.799743</v>
+        <v>146</v>
       </c>
       <c r="G40" t="n">
-        <v>278.04</v>
+        <v>153.3</v>
       </c>
       <c r="H40" t="n">
-        <v>101.65</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>145.75</v>
+        <v>112.25</v>
       </c>
       <c r="J40" t="n">
-        <v>44.1</v>
+        <v>25.1</v>
       </c>
       <c r="K40" t="n">
-        <v>-47.3</v>
+        <v>-19.5</v>
       </c>
       <c r="L40" t="n">
-        <v>0.93</v>
+        <v>1.29</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>39.7065</v>
+        <v>947.82327722</v>
       </c>
       <c r="C41" t="n">
-        <v>93.03</v>
+        <v>2910.13596825</v>
       </c>
       <c r="D41" t="n">
-        <v>67.59999999999999</v>
+        <v>1820</v>
       </c>
       <c r="E41" t="n">
-        <v>38.55</v>
+        <v>920.216774</v>
       </c>
       <c r="F41" t="n">
-        <v>88.59999999999999</v>
+        <v>2771.558065</v>
       </c>
       <c r="G41" t="n">
-        <v>93.03</v>
+        <v>2910.14</v>
       </c>
       <c r="H41" t="n">
-        <v>39.71</v>
+        <v>947.8200000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>53.04</v>
+        <v>1438.4</v>
       </c>
       <c r="J41" t="n">
-        <v>37.6</v>
+        <v>59.9</v>
       </c>
       <c r="K41" t="n">
-        <v>-41.3</v>
+        <v>-47.9</v>
       </c>
       <c r="L41" t="n">
-        <v>0.91</v>
+        <v>1.25</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2286,41 +2286,41 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>703.31864508</v>
+        <v>606.49914566</v>
       </c>
       <c r="C42" t="n">
-        <v>1826.16</v>
+        <v>1647.3453759</v>
       </c>
       <c r="D42" t="n">
-        <v>1300</v>
+        <v>1075</v>
       </c>
       <c r="E42" t="n">
-        <v>682.833636</v>
+        <v>588.834122</v>
       </c>
       <c r="F42" t="n">
-        <v>1739.2</v>
+        <v>1568.900358</v>
       </c>
       <c r="G42" t="n">
-        <v>1826.16</v>
+        <v>1647.35</v>
       </c>
       <c r="H42" t="n">
-        <v>703.3200000000001</v>
+        <v>606.5</v>
       </c>
       <c r="I42" t="n">
-        <v>984.03</v>
+        <v>866.71</v>
       </c>
       <c r="J42" t="n">
-        <v>40.5</v>
+        <v>53.2</v>
       </c>
       <c r="K42" t="n">
-        <v>-45.9</v>
+        <v>-43.6</v>
       </c>
       <c r="L42" t="n">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2331,41 +2331,41 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>276.555</v>
+        <v>101.64987909</v>
       </c>
       <c r="C43" t="n">
-        <v>459.9</v>
+        <v>278.03973015</v>
       </c>
       <c r="D43" t="n">
-        <v>377</v>
+        <v>181</v>
       </c>
       <c r="E43" t="n">
-        <v>268.5</v>
+        <v>98.68920300000001</v>
       </c>
       <c r="F43" t="n">
-        <v>438</v>
+        <v>264.799743</v>
       </c>
       <c r="G43" t="n">
-        <v>459.9</v>
+        <v>278.04</v>
       </c>
       <c r="H43" t="n">
-        <v>276.56</v>
+        <v>101.65</v>
       </c>
       <c r="I43" t="n">
-        <v>322.39</v>
+        <v>145.75</v>
       </c>
       <c r="J43" t="n">
-        <v>22</v>
+        <v>53.6</v>
       </c>
       <c r="K43" t="n">
-        <v>-26.6</v>
+        <v>-43.8</v>
       </c>
       <c r="L43" t="n">
-        <v>0.83</v>
+        <v>1.22</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -2376,41 +2376,41 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>252.15184757</v>
+        <v>309.20523574</v>
       </c>
       <c r="C44" t="n">
-        <v>541.8000000000001</v>
+        <v>611.0052333000001</v>
       </c>
       <c r="D44" t="n">
-        <v>411.5</v>
+        <v>448.5</v>
       </c>
       <c r="E44" t="n">
-        <v>244.807619</v>
+        <v>300.199258</v>
       </c>
       <c r="F44" t="n">
-        <v>516</v>
+        <v>581.909746</v>
       </c>
       <c r="G44" t="n">
-        <v>541.8</v>
+        <v>611.01</v>
       </c>
       <c r="H44" t="n">
-        <v>252.15</v>
+        <v>309.21</v>
       </c>
       <c r="I44" t="n">
-        <v>324.56</v>
+        <v>384.66</v>
       </c>
       <c r="J44" t="n">
-        <v>31.7</v>
+        <v>36.2</v>
       </c>
       <c r="K44" t="n">
-        <v>-38.7</v>
+        <v>-31.1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.82</v>
+        <v>1.17</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -2421,41 +2421,41 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>368.225</v>
+        <v>655.08</v>
       </c>
       <c r="C45" t="n">
-        <v>1564.5</v>
+        <v>3470.25</v>
       </c>
       <c r="D45" t="n">
-        <v>1030</v>
+        <v>2005</v>
       </c>
       <c r="E45" t="n">
-        <v>357.5</v>
+        <v>636</v>
       </c>
       <c r="F45" t="n">
-        <v>1490</v>
+        <v>3305</v>
       </c>
       <c r="G45" t="n">
-        <v>1564.5</v>
+        <v>3470.25</v>
       </c>
       <c r="H45" t="n">
-        <v>368.23</v>
+        <v>655.08</v>
       </c>
       <c r="I45" t="n">
-        <v>667.29</v>
+        <v>1358.87</v>
       </c>
       <c r="J45" t="n">
-        <v>51.9</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>-64.2</v>
+        <v>-67.3</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -2466,266 +2466,266 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>387.66964797</v>
+        <v>657.8355847500001</v>
       </c>
       <c r="C46" t="n">
-        <v>835.8000000000001</v>
+        <v>833.75727225</v>
       </c>
       <c r="D46" t="n">
-        <v>636</v>
+        <v>744</v>
       </c>
       <c r="E46" t="n">
-        <v>376.378299</v>
+        <v>638.675325</v>
       </c>
       <c r="F46" t="n">
-        <v>796</v>
+        <v>794.054545</v>
       </c>
       <c r="G46" t="n">
-        <v>835.8</v>
+        <v>833.76</v>
       </c>
       <c r="H46" t="n">
-        <v>387.67</v>
+        <v>657.84</v>
       </c>
       <c r="I46" t="n">
-        <v>499.7</v>
+        <v>701.8200000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>31.4</v>
+        <v>12.1</v>
       </c>
       <c r="K46" t="n">
-        <v>-39</v>
+        <v>-11.6</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8</v>
+        <v>1.04</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>136.92326733</v>
+        <v>2554.4</v>
       </c>
       <c r="C47" t="n">
-        <v>209.37295785</v>
+        <v>5922</v>
       </c>
       <c r="D47" t="n">
-        <v>177.5</v>
+        <v>4210</v>
       </c>
       <c r="E47" t="n">
-        <v>132.935211</v>
+        <v>2480</v>
       </c>
       <c r="F47" t="n">
-        <v>199.402817</v>
+        <v>5640</v>
       </c>
       <c r="G47" t="n">
-        <v>209.37</v>
+        <v>5922</v>
       </c>
       <c r="H47" t="n">
-        <v>136.92</v>
+        <v>2554.4</v>
       </c>
       <c r="I47" t="n">
-        <v>155.04</v>
+        <v>3396.3</v>
       </c>
       <c r="J47" t="n">
-        <v>18</v>
+        <v>40.7</v>
       </c>
       <c r="K47" t="n">
-        <v>-22.9</v>
+        <v>-39.3</v>
       </c>
       <c r="L47" t="n">
-        <v>0.79</v>
+        <v>1.03</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>842.8097436100001</v>
+        <v>181.795</v>
       </c>
       <c r="C48" t="n">
-        <v>1651.86</v>
+        <v>262.5</v>
       </c>
       <c r="D48" t="n">
-        <v>1305</v>
+        <v>221.5</v>
       </c>
       <c r="E48" t="n">
-        <v>818.261887</v>
+        <v>176.5</v>
       </c>
       <c r="F48" t="n">
-        <v>1573.2</v>
+        <v>250</v>
       </c>
       <c r="G48" t="n">
-        <v>1651.86</v>
+        <v>262.5</v>
       </c>
       <c r="H48" t="n">
-        <v>842.8099999999999</v>
+        <v>181.8</v>
       </c>
       <c r="I48" t="n">
-        <v>1045.07</v>
+        <v>201.97</v>
       </c>
       <c r="J48" t="n">
-        <v>26.6</v>
+        <v>18.5</v>
       </c>
       <c r="K48" t="n">
-        <v>-35.4</v>
+        <v>-17.9</v>
       </c>
       <c r="L48" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>30.8485</v>
+        <v>3502</v>
       </c>
       <c r="C49" t="n">
-        <v>37.3275</v>
+        <v>12064.5</v>
       </c>
       <c r="D49" t="n">
-        <v>34.55</v>
+        <v>7765</v>
       </c>
       <c r="E49" t="n">
-        <v>29.95</v>
+        <v>3400</v>
       </c>
       <c r="F49" t="n">
-        <v>35.55</v>
+        <v>11490</v>
       </c>
       <c r="G49" t="n">
-        <v>37.33</v>
+        <v>12064.5</v>
       </c>
       <c r="H49" t="n">
-        <v>30.85</v>
+        <v>3502</v>
       </c>
       <c r="I49" t="n">
-        <v>32.47</v>
+        <v>5642.62</v>
       </c>
       <c r="J49" t="n">
-        <v>8</v>
+        <v>55.4</v>
       </c>
       <c r="K49" t="n">
-        <v>-10.7</v>
+        <v>-54.9</v>
       </c>
       <c r="L49" t="n">
-        <v>0.75</v>
+        <v>1.01</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>294.13217351</v>
+        <v>115.875</v>
       </c>
       <c r="C50" t="n">
-        <v>556.1286129</v>
+        <v>170.1</v>
       </c>
       <c r="D50" t="n">
-        <v>445</v>
+        <v>143</v>
       </c>
       <c r="E50" t="n">
-        <v>285.565217</v>
+        <v>112.5</v>
       </c>
       <c r="F50" t="n">
-        <v>529.646298</v>
+        <v>162</v>
       </c>
       <c r="G50" t="n">
-        <v>556.13</v>
+        <v>170.1</v>
       </c>
       <c r="H50" t="n">
-        <v>294.13</v>
+        <v>115.88</v>
       </c>
       <c r="I50" t="n">
-        <v>359.63</v>
+        <v>129.43</v>
       </c>
       <c r="J50" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K50" t="n">
-        <v>-33.9</v>
+        <v>-19</v>
       </c>
       <c r="L50" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>143.685</v>
+        <v>1050.25820583</v>
       </c>
       <c r="C51" t="n">
-        <v>275.1</v>
+        <v>2700.13103115</v>
       </c>
       <c r="D51" t="n">
-        <v>219</v>
+        <v>1880</v>
       </c>
       <c r="E51" t="n">
-        <v>139.5</v>
+        <v>1019.668161</v>
       </c>
       <c r="F51" t="n">
-        <v>262</v>
+        <v>2571.553363</v>
       </c>
       <c r="G51" t="n">
-        <v>275.1</v>
+        <v>2700.13</v>
       </c>
       <c r="H51" t="n">
-        <v>143.69</v>
+        <v>1050.26</v>
       </c>
       <c r="I51" t="n">
-        <v>176.54</v>
+        <v>1462.73</v>
       </c>
       <c r="J51" t="n">
-        <v>25.6</v>
+        <v>43.6</v>
       </c>
       <c r="K51" t="n">
-        <v>-34.4</v>
+        <v>-44.1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.74</v>
+        <v>0.99</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -2736,131 +2736,131 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>690.1</v>
+        <v>691.49811788</v>
       </c>
       <c r="C52" t="n">
-        <v>874.6500000000001</v>
+        <v>1764</v>
       </c>
       <c r="D52" t="n">
-        <v>797</v>
+        <v>1230</v>
       </c>
       <c r="E52" t="n">
-        <v>670</v>
+        <v>671.357396</v>
       </c>
       <c r="F52" t="n">
-        <v>833</v>
+        <v>1680</v>
       </c>
       <c r="G52" t="n">
-        <v>874.65</v>
+        <v>1764</v>
       </c>
       <c r="H52" t="n">
-        <v>690.1</v>
+        <v>691.5</v>
       </c>
       <c r="I52" t="n">
-        <v>736.24</v>
+        <v>959.62</v>
       </c>
       <c r="J52" t="n">
-        <v>9.699999999999999</v>
+        <v>43.4</v>
       </c>
       <c r="K52" t="n">
-        <v>-13.4</v>
+        <v>-43.8</v>
       </c>
       <c r="L52" t="n">
-        <v>0.73</v>
+        <v>0.99</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>451.14</v>
+        <v>40.38815194</v>
       </c>
       <c r="C53" t="n">
-        <v>1018.5</v>
+        <v>60.31306155000001</v>
       </c>
       <c r="D53" t="n">
-        <v>783</v>
+        <v>50.4</v>
       </c>
       <c r="E53" t="n">
-        <v>438</v>
+        <v>39.211798</v>
       </c>
       <c r="F53" t="n">
-        <v>970</v>
+        <v>57.441011</v>
       </c>
       <c r="G53" t="n">
-        <v>1018.5</v>
+        <v>60.31</v>
       </c>
       <c r="H53" t="n">
-        <v>451.14</v>
+        <v>40.39</v>
       </c>
       <c r="I53" t="n">
-        <v>592.98</v>
+        <v>45.37</v>
       </c>
       <c r="J53" t="n">
-        <v>30.1</v>
+        <v>19.7</v>
       </c>
       <c r="K53" t="n">
-        <v>-42.4</v>
+        <v>-19.9</v>
       </c>
       <c r="L53" t="n">
-        <v>0.71</v>
+        <v>0.99</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>174.585</v>
+        <v>387.66964797</v>
       </c>
       <c r="C54" t="n">
-        <v>282.975</v>
+        <v>835.8000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>238</v>
+        <v>616</v>
       </c>
       <c r="E54" t="n">
-        <v>169.5</v>
+        <v>376.378299</v>
       </c>
       <c r="F54" t="n">
-        <v>269.5</v>
+        <v>796</v>
       </c>
       <c r="G54" t="n">
-        <v>282.98</v>
+        <v>835.8</v>
       </c>
       <c r="H54" t="n">
-        <v>174.59</v>
+        <v>387.67</v>
       </c>
       <c r="I54" t="n">
-        <v>201.68</v>
+        <v>499.7</v>
       </c>
       <c r="J54" t="n">
-        <v>18.9</v>
+        <v>35.7</v>
       </c>
       <c r="K54" t="n">
-        <v>-26.6</v>
+        <v>-37.1</v>
       </c>
       <c r="L54" t="n">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>5628</v>
       </c>
       <c r="D55" t="n">
-        <v>4230</v>
+        <v>3950</v>
       </c>
       <c r="E55" t="n">
         <v>2135</v>
@@ -2899,13 +2899,13 @@
         <v>3056.29</v>
       </c>
       <c r="J55" t="n">
-        <v>33</v>
+        <v>42.5</v>
       </c>
       <c r="K55" t="n">
-        <v>-48</v>
+        <v>-44.3</v>
       </c>
       <c r="L55" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -2916,86 +2916,86 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>86.31399999999999</v>
+        <v>136.92326733</v>
       </c>
       <c r="C56" t="n">
-        <v>245.175</v>
+        <v>209.37295785</v>
       </c>
       <c r="D56" t="n">
-        <v>184.5</v>
+        <v>174.5</v>
       </c>
       <c r="E56" t="n">
-        <v>83.8</v>
+        <v>132.935211</v>
       </c>
       <c r="F56" t="n">
-        <v>233.5</v>
+        <v>199.402817</v>
       </c>
       <c r="G56" t="n">
-        <v>245.18</v>
+        <v>209.37</v>
       </c>
       <c r="H56" t="n">
-        <v>86.31</v>
+        <v>136.92</v>
       </c>
       <c r="I56" t="n">
-        <v>126.03</v>
+        <v>155.04</v>
       </c>
       <c r="J56" t="n">
-        <v>32.9</v>
+        <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>-53.2</v>
+        <v>-21.5</v>
       </c>
       <c r="L56" t="n">
-        <v>0.62</v>
+        <v>0.93</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2554.4</v>
+        <v>276.555</v>
       </c>
       <c r="C57" t="n">
-        <v>5922</v>
+        <v>459.9</v>
       </c>
       <c r="D57" t="n">
-        <v>4650</v>
+        <v>373.5</v>
       </c>
       <c r="E57" t="n">
-        <v>2480</v>
+        <v>268.5</v>
       </c>
       <c r="F57" t="n">
-        <v>5640</v>
+        <v>438</v>
       </c>
       <c r="G57" t="n">
-        <v>5922</v>
+        <v>459.9</v>
       </c>
       <c r="H57" t="n">
-        <v>2554.4</v>
+        <v>276.56</v>
       </c>
       <c r="I57" t="n">
-        <v>3396.3</v>
+        <v>322.39</v>
       </c>
       <c r="J57" t="n">
-        <v>27.4</v>
+        <v>23.1</v>
       </c>
       <c r="K57" t="n">
-        <v>-45.1</v>
+        <v>-26</v>
       </c>
       <c r="L57" t="n">
-        <v>0.61</v>
+        <v>0.89</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -3006,86 +3006,86 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>113.3</v>
+        <v>2194.20362855</v>
       </c>
       <c r="C58" t="n">
-        <v>129.675</v>
+        <v>6219.16666665</v>
       </c>
       <c r="D58" t="n">
-        <v>123.5</v>
+        <v>4340</v>
       </c>
       <c r="E58" t="n">
-        <v>110</v>
+        <v>2130.294785</v>
       </c>
       <c r="F58" t="n">
-        <v>123.5</v>
+        <v>5923.015873</v>
       </c>
       <c r="G58" t="n">
-        <v>129.68</v>
+        <v>6219.17</v>
       </c>
       <c r="H58" t="n">
-        <v>113.3</v>
+        <v>2194.2</v>
       </c>
       <c r="I58" t="n">
-        <v>117.39</v>
+        <v>3200.44</v>
       </c>
       <c r="J58" t="n">
-        <v>5</v>
+        <v>43.3</v>
       </c>
       <c r="K58" t="n">
-        <v>-8.300000000000001</v>
+        <v>-49.4</v>
       </c>
       <c r="L58" t="n">
-        <v>0.61</v>
+        <v>0.88</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1012.34644684</v>
+        <v>143.685</v>
       </c>
       <c r="C59" t="n">
-        <v>2700.13103115</v>
+        <v>275.1</v>
       </c>
       <c r="D59" t="n">
-        <v>2075</v>
+        <v>213.5</v>
       </c>
       <c r="E59" t="n">
-        <v>982.860628</v>
+        <v>139.5</v>
       </c>
       <c r="F59" t="n">
-        <v>2571.553363</v>
+        <v>262</v>
       </c>
       <c r="G59" t="n">
-        <v>2700.13</v>
+        <v>275.1</v>
       </c>
       <c r="H59" t="n">
-        <v>1012.35</v>
+        <v>143.69</v>
       </c>
       <c r="I59" t="n">
-        <v>1434.29</v>
+        <v>176.54</v>
       </c>
       <c r="J59" t="n">
-        <v>30.1</v>
+        <v>28.9</v>
       </c>
       <c r="K59" t="n">
-        <v>-51.2</v>
+        <v>-32.7</v>
       </c>
       <c r="L59" t="n">
-        <v>0.59</v>
+        <v>0.88</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -3096,41 +3096,41 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>204.455</v>
+        <v>7479.819619880001</v>
       </c>
       <c r="C60" t="n">
-        <v>530.25</v>
+        <v>18889.24232475</v>
       </c>
       <c r="D60" t="n">
-        <v>409.5</v>
+        <v>13665</v>
       </c>
       <c r="E60" t="n">
-        <v>198.5</v>
+        <v>7261.960796</v>
       </c>
       <c r="F60" t="n">
-        <v>505</v>
+        <v>17989.754595</v>
       </c>
       <c r="G60" t="n">
-        <v>530.25</v>
+        <v>18889.24</v>
       </c>
       <c r="H60" t="n">
-        <v>204.46</v>
+        <v>7479.82</v>
       </c>
       <c r="I60" t="n">
-        <v>285.9</v>
+        <v>10332.18</v>
       </c>
       <c r="J60" t="n">
-        <v>29.5</v>
+        <v>38.2</v>
       </c>
       <c r="K60" t="n">
-        <v>-50.1</v>
+        <v>-45.3</v>
       </c>
       <c r="L60" t="n">
-        <v>0.59</v>
+        <v>0.84</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -3141,41 +3141,41 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>102.81265536</v>
+        <v>252.15184757</v>
       </c>
       <c r="C61" t="n">
-        <v>347.47028925</v>
+        <v>541.8000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>258</v>
+        <v>410</v>
       </c>
       <c r="E61" t="n">
-        <v>99.818112</v>
+        <v>244.807619</v>
       </c>
       <c r="F61" t="n">
-        <v>330.924085</v>
+        <v>516</v>
       </c>
       <c r="G61" t="n">
-        <v>347.47</v>
+        <v>541.8</v>
       </c>
       <c r="H61" t="n">
-        <v>102.81</v>
+        <v>252.15</v>
       </c>
       <c r="I61" t="n">
-        <v>163.98</v>
+        <v>324.56</v>
       </c>
       <c r="J61" t="n">
-        <v>34.7</v>
+        <v>32.1</v>
       </c>
       <c r="K61" t="n">
-        <v>-60.2</v>
+        <v>-38.5</v>
       </c>
       <c r="L61" t="n">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -3186,86 +3186,86 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>40.38815194</v>
+        <v>30.8485</v>
       </c>
       <c r="C62" t="n">
-        <v>60.31306155000001</v>
+        <v>37.3275</v>
       </c>
       <c r="D62" t="n">
-        <v>53.3</v>
+        <v>34.45</v>
       </c>
       <c r="E62" t="n">
-        <v>39.211798</v>
+        <v>29.95</v>
       </c>
       <c r="F62" t="n">
-        <v>57.441011</v>
+        <v>35.55</v>
       </c>
       <c r="G62" t="n">
-        <v>60.31</v>
+        <v>37.33</v>
       </c>
       <c r="H62" t="n">
-        <v>40.39</v>
+        <v>30.85</v>
       </c>
       <c r="I62" t="n">
-        <v>45.37</v>
+        <v>32.47</v>
       </c>
       <c r="J62" t="n">
-        <v>13.2</v>
+        <v>8.4</v>
       </c>
       <c r="K62" t="n">
-        <v>-24.2</v>
+        <v>-10.5</v>
       </c>
       <c r="L62" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>317.755</v>
+        <v>1302.95</v>
       </c>
       <c r="C63" t="n">
-        <v>627.9</v>
+        <v>3160.5</v>
       </c>
       <c r="D63" t="n">
-        <v>520</v>
+        <v>2350</v>
       </c>
       <c r="E63" t="n">
-        <v>308.5</v>
+        <v>1265</v>
       </c>
       <c r="F63" t="n">
-        <v>598</v>
+        <v>3010</v>
       </c>
       <c r="G63" t="n">
-        <v>627.9</v>
+        <v>3160.5</v>
       </c>
       <c r="H63" t="n">
-        <v>317.75</v>
+        <v>1302.95</v>
       </c>
       <c r="I63" t="n">
-        <v>395.29</v>
+        <v>1767.34</v>
       </c>
       <c r="J63" t="n">
-        <v>20.8</v>
+        <v>34.5</v>
       </c>
       <c r="K63" t="n">
-        <v>-38.9</v>
+        <v>-44.6</v>
       </c>
       <c r="L63" t="n">
-        <v>0.53</v>
+        <v>0.77</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -3276,41 +3276,41 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>181.795</v>
+        <v>39.7065</v>
       </c>
       <c r="C64" t="n">
-        <v>262.5</v>
+        <v>93.03</v>
       </c>
       <c r="D64" t="n">
-        <v>235</v>
+        <v>69.8</v>
       </c>
       <c r="E64" t="n">
-        <v>176.5</v>
+        <v>38.55</v>
       </c>
       <c r="F64" t="n">
-        <v>250</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>262.5</v>
+        <v>93.03</v>
       </c>
       <c r="H64" t="n">
-        <v>181.8</v>
+        <v>39.71</v>
       </c>
       <c r="I64" t="n">
-        <v>201.97</v>
+        <v>53.04</v>
       </c>
       <c r="J64" t="n">
-        <v>11.7</v>
+        <v>33.3</v>
       </c>
       <c r="K64" t="n">
-        <v>-22.6</v>
+        <v>-43.1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.52</v>
+        <v>0.77</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -3321,41 +3321,41 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>113.85245492</v>
+        <v>86.31399999999999</v>
       </c>
       <c r="C65" t="n">
-        <v>196.35</v>
+        <v>245.175</v>
       </c>
       <c r="D65" t="n">
-        <v>168</v>
+        <v>176.5</v>
       </c>
       <c r="E65" t="n">
-        <v>110.536364</v>
+        <v>83.8</v>
       </c>
       <c r="F65" t="n">
-        <v>187</v>
+        <v>233.5</v>
       </c>
       <c r="G65" t="n">
-        <v>196.35</v>
+        <v>245.18</v>
       </c>
       <c r="H65" t="n">
-        <v>113.85</v>
+        <v>86.31</v>
       </c>
       <c r="I65" t="n">
-        <v>134.48</v>
+        <v>126.03</v>
       </c>
       <c r="J65" t="n">
-        <v>16.9</v>
+        <v>38.9</v>
       </c>
       <c r="K65" t="n">
-        <v>-32.2</v>
+        <v>-51.1</v>
       </c>
       <c r="L65" t="n">
-        <v>0.52</v>
+        <v>0.76</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -3366,41 +3366,41 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>971.2900000000001</v>
+        <v>370.8</v>
       </c>
       <c r="C66" t="n">
-        <v>1680</v>
+        <v>1564.5</v>
       </c>
       <c r="D66" t="n">
-        <v>1440</v>
+        <v>1050</v>
       </c>
       <c r="E66" t="n">
-        <v>943</v>
+        <v>360</v>
       </c>
       <c r="F66" t="n">
-        <v>1600</v>
+        <v>1490</v>
       </c>
       <c r="G66" t="n">
-        <v>1680</v>
+        <v>1564.5</v>
       </c>
       <c r="H66" t="n">
-        <v>971.29</v>
+        <v>370.8</v>
       </c>
       <c r="I66" t="n">
-        <v>1148.47</v>
+        <v>669.23</v>
       </c>
       <c r="J66" t="n">
-        <v>16.7</v>
+        <v>49</v>
       </c>
       <c r="K66" t="n">
-        <v>-32.5</v>
+        <v>-64.7</v>
       </c>
       <c r="L66" t="n">
-        <v>0.51</v>
+        <v>0.76</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -3411,176 +3411,176 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>61.32276701</v>
+        <v>31.55249573</v>
       </c>
       <c r="C67" t="n">
-        <v>103.53</v>
+        <v>45.6715329</v>
       </c>
       <c r="D67" t="n">
-        <v>89.3</v>
+        <v>39.6</v>
       </c>
       <c r="E67" t="n">
-        <v>59.536667</v>
+        <v>30.633491</v>
       </c>
       <c r="F67" t="n">
-        <v>98.59999999999999</v>
+        <v>43.496698</v>
       </c>
       <c r="G67" t="n">
-        <v>103.53</v>
+        <v>45.67</v>
       </c>
       <c r="H67" t="n">
-        <v>61.32</v>
+        <v>31.55</v>
       </c>
       <c r="I67" t="n">
-        <v>71.87</v>
+        <v>35.08</v>
       </c>
       <c r="J67" t="n">
-        <v>15.9</v>
+        <v>15.3</v>
       </c>
       <c r="K67" t="n">
-        <v>-31.3</v>
+        <v>-20.3</v>
       </c>
       <c r="L67" t="n">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>606.49914566</v>
+        <v>113.3</v>
       </c>
       <c r="C68" t="n">
-        <v>1647.3453759</v>
+        <v>130.2</v>
       </c>
       <c r="D68" t="n">
-        <v>1305</v>
+        <v>123</v>
       </c>
       <c r="E68" t="n">
-        <v>588.834122</v>
+        <v>110</v>
       </c>
       <c r="F68" t="n">
-        <v>1568.900358</v>
+        <v>124</v>
       </c>
       <c r="G68" t="n">
-        <v>1647.35</v>
+        <v>130.2</v>
       </c>
       <c r="H68" t="n">
-        <v>606.5</v>
+        <v>113.3</v>
       </c>
       <c r="I68" t="n">
-        <v>866.71</v>
+        <v>117.53</v>
       </c>
       <c r="J68" t="n">
-        <v>26.2</v>
+        <v>5.9</v>
       </c>
       <c r="K68" t="n">
-        <v>-53.5</v>
+        <v>-7.9</v>
       </c>
       <c r="L68" t="n">
-        <v>0.49</v>
+        <v>0.74</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>578.80953618</v>
+        <v>209.605</v>
       </c>
       <c r="C69" t="n">
-        <v>1764</v>
+        <v>262.5</v>
       </c>
       <c r="D69" t="n">
-        <v>1380</v>
+        <v>241</v>
       </c>
       <c r="E69" t="n">
-        <v>561.951006</v>
+        <v>203.5</v>
       </c>
       <c r="F69" t="n">
-        <v>1680</v>
+        <v>250</v>
       </c>
       <c r="G69" t="n">
-        <v>1764</v>
+        <v>262.5</v>
       </c>
       <c r="H69" t="n">
-        <v>578.8099999999999</v>
+        <v>209.61</v>
       </c>
       <c r="I69" t="n">
-        <v>875.11</v>
+        <v>222.83</v>
       </c>
       <c r="J69" t="n">
-        <v>27.8</v>
+        <v>8.9</v>
       </c>
       <c r="K69" t="n">
-        <v>-58.1</v>
+        <v>-13</v>
       </c>
       <c r="L69" t="n">
-        <v>0.48</v>
+        <v>0.68</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>925.3533287</v>
+        <v>1071.2</v>
       </c>
       <c r="C70" t="n">
-        <v>2910.13596825</v>
+        <v>1743</v>
       </c>
       <c r="D70" t="n">
-        <v>2265</v>
+        <v>1480</v>
       </c>
       <c r="E70" t="n">
-        <v>898.40129</v>
+        <v>1040</v>
       </c>
       <c r="F70" t="n">
-        <v>2771.558065</v>
+        <v>1660</v>
       </c>
       <c r="G70" t="n">
-        <v>2910.14</v>
+        <v>1743</v>
       </c>
       <c r="H70" t="n">
-        <v>925.35</v>
+        <v>1071.2</v>
       </c>
       <c r="I70" t="n">
-        <v>1421.55</v>
+        <v>1239.15</v>
       </c>
       <c r="J70" t="n">
-        <v>28.5</v>
+        <v>17.8</v>
       </c>
       <c r="K70" t="n">
-        <v>-59.1</v>
+        <v>-27.6</v>
       </c>
       <c r="L70" t="n">
-        <v>0.48</v>
+        <v>0.64</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -3591,41 +3591,41 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1071.2</v>
+        <v>63.63683299</v>
       </c>
       <c r="C71" t="n">
-        <v>1743</v>
+        <v>103.53</v>
       </c>
       <c r="D71" t="n">
-        <v>1530</v>
+        <v>88.5</v>
       </c>
       <c r="E71" t="n">
-        <v>1040</v>
+        <v>61.783333</v>
       </c>
       <c r="F71" t="n">
-        <v>1660</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>1743</v>
+        <v>103.53</v>
       </c>
       <c r="H71" t="n">
-        <v>1071.2</v>
+        <v>63.64</v>
       </c>
       <c r="I71" t="n">
-        <v>1239.15</v>
+        <v>73.61</v>
       </c>
       <c r="J71" t="n">
-        <v>13.9</v>
+        <v>17</v>
       </c>
       <c r="K71" t="n">
-        <v>-30</v>
+        <v>-28.1</v>
       </c>
       <c r="L71" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -3636,41 +3636,41 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2194.20362855</v>
+        <v>245.43847958</v>
       </c>
       <c r="C72" t="n">
-        <v>6219.16666665</v>
+        <v>1281</v>
       </c>
       <c r="D72" t="n">
-        <v>5040</v>
+        <v>900</v>
       </c>
       <c r="E72" t="n">
-        <v>2130.294785</v>
+        <v>238.289786</v>
       </c>
       <c r="F72" t="n">
-        <v>5923.015873</v>
+        <v>1220</v>
       </c>
       <c r="G72" t="n">
-        <v>6219.17</v>
+        <v>1281</v>
       </c>
       <c r="H72" t="n">
-        <v>2194.2</v>
+        <v>245.44</v>
       </c>
       <c r="I72" t="n">
-        <v>3200.44</v>
+        <v>504.33</v>
       </c>
       <c r="J72" t="n">
-        <v>23.4</v>
+        <v>42.3</v>
       </c>
       <c r="K72" t="n">
-        <v>-56.5</v>
+        <v>-72.7</v>
       </c>
       <c r="L72" t="n">
-        <v>0.41</v>
+        <v>0.58</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -3681,41 +3681,41 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>243.62129178</v>
+        <v>108.38378425</v>
       </c>
       <c r="C73" t="n">
-        <v>642.6</v>
+        <v>347.47028925</v>
       </c>
       <c r="D73" t="n">
-        <v>530</v>
+        <v>260.5</v>
       </c>
       <c r="E73" t="n">
-        <v>236.525526</v>
+        <v>105.226975</v>
       </c>
       <c r="F73" t="n">
-        <v>612</v>
+        <v>330.924085</v>
       </c>
       <c r="G73" t="n">
-        <v>642.6</v>
+        <v>347.47</v>
       </c>
       <c r="H73" t="n">
-        <v>243.62</v>
+        <v>108.38</v>
       </c>
       <c r="I73" t="n">
-        <v>343.37</v>
+        <v>168.16</v>
       </c>
       <c r="J73" t="n">
-        <v>21.2</v>
+        <v>33.4</v>
       </c>
       <c r="K73" t="n">
-        <v>-54</v>
+        <v>-58.4</v>
       </c>
       <c r="L73" t="n">
-        <v>0.39</v>
+        <v>0.57</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -3726,41 +3726,41 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>312.09</v>
+        <v>113.85245492</v>
       </c>
       <c r="C74" t="n">
-        <v>1060.5</v>
+        <v>196.35</v>
       </c>
       <c r="D74" t="n">
-        <v>851</v>
+        <v>167</v>
       </c>
       <c r="E74" t="n">
-        <v>303</v>
+        <v>110.536364</v>
       </c>
       <c r="F74" t="n">
-        <v>1010</v>
+        <v>187</v>
       </c>
       <c r="G74" t="n">
-        <v>1060.5</v>
+        <v>196.35</v>
       </c>
       <c r="H74" t="n">
-        <v>312.09</v>
+        <v>113.85</v>
       </c>
       <c r="I74" t="n">
-        <v>499.19</v>
+        <v>134.48</v>
       </c>
       <c r="J74" t="n">
-        <v>24.6</v>
+        <v>17.6</v>
       </c>
       <c r="K74" t="n">
-        <v>-63.3</v>
+        <v>-31.8</v>
       </c>
       <c r="L74" t="n">
-        <v>0.39</v>
+        <v>0.55</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -3771,41 +3771,41 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>156.56</v>
+        <v>3293.32097618</v>
       </c>
       <c r="C75" t="n">
-        <v>213.3067608</v>
+        <v>6000.22536855</v>
       </c>
       <c r="D75" t="n">
-        <v>197.5</v>
+        <v>5040</v>
       </c>
       <c r="E75" t="n">
-        <v>152</v>
+        <v>3197.399006</v>
       </c>
       <c r="F75" t="n">
-        <v>203.149296</v>
+        <v>5714.500351</v>
       </c>
       <c r="G75" t="n">
-        <v>213.31</v>
+        <v>6000.23</v>
       </c>
       <c r="H75" t="n">
-        <v>156.56</v>
+        <v>3293.32</v>
       </c>
       <c r="I75" t="n">
-        <v>170.75</v>
+        <v>3970.05</v>
       </c>
       <c r="J75" t="n">
-        <v>8</v>
+        <v>19.1</v>
       </c>
       <c r="K75" t="n">
-        <v>-20.7</v>
+        <v>-34.7</v>
       </c>
       <c r="L75" t="n">
-        <v>0.39</v>
+        <v>0.55</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -3816,41 +3816,41 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>33.1145</v>
+        <v>243.62129178</v>
       </c>
       <c r="C76" t="n">
-        <v>47.9325</v>
+        <v>642.6</v>
       </c>
       <c r="D76" t="n">
-        <v>43.85</v>
+        <v>502</v>
       </c>
       <c r="E76" t="n">
-        <v>32.15</v>
+        <v>236.525526</v>
       </c>
       <c r="F76" t="n">
-        <v>45.65</v>
+        <v>612</v>
       </c>
       <c r="G76" t="n">
-        <v>47.93</v>
+        <v>642.6</v>
       </c>
       <c r="H76" t="n">
-        <v>33.11</v>
+        <v>243.62</v>
       </c>
       <c r="I76" t="n">
-        <v>36.82</v>
+        <v>343.37</v>
       </c>
       <c r="J76" t="n">
-        <v>9.300000000000001</v>
+        <v>28</v>
       </c>
       <c r="K76" t="n">
-        <v>-24.5</v>
+        <v>-51.5</v>
       </c>
       <c r="L76" t="n">
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -3865,16 +3865,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>306.94</v>
+        <v>311.575</v>
       </c>
       <c r="C77" t="n">
         <v>616.35</v>
       </c>
       <c r="D77" t="n">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="E77" t="n">
-        <v>298</v>
+        <v>302.5</v>
       </c>
       <c r="F77" t="n">
         <v>587</v>
@@ -3883,19 +3883,19 @@
         <v>616.35</v>
       </c>
       <c r="H77" t="n">
-        <v>306.94</v>
+        <v>311.57</v>
       </c>
       <c r="I77" t="n">
-        <v>384.29</v>
+        <v>387.77</v>
       </c>
       <c r="J77" t="n">
-        <v>16.1</v>
+        <v>21.1</v>
       </c>
       <c r="K77" t="n">
-        <v>-42.2</v>
+        <v>-38.8</v>
       </c>
       <c r="L77" t="n">
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -3906,86 +3906,86 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1457.45</v>
+        <v>156.56</v>
       </c>
       <c r="C78" t="n">
-        <v>5218.5</v>
+        <v>213.3067608</v>
       </c>
       <c r="D78" t="n">
-        <v>4195</v>
+        <v>194</v>
       </c>
       <c r="E78" t="n">
-        <v>1415</v>
+        <v>152</v>
       </c>
       <c r="F78" t="n">
-        <v>4970</v>
+        <v>203.149296</v>
       </c>
       <c r="G78" t="n">
-        <v>5218.5</v>
+        <v>213.31</v>
       </c>
       <c r="H78" t="n">
-        <v>1457.45</v>
+        <v>156.56</v>
       </c>
       <c r="I78" t="n">
-        <v>2397.71</v>
+        <v>170.75</v>
       </c>
       <c r="J78" t="n">
-        <v>24.4</v>
+        <v>10</v>
       </c>
       <c r="K78" t="n">
-        <v>-65.3</v>
+        <v>-19.3</v>
       </c>
       <c r="L78" t="n">
-        <v>0.37</v>
+        <v>0.52</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3293.32097618</v>
+        <v>1464.15186701</v>
       </c>
       <c r="C79" t="n">
-        <v>6000.22536855</v>
+        <v>5187.505272599999</v>
       </c>
       <c r="D79" t="n">
-        <v>5265</v>
+        <v>3925</v>
       </c>
       <c r="E79" t="n">
-        <v>3197.399006</v>
+        <v>1421.506667</v>
       </c>
       <c r="F79" t="n">
-        <v>5714.500351</v>
+        <v>4940.481212</v>
       </c>
       <c r="G79" t="n">
-        <v>6000.23</v>
+        <v>5187.51</v>
       </c>
       <c r="H79" t="n">
-        <v>3293.32</v>
+        <v>1464.15</v>
       </c>
       <c r="I79" t="n">
-        <v>3970.05</v>
+        <v>2394.99</v>
       </c>
       <c r="J79" t="n">
-        <v>14</v>
+        <v>32.2</v>
       </c>
       <c r="K79" t="n">
-        <v>-37.4</v>
+        <v>-62.7</v>
       </c>
       <c r="L79" t="n">
-        <v>0.37</v>
+        <v>0.51</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -3996,41 +3996,41 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>7351.19423237</v>
+        <v>104.545</v>
       </c>
       <c r="C80" t="n">
-        <v>20778.1652799</v>
+        <v>512.4</v>
       </c>
       <c r="D80" t="n">
-        <v>17265</v>
+        <v>376</v>
       </c>
       <c r="E80" t="n">
-        <v>7137.081779</v>
+        <v>101.5</v>
       </c>
       <c r="F80" t="n">
-        <v>19788.728838</v>
+        <v>488</v>
       </c>
       <c r="G80" t="n">
-        <v>20778.17</v>
+        <v>512.4</v>
       </c>
       <c r="H80" t="n">
-        <v>7351.19</v>
+        <v>104.55</v>
       </c>
       <c r="I80" t="n">
-        <v>10707.94</v>
+        <v>206.51</v>
       </c>
       <c r="J80" t="n">
-        <v>20.3</v>
+        <v>36.3</v>
       </c>
       <c r="K80" t="n">
-        <v>-57.4</v>
+        <v>-72.2</v>
       </c>
       <c r="L80" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -4041,41 +4041,41 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>115.875</v>
+        <v>312.09</v>
       </c>
       <c r="C81" t="n">
-        <v>168.525</v>
+        <v>1060.5</v>
       </c>
       <c r="D81" t="n">
-        <v>155</v>
+        <v>817</v>
       </c>
       <c r="E81" t="n">
-        <v>112.5</v>
+        <v>303</v>
       </c>
       <c r="F81" t="n">
-        <v>160.5</v>
+        <v>1010</v>
       </c>
       <c r="G81" t="n">
-        <v>168.53</v>
+        <v>1060.5</v>
       </c>
       <c r="H81" t="n">
-        <v>115.88</v>
+        <v>312.09</v>
       </c>
       <c r="I81" t="n">
-        <v>129.04</v>
+        <v>499.19</v>
       </c>
       <c r="J81" t="n">
-        <v>8.699999999999999</v>
+        <v>29.8</v>
       </c>
       <c r="K81" t="n">
-        <v>-25.2</v>
+        <v>-61.8</v>
       </c>
       <c r="L81" t="n">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -4086,41 +4086,41 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3182.7</v>
+        <v>451.14</v>
       </c>
       <c r="C82" t="n">
-        <v>12064.5</v>
+        <v>1018.5</v>
       </c>
       <c r="D82" t="n">
-        <v>9900</v>
+        <v>840</v>
       </c>
       <c r="E82" t="n">
-        <v>3090</v>
+        <v>438</v>
       </c>
       <c r="F82" t="n">
-        <v>11490</v>
+        <v>970</v>
       </c>
       <c r="G82" t="n">
-        <v>12064.5</v>
+        <v>1018.5</v>
       </c>
       <c r="H82" t="n">
-        <v>3182.7</v>
+        <v>451.14</v>
       </c>
       <c r="I82" t="n">
-        <v>5403.15</v>
+        <v>592.98</v>
       </c>
       <c r="J82" t="n">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="K82" t="n">
-        <v>-67.90000000000001</v>
+        <v>-46.3</v>
       </c>
       <c r="L82" t="n">
-        <v>0.32</v>
+        <v>0.46</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -4131,131 +4131,131 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>65.405</v>
+        <v>491.825</v>
       </c>
       <c r="C83" t="n">
-        <v>85.05</v>
+        <v>1036.35</v>
       </c>
       <c r="D83" t="n">
-        <v>80.40000000000001</v>
+        <v>875</v>
       </c>
       <c r="E83" t="n">
-        <v>63.5</v>
+        <v>477.5</v>
       </c>
       <c r="F83" t="n">
-        <v>81</v>
+        <v>987</v>
       </c>
       <c r="G83" t="n">
-        <v>85.05</v>
+        <v>1036.35</v>
       </c>
       <c r="H83" t="n">
-        <v>65.41</v>
+        <v>491.82</v>
       </c>
       <c r="I83" t="n">
-        <v>70.31999999999999</v>
+        <v>627.96</v>
       </c>
       <c r="J83" t="n">
-        <v>5.8</v>
+        <v>18.4</v>
       </c>
       <c r="K83" t="n">
-        <v>-18.7</v>
+        <v>-43.8</v>
       </c>
       <c r="L83" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>38.59008918000001</v>
+        <v>52.34033477000001</v>
       </c>
       <c r="C84" t="n">
-        <v>85.98940350000001</v>
+        <v>67.74120465</v>
       </c>
       <c r="D84" t="n">
-        <v>75</v>
+        <v>63.3</v>
       </c>
       <c r="E84" t="n">
-        <v>37.466106</v>
+        <v>50.815859</v>
       </c>
       <c r="F84" t="n">
-        <v>81.89467</v>
+        <v>64.515433</v>
       </c>
       <c r="G84" t="n">
-        <v>85.98999999999999</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>38.59</v>
+        <v>52.34</v>
       </c>
       <c r="I84" t="n">
-        <v>50.44</v>
+        <v>56.19</v>
       </c>
       <c r="J84" t="n">
-        <v>14.7</v>
+        <v>7</v>
       </c>
       <c r="K84" t="n">
-        <v>-48.5</v>
+        <v>-17.3</v>
       </c>
       <c r="L84" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1694.58551877</v>
+        <v>203.79860469</v>
       </c>
       <c r="C85" t="n">
-        <v>2661.75</v>
+        <v>528.5476518</v>
       </c>
       <c r="D85" t="n">
-        <v>2445</v>
+        <v>435.5</v>
       </c>
       <c r="E85" t="n">
-        <v>1645.228659</v>
+        <v>197.862723</v>
       </c>
       <c r="F85" t="n">
-        <v>2535</v>
+        <v>503.378716</v>
       </c>
       <c r="G85" t="n">
-        <v>2661.75</v>
+        <v>528.55</v>
       </c>
       <c r="H85" t="n">
-        <v>1694.59</v>
+        <v>203.8</v>
       </c>
       <c r="I85" t="n">
-        <v>1936.38</v>
+        <v>284.99</v>
       </c>
       <c r="J85" t="n">
-        <v>8.9</v>
+        <v>21.4</v>
       </c>
       <c r="K85" t="n">
-        <v>-30.7</v>
+        <v>-53.2</v>
       </c>
       <c r="L85" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -4266,41 +4266,41 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>239.81384837</v>
+        <v>450.62400914</v>
       </c>
       <c r="C86" t="n">
-        <v>1281</v>
+        <v>2016</v>
       </c>
       <c r="D86" t="n">
-        <v>1045</v>
+        <v>1570</v>
       </c>
       <c r="E86" t="n">
-        <v>232.828979</v>
+        <v>437.499038</v>
       </c>
       <c r="F86" t="n">
-        <v>1220</v>
+        <v>1920</v>
       </c>
       <c r="G86" t="n">
-        <v>1281</v>
+        <v>2016</v>
       </c>
       <c r="H86" t="n">
-        <v>239.81</v>
+        <v>450.62</v>
       </c>
       <c r="I86" t="n">
-        <v>500.11</v>
+        <v>841.97</v>
       </c>
       <c r="J86" t="n">
-        <v>22.6</v>
+        <v>28.4</v>
       </c>
       <c r="K86" t="n">
-        <v>-77.09999999999999</v>
+        <v>-71.3</v>
       </c>
       <c r="L86" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -4311,41 +4311,41 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>104.545</v>
+        <v>397.58</v>
       </c>
       <c r="C87" t="n">
-        <v>512.4</v>
+        <v>829.5</v>
       </c>
       <c r="D87" t="n">
-        <v>425</v>
+        <v>709</v>
       </c>
       <c r="E87" t="n">
-        <v>101.5</v>
+        <v>386</v>
       </c>
       <c r="F87" t="n">
-        <v>488</v>
+        <v>790</v>
       </c>
       <c r="G87" t="n">
-        <v>512.4</v>
+        <v>829.5</v>
       </c>
       <c r="H87" t="n">
-        <v>104.55</v>
+        <v>397.58</v>
       </c>
       <c r="I87" t="n">
-        <v>206.51</v>
+        <v>505.56</v>
       </c>
       <c r="J87" t="n">
-        <v>20.6</v>
+        <v>17</v>
       </c>
       <c r="K87" t="n">
-        <v>-75.40000000000001</v>
+        <v>-43.9</v>
       </c>
       <c r="L87" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -4356,41 +4356,41 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1302.95</v>
+        <v>12.1025</v>
       </c>
       <c r="C88" t="n">
-        <v>3160.5</v>
+        <v>44.7825</v>
       </c>
       <c r="D88" t="n">
-        <v>2760</v>
+        <v>36</v>
       </c>
       <c r="E88" t="n">
-        <v>1265</v>
+        <v>11.75</v>
       </c>
       <c r="F88" t="n">
-        <v>3010</v>
+        <v>42.65</v>
       </c>
       <c r="G88" t="n">
-        <v>3160.5</v>
+        <v>44.78</v>
       </c>
       <c r="H88" t="n">
-        <v>1302.95</v>
+        <v>12.1</v>
       </c>
       <c r="I88" t="n">
-        <v>1767.34</v>
+        <v>20.27</v>
       </c>
       <c r="J88" t="n">
-        <v>14.5</v>
+        <v>24.4</v>
       </c>
       <c r="K88" t="n">
-        <v>-52.8</v>
+        <v>-66.40000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -4401,41 +4401,41 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>397.58</v>
+        <v>1122.7</v>
       </c>
       <c r="C89" t="n">
-        <v>829.5</v>
+        <v>2966.25</v>
       </c>
       <c r="D89" t="n">
-        <v>756</v>
+        <v>2470</v>
       </c>
       <c r="E89" t="n">
-        <v>386</v>
+        <v>1090</v>
       </c>
       <c r="F89" t="n">
-        <v>790</v>
+        <v>2825</v>
       </c>
       <c r="G89" t="n">
-        <v>829.5</v>
+        <v>2966.25</v>
       </c>
       <c r="H89" t="n">
-        <v>397.58</v>
+        <v>1122.7</v>
       </c>
       <c r="I89" t="n">
-        <v>505.56</v>
+        <v>1583.59</v>
       </c>
       <c r="J89" t="n">
-        <v>9.699999999999999</v>
+        <v>20.1</v>
       </c>
       <c r="K89" t="n">
-        <v>-47.4</v>
+        <v>-54.5</v>
       </c>
       <c r="L89" t="n">
-        <v>0.21</v>
+        <v>0.37</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -4446,41 +4446,41 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>282.735</v>
+        <v>1720.18348768</v>
       </c>
       <c r="C90" t="n">
-        <v>565.95</v>
+        <v>2661.75</v>
       </c>
       <c r="D90" t="n">
-        <v>521</v>
+        <v>2415</v>
       </c>
       <c r="E90" t="n">
-        <v>274.5</v>
+        <v>1670.081056</v>
       </c>
       <c r="F90" t="n">
-        <v>539</v>
+        <v>2535</v>
       </c>
       <c r="G90" t="n">
-        <v>565.95</v>
+        <v>2661.75</v>
       </c>
       <c r="H90" t="n">
-        <v>282.74</v>
+        <v>1720.18</v>
       </c>
       <c r="I90" t="n">
-        <v>353.54</v>
+        <v>1955.58</v>
       </c>
       <c r="J90" t="n">
-        <v>8.6</v>
+        <v>10.2</v>
       </c>
       <c r="K90" t="n">
-        <v>-45.7</v>
+        <v>-28.8</v>
       </c>
       <c r="L90" t="n">
-        <v>0.19</v>
+        <v>0.36</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -4491,41 +4491,41 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>491.825</v>
+        <v>1591.35</v>
       </c>
       <c r="C91" t="n">
-        <v>1036.35</v>
+        <v>6562.5</v>
       </c>
       <c r="D91" t="n">
-        <v>948</v>
+        <v>5295</v>
       </c>
       <c r="E91" t="n">
-        <v>477.5</v>
+        <v>1545</v>
       </c>
       <c r="F91" t="n">
-        <v>987</v>
+        <v>6250</v>
       </c>
       <c r="G91" t="n">
-        <v>1036.35</v>
+        <v>6562.5</v>
       </c>
       <c r="H91" t="n">
-        <v>491.82</v>
+        <v>1591.35</v>
       </c>
       <c r="I91" t="n">
-        <v>627.96</v>
+        <v>2834.14</v>
       </c>
       <c r="J91" t="n">
-        <v>9.300000000000001</v>
+        <v>23.9</v>
       </c>
       <c r="K91" t="n">
-        <v>-48.1</v>
+        <v>-69.90000000000001</v>
       </c>
       <c r="L91" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -4536,41 +4536,41 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>266.90718673</v>
+        <v>74.366</v>
       </c>
       <c r="C92" t="n">
-        <v>758.5219929</v>
+        <v>147</v>
       </c>
       <c r="D92" t="n">
-        <v>682</v>
+        <v>129</v>
       </c>
       <c r="E92" t="n">
-        <v>259.133191</v>
+        <v>72.2</v>
       </c>
       <c r="F92" t="n">
-        <v>722.401898</v>
+        <v>140</v>
       </c>
       <c r="G92" t="n">
-        <v>758.52</v>
+        <v>147</v>
       </c>
       <c r="H92" t="n">
-        <v>266.91</v>
+        <v>74.37</v>
       </c>
       <c r="I92" t="n">
-        <v>389.81</v>
+        <v>92.52</v>
       </c>
       <c r="J92" t="n">
-        <v>11.2</v>
+        <v>14</v>
       </c>
       <c r="K92" t="n">
-        <v>-60.9</v>
+        <v>-42.4</v>
       </c>
       <c r="L92" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -4581,41 +4581,41 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>74.366</v>
+        <v>149.35</v>
       </c>
       <c r="C93" t="n">
-        <v>142.8</v>
+        <v>269.325</v>
       </c>
       <c r="D93" t="n">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="E93" t="n">
-        <v>72.2</v>
+        <v>145</v>
       </c>
       <c r="F93" t="n">
-        <v>136</v>
+        <v>256.5</v>
       </c>
       <c r="G93" t="n">
-        <v>142.8</v>
+        <v>269.32</v>
       </c>
       <c r="H93" t="n">
-        <v>74.37</v>
+        <v>149.35</v>
       </c>
       <c r="I93" t="n">
-        <v>91.47</v>
+        <v>179.34</v>
       </c>
       <c r="J93" t="n">
-        <v>7.4</v>
+        <v>12.2</v>
       </c>
       <c r="K93" t="n">
-        <v>-44.1</v>
+        <v>-37.8</v>
       </c>
       <c r="L93" t="n">
-        <v>0.17</v>
+        <v>0.32</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -4626,41 +4626,41 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>450.62400914</v>
+        <v>139.8182976</v>
       </c>
       <c r="C94" t="n">
-        <v>2016</v>
+        <v>425.25</v>
       </c>
       <c r="D94" t="n">
-        <v>1790</v>
+        <v>358.5</v>
       </c>
       <c r="E94" t="n">
-        <v>437.499038</v>
+        <v>135.74592</v>
       </c>
       <c r="F94" t="n">
-        <v>1920</v>
+        <v>405</v>
       </c>
       <c r="G94" t="n">
-        <v>2016</v>
+        <v>425.25</v>
       </c>
       <c r="H94" t="n">
-        <v>450.62</v>
+        <v>139.82</v>
       </c>
       <c r="I94" t="n">
-        <v>841.97</v>
+        <v>211.18</v>
       </c>
       <c r="J94" t="n">
-        <v>12.6</v>
+        <v>18.6</v>
       </c>
       <c r="K94" t="n">
-        <v>-74.8</v>
+        <v>-61</v>
       </c>
       <c r="L94" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -4671,41 +4671,41 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>404.275</v>
+        <v>40.32664343</v>
       </c>
       <c r="C95" t="n">
-        <v>772.8000000000001</v>
+        <v>86.52000000000001</v>
       </c>
       <c r="D95" t="n">
-        <v>721</v>
+        <v>76</v>
       </c>
       <c r="E95" t="n">
-        <v>392.5</v>
+        <v>39.152081</v>
       </c>
       <c r="F95" t="n">
-        <v>736</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G95" t="n">
-        <v>772.8</v>
+        <v>86.52</v>
       </c>
       <c r="H95" t="n">
-        <v>404.28</v>
+        <v>40.33</v>
       </c>
       <c r="I95" t="n">
-        <v>496.41</v>
+        <v>51.87</v>
       </c>
       <c r="J95" t="n">
-        <v>7.2</v>
+        <v>13.8</v>
       </c>
       <c r="K95" t="n">
-        <v>-43.9</v>
+        <v>-46.9</v>
       </c>
       <c r="L95" t="n">
-        <v>0.16</v>
+        <v>0.29</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -4716,41 +4716,41 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>11.5875</v>
+        <v>255.95657075</v>
       </c>
       <c r="C96" t="n">
-        <v>43.05</v>
+        <v>627.9</v>
       </c>
       <c r="D96" t="n">
-        <v>38.8</v>
+        <v>549</v>
       </c>
       <c r="E96" t="n">
-        <v>11.25</v>
+        <v>248.501525</v>
       </c>
       <c r="F96" t="n">
-        <v>41</v>
+        <v>598</v>
       </c>
       <c r="G96" t="n">
-        <v>43.05</v>
+        <v>627.9</v>
       </c>
       <c r="H96" t="n">
-        <v>11.59</v>
+        <v>255.96</v>
       </c>
       <c r="I96" t="n">
-        <v>19.45</v>
+        <v>348.94</v>
       </c>
       <c r="J96" t="n">
-        <v>11</v>
+        <v>14.4</v>
       </c>
       <c r="K96" t="n">
-        <v>-70.09999999999999</v>
+        <v>-53.4</v>
       </c>
       <c r="L96" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -4761,41 +4761,41 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>147.29</v>
+        <v>404.275</v>
       </c>
       <c r="C97" t="n">
-        <v>227.325</v>
+        <v>805.35</v>
       </c>
       <c r="D97" t="n">
-        <v>216.5</v>
+        <v>720</v>
       </c>
       <c r="E97" t="n">
-        <v>143</v>
+        <v>392.5</v>
       </c>
       <c r="F97" t="n">
-        <v>216.5</v>
+        <v>767</v>
       </c>
       <c r="G97" t="n">
-        <v>227.33</v>
+        <v>805.35</v>
       </c>
       <c r="H97" t="n">
-        <v>147.29</v>
+        <v>404.28</v>
       </c>
       <c r="I97" t="n">
-        <v>167.3</v>
+        <v>504.54</v>
       </c>
       <c r="J97" t="n">
-        <v>5</v>
+        <v>11.9</v>
       </c>
       <c r="K97" t="n">
-        <v>-32</v>
+        <v>-43.9</v>
       </c>
       <c r="L97" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -4806,41 +4806,41 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1122.7</v>
+        <v>483.29318658</v>
       </c>
       <c r="C98" t="n">
-        <v>2940</v>
+        <v>1484.6520297</v>
       </c>
       <c r="D98" t="n">
-        <v>2735</v>
+        <v>1285</v>
       </c>
       <c r="E98" t="n">
-        <v>1090</v>
+        <v>469.216686</v>
       </c>
       <c r="F98" t="n">
-        <v>2800</v>
+        <v>1413.954314</v>
       </c>
       <c r="G98" t="n">
-        <v>2940</v>
+        <v>1484.65</v>
       </c>
       <c r="H98" t="n">
-        <v>1122.7</v>
+        <v>483.29</v>
       </c>
       <c r="I98" t="n">
-        <v>1577.03</v>
+        <v>733.63</v>
       </c>
       <c r="J98" t="n">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="K98" t="n">
-        <v>-59</v>
+        <v>-62.4</v>
       </c>
       <c r="L98" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -4851,41 +4851,41 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>255.95657075</v>
+        <v>284.76904503</v>
       </c>
       <c r="C99" t="n">
-        <v>627.9</v>
+        <v>758.5219929</v>
       </c>
       <c r="D99" t="n">
-        <v>588</v>
+        <v>677</v>
       </c>
       <c r="E99" t="n">
-        <v>248.501525</v>
+        <v>276.474801</v>
       </c>
       <c r="F99" t="n">
-        <v>598</v>
+        <v>722.401898</v>
       </c>
       <c r="G99" t="n">
-        <v>627.9</v>
+        <v>758.52</v>
       </c>
       <c r="H99" t="n">
-        <v>255.96</v>
+        <v>284.77</v>
       </c>
       <c r="I99" t="n">
-        <v>348.94</v>
+        <v>403.21</v>
       </c>
       <c r="J99" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="K99" t="n">
-        <v>-56.5</v>
+        <v>-57.9</v>
       </c>
       <c r="L99" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -4896,41 +4896,41 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>512.4250000000001</v>
+        <v>2258.2829722</v>
       </c>
       <c r="C100" t="n">
-        <v>1501.5</v>
+        <v>8057.4659445</v>
       </c>
       <c r="D100" t="n">
-        <v>1395</v>
+        <v>7080</v>
       </c>
       <c r="E100" t="n">
-        <v>497.5</v>
+        <v>2192.50774</v>
       </c>
       <c r="F100" t="n">
-        <v>1430</v>
+        <v>7673.77709</v>
       </c>
       <c r="G100" t="n">
-        <v>1501.5</v>
+        <v>8057.47</v>
       </c>
       <c r="H100" t="n">
-        <v>512.4299999999999</v>
+        <v>2258.28</v>
       </c>
       <c r="I100" t="n">
-        <v>759.6900000000001</v>
+        <v>3708.08</v>
       </c>
       <c r="J100" t="n">
-        <v>7.6</v>
+        <v>13.8</v>
       </c>
       <c r="K100" t="n">
-        <v>-63.3</v>
+        <v>-68.09999999999999</v>
       </c>
       <c r="L100" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -4941,41 +4941,41 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2961.25</v>
+        <v>282.735</v>
       </c>
       <c r="C101" t="n">
-        <v>8557.5</v>
+        <v>590.1</v>
       </c>
       <c r="D101" t="n">
-        <v>8000</v>
+        <v>540</v>
       </c>
       <c r="E101" t="n">
-        <v>2875</v>
+        <v>274.5</v>
       </c>
       <c r="F101" t="n">
-        <v>8150</v>
+        <v>562</v>
       </c>
       <c r="G101" t="n">
-        <v>8557.5</v>
+        <v>590.1</v>
       </c>
       <c r="H101" t="n">
-        <v>2961.25</v>
+        <v>282.74</v>
       </c>
       <c r="I101" t="n">
-        <v>4360.31</v>
+        <v>359.58</v>
       </c>
       <c r="J101" t="n">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K101" t="n">
-        <v>-63</v>
+        <v>-47.6</v>
       </c>
       <c r="L101" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -4986,41 +4986,41 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>139.8182976</v>
+        <v>2961.25</v>
       </c>
       <c r="C102" t="n">
-        <v>395.69690475</v>
+        <v>8988</v>
       </c>
       <c r="D102" t="n">
-        <v>372.5</v>
+        <v>8250</v>
       </c>
       <c r="E102" t="n">
-        <v>135.74592</v>
+        <v>2875</v>
       </c>
       <c r="F102" t="n">
-        <v>376.854195</v>
+        <v>8560</v>
       </c>
       <c r="G102" t="n">
-        <v>395.7</v>
+        <v>8988</v>
       </c>
       <c r="H102" t="n">
-        <v>139.82</v>
+        <v>2961.25</v>
       </c>
       <c r="I102" t="n">
-        <v>203.79</v>
+        <v>4467.94</v>
       </c>
       <c r="J102" t="n">
-        <v>6.2</v>
+        <v>8.9</v>
       </c>
       <c r="K102" t="n">
-        <v>-62.5</v>
+        <v>-64.09999999999999</v>
       </c>
       <c r="L102" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -5031,90 +5031,86 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2085.75</v>
+        <v>742.63</v>
       </c>
       <c r="C103" t="n">
-        <v>7770</v>
+        <v>1170.75</v>
       </c>
       <c r="D103" t="n">
-        <v>7380</v>
+        <v>721</v>
       </c>
       <c r="E103" t="n">
-        <v>2025</v>
+        <v>721</v>
       </c>
       <c r="F103" t="n">
-        <v>7400</v>
+        <v>1115</v>
       </c>
       <c r="G103" t="n">
-        <v>7770</v>
+        <v>1170.75</v>
       </c>
       <c r="H103" t="n">
-        <v>2085.75</v>
+        <v>742.63</v>
       </c>
       <c r="I103" t="n">
-        <v>3506.81</v>
+        <v>849.66</v>
       </c>
       <c r="J103" t="n">
-        <v>5.3</v>
+        <v>62.4</v>
       </c>
       <c r="K103" t="n">
-        <v>-71.7</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0.07000000000000001</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🚨 已破止損(SL 失守, 重新評估支撐)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1575.9</v>
+        <v>38.934</v>
       </c>
       <c r="C104" t="n">
-        <v>6384</v>
+        <v>55.23</v>
       </c>
       <c r="D104" t="n">
-        <v>6080</v>
+        <v>38.8</v>
       </c>
       <c r="E104" t="n">
-        <v>1530</v>
+        <v>37.8</v>
       </c>
       <c r="F104" t="n">
-        <v>6080</v>
+        <v>52.6</v>
       </c>
       <c r="G104" t="n">
-        <v>6384</v>
+        <v>55.23</v>
       </c>
       <c r="H104" t="n">
-        <v>1575.9</v>
+        <v>38.93</v>
       </c>
       <c r="I104" t="n">
-        <v>2777.93</v>
+        <v>43.01</v>
       </c>
       <c r="J104" t="n">
-        <v>5</v>
+        <v>42.3</v>
       </c>
       <c r="K104" t="n">
-        <v>-74.09999999999999</v>
-      </c>
-      <c r="L104" t="n">
-        <v>0.07000000000000001</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🚨 已破止損(SL 失守, 重新評估支撐)</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5127,7 @@
         <v>163.24184205</v>
       </c>
       <c r="D105" t="n">
-        <v>112.5</v>
+        <v>112</v>
       </c>
       <c r="E105" t="n">
         <v>109.5</v>
@@ -5149,10 +5145,10 @@
         <v>125.4</v>
       </c>
       <c r="J105" t="n">
-        <v>45.1</v>
+        <v>45.8</v>
       </c>
       <c r="K105" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">

--- a/data/entry_signals_tw.xlsx
+++ b/data/entry_signals_tw.xlsx
@@ -486,41 +486,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.805</v>
+        <v>19.58896127</v>
       </c>
       <c r="C2" t="n">
-        <v>65.205</v>
+        <v>30.5471418</v>
       </c>
       <c r="D2" t="n">
-        <v>45.6</v>
+        <v>19.8</v>
       </c>
       <c r="E2" t="n">
-        <v>43.5</v>
+        <v>19.018409</v>
       </c>
       <c r="F2" t="n">
-        <v>62.1</v>
+        <v>29.092516</v>
       </c>
       <c r="G2" t="n">
-        <v>65.2</v>
+        <v>30.55</v>
       </c>
       <c r="H2" t="n">
-        <v>44.8</v>
+        <v>19.59</v>
       </c>
       <c r="I2" t="n">
-        <v>49.91</v>
+        <v>22.33</v>
       </c>
       <c r="J2" t="n">
-        <v>43</v>
+        <v>54.3</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.7</v>
+        <v>-1.1</v>
       </c>
       <c r="L2" t="n">
-        <v>24.66</v>
+        <v>50.92</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -531,41 +531,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>891.03583299</v>
+        <v>1266.9</v>
       </c>
       <c r="C3" t="n">
-        <v>1354.7205</v>
+        <v>2644.1631783</v>
       </c>
       <c r="D3" t="n">
-        <v>920</v>
+        <v>1300</v>
       </c>
       <c r="E3" t="n">
-        <v>865.083333</v>
+        <v>1230</v>
       </c>
       <c r="F3" t="n">
-        <v>1290.21</v>
+        <v>2518.250646</v>
       </c>
       <c r="G3" t="n">
-        <v>1354.72</v>
+        <v>2644.16</v>
       </c>
       <c r="H3" t="n">
-        <v>891.04</v>
+        <v>1266.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1006.96</v>
+        <v>1611.22</v>
       </c>
       <c r="J3" t="n">
-        <v>47.3</v>
+        <v>103.4</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.1</v>
+        <v>-2.5</v>
       </c>
       <c r="L3" t="n">
-        <v>15.01</v>
+        <v>40.61</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -576,41 +576,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.866</v>
+        <v>56.032</v>
       </c>
       <c r="C4" t="n">
-        <v>33.81861420000001</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>23.6</v>
+        <v>57</v>
       </c>
       <c r="E4" t="n">
-        <v>22.2</v>
+        <v>54.4</v>
       </c>
       <c r="F4" t="n">
-        <v>32.208204</v>
+        <v>81.2</v>
       </c>
       <c r="G4" t="n">
-        <v>33.82</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>22.87</v>
+        <v>56.03</v>
       </c>
       <c r="I4" t="n">
-        <v>25.6</v>
+        <v>63.34</v>
       </c>
       <c r="J4" t="n">
-        <v>43.3</v>
+        <v>49.6</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.1</v>
+        <v>-1.7</v>
       </c>
       <c r="L4" t="n">
-        <v>13.92</v>
+        <v>29.19</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -621,41 +621,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71.07000000000001</v>
+        <v>38.84708345</v>
       </c>
       <c r="C5" t="n">
-        <v>111.0765831</v>
+        <v>45.24471735</v>
       </c>
       <c r="D5" t="n">
-        <v>73.90000000000001</v>
+        <v>39.1</v>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>37.715615</v>
       </c>
       <c r="F5" t="n">
-        <v>105.787222</v>
+        <v>43.090207</v>
       </c>
       <c r="G5" t="n">
-        <v>111.08</v>
+        <v>45.24</v>
       </c>
       <c r="H5" t="n">
-        <v>71.06999999999999</v>
+        <v>38.85</v>
       </c>
       <c r="I5" t="n">
-        <v>81.06999999999999</v>
+        <v>40.45</v>
       </c>
       <c r="J5" t="n">
-        <v>50.3</v>
+        <v>15.7</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.8</v>
+        <v>-0.6</v>
       </c>
       <c r="L5" t="n">
-        <v>13.14</v>
+        <v>24.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -666,41 +666,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>89.404</v>
+        <v>250.805</v>
       </c>
       <c r="C6" t="n">
-        <v>124.425</v>
+        <v>486.675</v>
       </c>
       <c r="D6" t="n">
-        <v>92.2</v>
+        <v>262</v>
       </c>
       <c r="E6" t="n">
-        <v>86.8</v>
+        <v>243.5</v>
       </c>
       <c r="F6" t="n">
-        <v>118.5</v>
+        <v>463.5</v>
       </c>
       <c r="G6" t="n">
-        <v>124.43</v>
+        <v>486.68</v>
       </c>
       <c r="H6" t="n">
-        <v>89.40000000000001</v>
+        <v>250.81</v>
       </c>
       <c r="I6" t="n">
-        <v>98.16</v>
+        <v>309.77</v>
       </c>
       <c r="J6" t="n">
-        <v>35</v>
+        <v>85.8</v>
       </c>
       <c r="K6" t="n">
-        <v>-3</v>
+        <v>-4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>11.53</v>
+        <v>20.07</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -711,41 +711,41 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38.36570677</v>
+        <v>89.404</v>
       </c>
       <c r="C7" t="n">
-        <v>45.24471735</v>
+        <v>124.425</v>
       </c>
       <c r="D7" t="n">
-        <v>39.25</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>37.248259</v>
+        <v>86.8</v>
       </c>
       <c r="F7" t="n">
-        <v>43.090207</v>
+        <v>118.5</v>
       </c>
       <c r="G7" t="n">
-        <v>45.24</v>
+        <v>124.43</v>
       </c>
       <c r="H7" t="n">
-        <v>38.37</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>40.09</v>
+        <v>98.16</v>
       </c>
       <c r="J7" t="n">
-        <v>15.3</v>
+        <v>36.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.3</v>
+        <v>-1.9</v>
       </c>
       <c r="L7" t="n">
-        <v>6.78</v>
+        <v>19.65</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -756,41 +756,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>130.8919571</v>
+        <v>173.57934302</v>
       </c>
       <c r="C8" t="n">
-        <v>148.5964515</v>
+        <v>250.6371336</v>
       </c>
       <c r="D8" t="n">
-        <v>133.5</v>
+        <v>178</v>
       </c>
       <c r="E8" t="n">
-        <v>127.07957</v>
+        <v>168.523634</v>
       </c>
       <c r="F8" t="n">
-        <v>141.52043</v>
+        <v>238.702032</v>
       </c>
       <c r="G8" t="n">
-        <v>148.6</v>
+        <v>250.64</v>
       </c>
       <c r="H8" t="n">
-        <v>130.89</v>
+        <v>173.58</v>
       </c>
       <c r="I8" t="n">
-        <v>135.32</v>
+        <v>192.84</v>
       </c>
       <c r="J8" t="n">
-        <v>11.3</v>
+        <v>40.8</v>
       </c>
       <c r="K8" t="n">
-        <v>-2</v>
+        <v>-2.5</v>
       </c>
       <c r="L8" t="n">
-        <v>5.79</v>
+        <v>16.43</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -801,41 +801,41 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1236</v>
+        <v>22.866</v>
       </c>
       <c r="C9" t="n">
-        <v>2667</v>
+        <v>33.81861420000001</v>
       </c>
       <c r="D9" t="n">
-        <v>1480</v>
+        <v>23.5</v>
       </c>
       <c r="E9" t="n">
-        <v>1200</v>
+        <v>22.2</v>
       </c>
       <c r="F9" t="n">
-        <v>2540</v>
+        <v>32.208204</v>
       </c>
       <c r="G9" t="n">
-        <v>2667</v>
+        <v>33.82</v>
       </c>
       <c r="H9" t="n">
-        <v>1236</v>
+        <v>22.87</v>
       </c>
       <c r="I9" t="n">
-        <v>1593.75</v>
+        <v>25.6</v>
       </c>
       <c r="J9" t="n">
-        <v>80.2</v>
+        <v>43.9</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.5</v>
+        <v>-2.7</v>
       </c>
       <c r="L9" t="n">
-        <v>4.86</v>
+        <v>16.28</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -846,41 +846,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69.99253039</v>
+        <v>122.04276875</v>
       </c>
       <c r="C10" t="n">
-        <v>142.9118481</v>
+        <v>180.779025</v>
       </c>
       <c r="D10" t="n">
-        <v>82.8</v>
+        <v>127</v>
       </c>
       <c r="E10" t="n">
-        <v>67.953913</v>
+        <v>118.488125</v>
       </c>
       <c r="F10" t="n">
-        <v>136.106522</v>
+        <v>172.1705</v>
       </c>
       <c r="G10" t="n">
-        <v>142.91</v>
+        <v>180.78</v>
       </c>
       <c r="H10" t="n">
-        <v>69.98999999999999</v>
+        <v>122.04</v>
       </c>
       <c r="I10" t="n">
-        <v>88.22</v>
+        <v>136.73</v>
       </c>
       <c r="J10" t="n">
-        <v>72.59999999999999</v>
+        <v>42.3</v>
       </c>
       <c r="K10" t="n">
-        <v>-15.5</v>
+        <v>-3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>4.69</v>
+        <v>10.85</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -891,41 +891,41 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>141.71465429</v>
+        <v>183.34</v>
       </c>
       <c r="C11" t="n">
-        <v>161.7</v>
+        <v>282.975</v>
       </c>
       <c r="D11" t="n">
-        <v>145.5</v>
+        <v>194</v>
       </c>
       <c r="E11" t="n">
-        <v>137.587043</v>
+        <v>178</v>
       </c>
       <c r="F11" t="n">
-        <v>154</v>
+        <v>269.5</v>
       </c>
       <c r="G11" t="n">
-        <v>161.7</v>
+        <v>282.98</v>
       </c>
       <c r="H11" t="n">
-        <v>141.71</v>
+        <v>183.34</v>
       </c>
       <c r="I11" t="n">
-        <v>146.71</v>
+        <v>208.25</v>
       </c>
       <c r="J11" t="n">
-        <v>11.1</v>
+        <v>45.9</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.6</v>
+        <v>-5.5</v>
       </c>
       <c r="L11" t="n">
-        <v>4.28</v>
+        <v>8.35</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -936,41 +936,41 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19.58896127</v>
+        <v>96.45715881000001</v>
       </c>
       <c r="C12" t="n">
-        <v>30.5471418</v>
+        <v>114.975</v>
       </c>
       <c r="D12" t="n">
-        <v>21.8</v>
+        <v>98.5</v>
       </c>
       <c r="E12" t="n">
-        <v>19.018409</v>
+        <v>93.647727</v>
       </c>
       <c r="F12" t="n">
-        <v>29.092516</v>
+        <v>109.5</v>
       </c>
       <c r="G12" t="n">
-        <v>30.55</v>
+        <v>114.98</v>
       </c>
       <c r="H12" t="n">
-        <v>19.59</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>22.33</v>
+        <v>101.09</v>
       </c>
       <c r="J12" t="n">
-        <v>40.1</v>
+        <v>16.7</v>
       </c>
       <c r="K12" t="n">
-        <v>-10.1</v>
+        <v>-2.1</v>
       </c>
       <c r="L12" t="n">
-        <v>3.96</v>
+        <v>8.06</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -981,41 +981,41 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>170.11119397</v>
+        <v>289.48193054</v>
       </c>
       <c r="C13" t="n">
-        <v>197.6116716</v>
+        <v>795.9944748</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>356</v>
       </c>
       <c r="E13" t="n">
-        <v>165.156499</v>
+        <v>281.050418</v>
       </c>
       <c r="F13" t="n">
-        <v>188.201592</v>
+        <v>758.089976</v>
       </c>
       <c r="G13" t="n">
-        <v>197.61</v>
+        <v>795.99</v>
       </c>
       <c r="H13" t="n">
-        <v>170.11</v>
+        <v>289.48</v>
       </c>
       <c r="I13" t="n">
-        <v>176.99</v>
+        <v>416.11</v>
       </c>
       <c r="J13" t="n">
-        <v>12.3</v>
+        <v>123.6</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.3</v>
+        <v>-18.7</v>
       </c>
       <c r="L13" t="n">
-        <v>3.67</v>
+        <v>6.61</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1026,41 +1026,41 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2335.80629197</v>
+        <v>98.57100000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>4673.55212625</v>
+        <v>153.3</v>
       </c>
       <c r="D14" t="n">
-        <v>2855</v>
+        <v>106</v>
       </c>
       <c r="E14" t="n">
-        <v>2267.773099</v>
+        <v>95.7</v>
       </c>
       <c r="F14" t="n">
-        <v>4451.002025</v>
+        <v>146</v>
       </c>
       <c r="G14" t="n">
-        <v>4673.55</v>
+        <v>153.3</v>
       </c>
       <c r="H14" t="n">
-        <v>2335.81</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>2920.24</v>
+        <v>112.25</v>
       </c>
       <c r="J14" t="n">
-        <v>63.7</v>
+        <v>44.6</v>
       </c>
       <c r="K14" t="n">
-        <v>-18.2</v>
+        <v>-7</v>
       </c>
       <c r="L14" t="n">
-        <v>3.5</v>
+        <v>6.37</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1071,41 +1071,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>56.032</v>
+        <v>843.5700000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>85.26000000000001</v>
+        <v>1354.7205</v>
       </c>
       <c r="D15" t="n">
-        <v>62.6</v>
+        <v>913</v>
       </c>
       <c r="E15" t="n">
-        <v>54.4</v>
+        <v>819</v>
       </c>
       <c r="F15" t="n">
-        <v>81.2</v>
+        <v>1290.21</v>
       </c>
       <c r="G15" t="n">
-        <v>85.26000000000001</v>
+        <v>1354.72</v>
       </c>
       <c r="H15" t="n">
-        <v>56.03</v>
+        <v>843.5700000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>63.34</v>
+        <v>971.36</v>
       </c>
       <c r="J15" t="n">
-        <v>36.2</v>
+        <v>48.4</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.5</v>
+        <v>-7.6</v>
       </c>
       <c r="L15" t="n">
-        <v>3.45</v>
+        <v>6.36</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1116,41 +1116,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2369</v>
+        <v>106.605</v>
       </c>
       <c r="C16" t="n">
-        <v>5969.25</v>
+        <v>192.15</v>
       </c>
       <c r="D16" t="n">
-        <v>3205</v>
+        <v>118.5</v>
       </c>
       <c r="E16" t="n">
-        <v>2300</v>
+        <v>103.5</v>
       </c>
       <c r="F16" t="n">
-        <v>5685</v>
+        <v>183</v>
       </c>
       <c r="G16" t="n">
-        <v>5969.25</v>
+        <v>192.15</v>
       </c>
       <c r="H16" t="n">
-        <v>2369</v>
+        <v>106.61</v>
       </c>
       <c r="I16" t="n">
-        <v>3269.06</v>
+        <v>127.99</v>
       </c>
       <c r="J16" t="n">
-        <v>86.2</v>
+        <v>62.2</v>
       </c>
       <c r="K16" t="n">
-        <v>-26.1</v>
+        <v>-10</v>
       </c>
       <c r="L16" t="n">
-        <v>3.31</v>
+        <v>6.19</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1161,446 +1161,446 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94.863</v>
+        <v>153.80987013</v>
       </c>
       <c r="C17" t="n">
-        <v>124.13135595</v>
+        <v>192.6356628</v>
       </c>
       <c r="D17" t="n">
-        <v>103</v>
+        <v>159.5</v>
       </c>
       <c r="E17" t="n">
-        <v>92.09999999999999</v>
+        <v>149.329971</v>
       </c>
       <c r="F17" t="n">
-        <v>118.220339</v>
+        <v>183.462536</v>
       </c>
       <c r="G17" t="n">
-        <v>124.13</v>
+        <v>192.64</v>
       </c>
       <c r="H17" t="n">
-        <v>94.86</v>
+        <v>153.81</v>
       </c>
       <c r="I17" t="n">
-        <v>102.18</v>
+        <v>163.52</v>
       </c>
       <c r="J17" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.9</v>
+        <v>-3.6</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>5.82</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>87.38638965</v>
+        <v>657.8355847500001</v>
       </c>
       <c r="C18" t="n">
-        <v>114.7666821</v>
+        <v>833.75727225</v>
       </c>
       <c r="D18" t="n">
-        <v>95</v>
+        <v>686</v>
       </c>
       <c r="E18" t="n">
-        <v>84.841155</v>
+        <v>638.675325</v>
       </c>
       <c r="F18" t="n">
-        <v>109.301602</v>
+        <v>794.054545</v>
       </c>
       <c r="G18" t="n">
-        <v>114.77</v>
+        <v>833.76</v>
       </c>
       <c r="H18" t="n">
-        <v>87.39</v>
+        <v>657.84</v>
       </c>
       <c r="I18" t="n">
-        <v>94.23</v>
+        <v>701.8200000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="K18" t="n">
-        <v>-8</v>
+        <v>-4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6</v>
+        <v>5.25</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>121.71221909</v>
+        <v>170.11119397</v>
       </c>
       <c r="C19" t="n">
-        <v>203.58520875</v>
+        <v>197.6116716</v>
       </c>
       <c r="D19" t="n">
-        <v>144.5</v>
+        <v>175</v>
       </c>
       <c r="E19" t="n">
-        <v>118.167203</v>
+        <v>165.156499</v>
       </c>
       <c r="F19" t="n">
-        <v>193.890675</v>
+        <v>188.201592</v>
       </c>
       <c r="G19" t="n">
-        <v>203.59</v>
+        <v>197.61</v>
       </c>
       <c r="H19" t="n">
-        <v>121.71</v>
+        <v>170.11</v>
       </c>
       <c r="I19" t="n">
-        <v>142.18</v>
+        <v>176.99</v>
       </c>
       <c r="J19" t="n">
-        <v>40.9</v>
+        <v>12.9</v>
       </c>
       <c r="K19" t="n">
-        <v>-15.8</v>
+        <v>-2.8</v>
       </c>
       <c r="L19" t="n">
-        <v>2.59</v>
+        <v>4.63</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>103.12004547</v>
+        <v>294.13217351</v>
       </c>
       <c r="C20" t="n">
-        <v>122.22362355</v>
+        <v>556.1286129</v>
       </c>
       <c r="D20" t="n">
-        <v>108.5</v>
+        <v>349</v>
       </c>
       <c r="E20" t="n">
-        <v>100.116549</v>
+        <v>285.565217</v>
       </c>
       <c r="F20" t="n">
-        <v>116.403451</v>
+        <v>529.646298</v>
       </c>
       <c r="G20" t="n">
-        <v>122.22</v>
+        <v>556.13</v>
       </c>
       <c r="H20" t="n">
-        <v>103.12</v>
+        <v>294.13</v>
       </c>
       <c r="I20" t="n">
-        <v>107.9</v>
+        <v>359.63</v>
       </c>
       <c r="J20" t="n">
-        <v>12.6</v>
+        <v>59.3</v>
       </c>
       <c r="K20" t="n">
-        <v>-5</v>
+        <v>-15.7</v>
       </c>
       <c r="L20" t="n">
-        <v>2.55</v>
+        <v>3.78</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>101.36665072</v>
+        <v>121.71221909</v>
       </c>
       <c r="C21" t="n">
-        <v>122.8038357</v>
+        <v>203.58520875</v>
       </c>
       <c r="D21" t="n">
-        <v>107.5</v>
+        <v>139</v>
       </c>
       <c r="E21" t="n">
-        <v>98.414224</v>
+        <v>118.167203</v>
       </c>
       <c r="F21" t="n">
-        <v>116.956034</v>
+        <v>193.890675</v>
       </c>
       <c r="G21" t="n">
-        <v>122.8</v>
+        <v>203.59</v>
       </c>
       <c r="H21" t="n">
-        <v>101.37</v>
+        <v>121.71</v>
       </c>
       <c r="I21" t="n">
-        <v>106.73</v>
+        <v>142.18</v>
       </c>
       <c r="J21" t="n">
-        <v>14.2</v>
+        <v>46.5</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.7</v>
+        <v>-12.4</v>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>3.74</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>95.97727254000002</v>
+        <v>2369</v>
       </c>
       <c r="C22" t="n">
-        <v>114.975</v>
+        <v>5969.25</v>
       </c>
       <c r="D22" t="n">
-        <v>101.5</v>
+        <v>3210</v>
       </c>
       <c r="E22" t="n">
-        <v>93.18181800000001</v>
+        <v>2300</v>
       </c>
       <c r="F22" t="n">
-        <v>109.5</v>
+        <v>5685</v>
       </c>
       <c r="G22" t="n">
-        <v>114.98</v>
+        <v>5969.25</v>
       </c>
       <c r="H22" t="n">
-        <v>95.98</v>
+        <v>2369</v>
       </c>
       <c r="I22" t="n">
-        <v>100.73</v>
+        <v>3269.06</v>
       </c>
       <c r="J22" t="n">
-        <v>13.3</v>
+        <v>86</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.4</v>
+        <v>-26.2</v>
       </c>
       <c r="L22" t="n">
-        <v>2.44</v>
+        <v>3.28</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>270.89</v>
+        <v>68.90700000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>800.1</v>
+        <v>150.675</v>
       </c>
       <c r="D23" t="n">
-        <v>432.5</v>
+        <v>88.7</v>
       </c>
       <c r="E23" t="n">
-        <v>263</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>762</v>
+        <v>143.5</v>
       </c>
       <c r="G23" t="n">
-        <v>800.1</v>
+        <v>150.68</v>
       </c>
       <c r="H23" t="n">
-        <v>270.89</v>
+        <v>68.91</v>
       </c>
       <c r="I23" t="n">
-        <v>403.19</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>85</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-37.4</v>
+        <v>-22.3</v>
       </c>
       <c r="L23" t="n">
-        <v>2.27</v>
+        <v>3.13</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟢 進場區(盈虧比 &gt;= 3:1)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>703.31864508</v>
+        <v>94.863</v>
       </c>
       <c r="C24" t="n">
-        <v>1826.16</v>
+        <v>124.13135595</v>
       </c>
       <c r="D24" t="n">
-        <v>1055</v>
+        <v>102.5</v>
       </c>
       <c r="E24" t="n">
-        <v>682.833636</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>1739.2</v>
+        <v>118.220339</v>
       </c>
       <c r="G24" t="n">
-        <v>1826.16</v>
+        <v>124.13</v>
       </c>
       <c r="H24" t="n">
-        <v>703.3200000000001</v>
+        <v>94.86</v>
       </c>
       <c r="I24" t="n">
-        <v>984.03</v>
+        <v>102.18</v>
       </c>
       <c r="J24" t="n">
-        <v>73.09999999999999</v>
+        <v>21.1</v>
       </c>
       <c r="K24" t="n">
-        <v>-33.3</v>
+        <v>-7.5</v>
       </c>
       <c r="L24" t="n">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>250.805</v>
+        <v>141.64001431</v>
       </c>
       <c r="C25" t="n">
-        <v>486.675</v>
+        <v>203.6663265</v>
       </c>
       <c r="D25" t="n">
-        <v>325.5</v>
+        <v>158.5</v>
       </c>
       <c r="E25" t="n">
-        <v>243.5</v>
+        <v>137.514577</v>
       </c>
       <c r="F25" t="n">
-        <v>463.5</v>
+        <v>193.96793</v>
       </c>
       <c r="G25" t="n">
-        <v>486.68</v>
+        <v>203.67</v>
       </c>
       <c r="H25" t="n">
-        <v>250.81</v>
+        <v>141.64</v>
       </c>
       <c r="I25" t="n">
-        <v>309.77</v>
+        <v>157.15</v>
       </c>
       <c r="J25" t="n">
-        <v>49.5</v>
+        <v>28.5</v>
       </c>
       <c r="K25" t="n">
-        <v>-22.9</v>
+        <v>-10.6</v>
       </c>
       <c r="L25" t="n">
-        <v>2.16</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>153.80987013</v>
+        <v>2554.4</v>
       </c>
       <c r="C26" t="n">
-        <v>192.6356628</v>
+        <v>5922</v>
       </c>
       <c r="D26" t="n">
-        <v>166.5</v>
+        <v>3480</v>
       </c>
       <c r="E26" t="n">
-        <v>149.329971</v>
+        <v>2480</v>
       </c>
       <c r="F26" t="n">
-        <v>183.462536</v>
+        <v>5640</v>
       </c>
       <c r="G26" t="n">
-        <v>192.64</v>
+        <v>5922</v>
       </c>
       <c r="H26" t="n">
-        <v>153.81</v>
+        <v>2554.4</v>
       </c>
       <c r="I26" t="n">
-        <v>163.52</v>
+        <v>3396.3</v>
       </c>
       <c r="J26" t="n">
-        <v>15.7</v>
+        <v>70.2</v>
       </c>
       <c r="K26" t="n">
-        <v>-7.6</v>
+        <v>-26.6</v>
       </c>
       <c r="L26" t="n">
-        <v>2.06</v>
+        <v>2.64</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1611,86 +1611,86 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>106.605</v>
+        <v>158.105</v>
       </c>
       <c r="C27" t="n">
-        <v>192.15</v>
+        <v>369.6</v>
       </c>
       <c r="D27" t="n">
-        <v>136</v>
+        <v>217</v>
       </c>
       <c r="E27" t="n">
-        <v>103.5</v>
+        <v>153.5</v>
       </c>
       <c r="F27" t="n">
-        <v>183</v>
+        <v>352</v>
       </c>
       <c r="G27" t="n">
-        <v>192.15</v>
+        <v>369.6</v>
       </c>
       <c r="H27" t="n">
-        <v>106.61</v>
+        <v>158.11</v>
       </c>
       <c r="I27" t="n">
-        <v>127.99</v>
+        <v>210.98</v>
       </c>
       <c r="J27" t="n">
-        <v>41.3</v>
+        <v>70.3</v>
       </c>
       <c r="K27" t="n">
-        <v>-21.6</v>
+        <v>-27.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.91</v>
+        <v>2.59</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>122.04276875</v>
+        <v>3772.79998418</v>
       </c>
       <c r="C28" t="n">
-        <v>180.779025</v>
+        <v>11975.93743395</v>
       </c>
       <c r="D28" t="n">
-        <v>142.5</v>
+        <v>6055</v>
       </c>
       <c r="E28" t="n">
-        <v>118.488125</v>
+        <v>3662.912606</v>
       </c>
       <c r="F28" t="n">
-        <v>172.1705</v>
+        <v>11405.654699</v>
       </c>
       <c r="G28" t="n">
-        <v>180.78</v>
+        <v>11975.94</v>
       </c>
       <c r="H28" t="n">
-        <v>122.04</v>
+        <v>3772.8</v>
       </c>
       <c r="I28" t="n">
-        <v>136.73</v>
+        <v>5823.58</v>
       </c>
       <c r="J28" t="n">
-        <v>26.9</v>
+        <v>97.8</v>
       </c>
       <c r="K28" t="n">
-        <v>-14.4</v>
+        <v>-37.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.87</v>
+        <v>2.59</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1701,131 +1701,131 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>157.59</v>
+        <v>311.7109517600001</v>
       </c>
       <c r="C29" t="n">
-        <v>369.6</v>
+        <v>611.0052333000001</v>
       </c>
       <c r="D29" t="n">
-        <v>232</v>
+        <v>397.5</v>
       </c>
       <c r="E29" t="n">
-        <v>153</v>
+        <v>302.631992</v>
       </c>
       <c r="F29" t="n">
-        <v>352</v>
+        <v>581.909746</v>
       </c>
       <c r="G29" t="n">
-        <v>369.6</v>
+        <v>611.01</v>
       </c>
       <c r="H29" t="n">
-        <v>157.59</v>
+        <v>311.71</v>
       </c>
       <c r="I29" t="n">
-        <v>210.59</v>
+        <v>386.53</v>
       </c>
       <c r="J29" t="n">
-        <v>59.3</v>
+        <v>53.7</v>
       </c>
       <c r="K29" t="n">
-        <v>-32.1</v>
+        <v>-21.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>2.49</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>68.90700000000001</v>
+        <v>387.66964797</v>
       </c>
       <c r="C30" t="n">
-        <v>150.675</v>
+        <v>835.8000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>97.8</v>
+        <v>519</v>
       </c>
       <c r="E30" t="n">
-        <v>66.90000000000001</v>
+        <v>376.378299</v>
       </c>
       <c r="F30" t="n">
-        <v>143.5</v>
+        <v>796</v>
       </c>
       <c r="G30" t="n">
-        <v>150.68</v>
+        <v>835.8</v>
       </c>
       <c r="H30" t="n">
-        <v>68.91</v>
+        <v>387.67</v>
       </c>
       <c r="I30" t="n">
-        <v>89.34999999999999</v>
+        <v>499.7</v>
       </c>
       <c r="J30" t="n">
-        <v>54.1</v>
+        <v>61</v>
       </c>
       <c r="K30" t="n">
-        <v>-29.5</v>
+        <v>-25.3</v>
       </c>
       <c r="L30" t="n">
-        <v>1.83</v>
+        <v>2.41</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>103</v>
+        <v>691.49811788</v>
       </c>
       <c r="C31" t="n">
-        <v>156.975</v>
+        <v>1764</v>
       </c>
       <c r="D31" t="n">
-        <v>122.5</v>
+        <v>1015</v>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>671.357396</v>
       </c>
       <c r="F31" t="n">
-        <v>149.5</v>
+        <v>1680</v>
       </c>
       <c r="G31" t="n">
-        <v>156.97</v>
+        <v>1764</v>
       </c>
       <c r="H31" t="n">
-        <v>103</v>
+        <v>691.5</v>
       </c>
       <c r="I31" t="n">
-        <v>116.49</v>
+        <v>959.62</v>
       </c>
       <c r="J31" t="n">
-        <v>28.1</v>
+        <v>73.8</v>
       </c>
       <c r="K31" t="n">
-        <v>-15.9</v>
+        <v>-31.9</v>
       </c>
       <c r="L31" t="n">
-        <v>1.77</v>
+        <v>2.32</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -1836,41 +1836,41 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>187.54150699</v>
+        <v>606.49914566</v>
       </c>
       <c r="C32" t="n">
-        <v>320.16794775</v>
+        <v>1647.3453759</v>
       </c>
       <c r="D32" t="n">
-        <v>237.5</v>
+        <v>927</v>
       </c>
       <c r="E32" t="n">
-        <v>182.079133</v>
+        <v>588.834122</v>
       </c>
       <c r="F32" t="n">
-        <v>304.921855</v>
+        <v>1568.900358</v>
       </c>
       <c r="G32" t="n">
-        <v>320.17</v>
+        <v>1647.35</v>
       </c>
       <c r="H32" t="n">
-        <v>187.54</v>
+        <v>606.5</v>
       </c>
       <c r="I32" t="n">
-        <v>220.7</v>
+        <v>866.71</v>
       </c>
       <c r="J32" t="n">
-        <v>34.8</v>
+        <v>77.7</v>
       </c>
       <c r="K32" t="n">
-        <v>-21</v>
+        <v>-34.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -1881,86 +1881,86 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>183.34</v>
+        <v>842.8097436100001</v>
       </c>
       <c r="C33" t="n">
-        <v>282.975</v>
+        <v>1651.86</v>
       </c>
       <c r="D33" t="n">
-        <v>221.5</v>
+        <v>1095</v>
       </c>
       <c r="E33" t="n">
-        <v>178</v>
+        <v>818.261887</v>
       </c>
       <c r="F33" t="n">
-        <v>269.5</v>
+        <v>1573.2</v>
       </c>
       <c r="G33" t="n">
-        <v>282.98</v>
+        <v>1651.86</v>
       </c>
       <c r="H33" t="n">
-        <v>183.34</v>
+        <v>842.8099999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>208.25</v>
+        <v>1045.07</v>
       </c>
       <c r="J33" t="n">
-        <v>27.8</v>
+        <v>50.9</v>
       </c>
       <c r="K33" t="n">
-        <v>-17.2</v>
+        <v>-23</v>
       </c>
       <c r="L33" t="n">
-        <v>1.61</v>
+        <v>2.21</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>126.175</v>
+        <v>684.3489290799999</v>
       </c>
       <c r="C34" t="n">
-        <v>208.95</v>
+        <v>3149.8512822</v>
       </c>
       <c r="D34" t="n">
-        <v>158</v>
+        <v>1480</v>
       </c>
       <c r="E34" t="n">
-        <v>122.5</v>
+        <v>664.416436</v>
       </c>
       <c r="F34" t="n">
-        <v>199</v>
+        <v>2999.858364</v>
       </c>
       <c r="G34" t="n">
-        <v>208.95</v>
+        <v>3149.85</v>
       </c>
       <c r="H34" t="n">
-        <v>126.17</v>
+        <v>684.35</v>
       </c>
       <c r="I34" t="n">
-        <v>146.87</v>
+        <v>1300.72</v>
       </c>
       <c r="J34" t="n">
-        <v>32.2</v>
+        <v>112.8</v>
       </c>
       <c r="K34" t="n">
-        <v>-20.1</v>
+        <v>-53.8</v>
       </c>
       <c r="L34" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -1971,86 +1971,86 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>842.8097436100001</v>
+        <v>127.72</v>
       </c>
       <c r="C35" t="n">
-        <v>1651.86</v>
+        <v>223.125</v>
       </c>
       <c r="D35" t="n">
-        <v>1175</v>
+        <v>158.5</v>
       </c>
       <c r="E35" t="n">
-        <v>818.261887</v>
+        <v>124</v>
       </c>
       <c r="F35" t="n">
-        <v>1573.2</v>
+        <v>212.5</v>
       </c>
       <c r="G35" t="n">
-        <v>1651.86</v>
+        <v>223.12</v>
       </c>
       <c r="H35" t="n">
-        <v>842.8099999999999</v>
+        <v>127.72</v>
       </c>
       <c r="I35" t="n">
-        <v>1045.07</v>
+        <v>151.57</v>
       </c>
       <c r="J35" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="K35" t="n">
-        <v>-28.3</v>
+        <v>-19.4</v>
       </c>
       <c r="L35" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>294.13217351</v>
+        <v>265.23148797</v>
       </c>
       <c r="C36" t="n">
-        <v>556.1286129</v>
+        <v>441.0694491</v>
       </c>
       <c r="D36" t="n">
-        <v>403.5</v>
+        <v>325.5</v>
       </c>
       <c r="E36" t="n">
-        <v>285.565217</v>
+        <v>257.506299</v>
       </c>
       <c r="F36" t="n">
-        <v>529.646298</v>
+        <v>420.066142</v>
       </c>
       <c r="G36" t="n">
-        <v>556.13</v>
+        <v>441.07</v>
       </c>
       <c r="H36" t="n">
-        <v>294.13</v>
+        <v>265.23</v>
       </c>
       <c r="I36" t="n">
-        <v>359.63</v>
+        <v>309.19</v>
       </c>
       <c r="J36" t="n">
-        <v>37.8</v>
+        <v>35.5</v>
       </c>
       <c r="K36" t="n">
-        <v>-27.1</v>
+        <v>-18.5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.4</v>
+        <v>1.92</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2061,86 +2061,86 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>127.72</v>
+        <v>40.38815194</v>
       </c>
       <c r="C37" t="n">
-        <v>223.125</v>
+        <v>60.31306155000001</v>
       </c>
       <c r="D37" t="n">
-        <v>168</v>
+        <v>47.35</v>
       </c>
       <c r="E37" t="n">
-        <v>124</v>
+        <v>39.211798</v>
       </c>
       <c r="F37" t="n">
-        <v>212.5</v>
+        <v>57.441011</v>
       </c>
       <c r="G37" t="n">
-        <v>223.12</v>
+        <v>60.31</v>
       </c>
       <c r="H37" t="n">
-        <v>127.72</v>
+        <v>40.39</v>
       </c>
       <c r="I37" t="n">
-        <v>151.57</v>
+        <v>45.37</v>
       </c>
       <c r="J37" t="n">
-        <v>32.8</v>
+        <v>27.4</v>
       </c>
       <c r="K37" t="n">
-        <v>-24</v>
+        <v>-14.7</v>
       </c>
       <c r="L37" t="n">
-        <v>1.37</v>
+        <v>1.86</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>141.64001431</v>
+        <v>187.54150699</v>
       </c>
       <c r="C38" t="n">
-        <v>203.6663265</v>
+        <v>320.16794775</v>
       </c>
       <c r="D38" t="n">
-        <v>168.5</v>
+        <v>234</v>
       </c>
       <c r="E38" t="n">
-        <v>137.514577</v>
+        <v>182.079133</v>
       </c>
       <c r="F38" t="n">
-        <v>193.96793</v>
+        <v>304.921855</v>
       </c>
       <c r="G38" t="n">
-        <v>203.67</v>
+        <v>320.17</v>
       </c>
       <c r="H38" t="n">
-        <v>141.64</v>
+        <v>187.54</v>
       </c>
       <c r="I38" t="n">
-        <v>157.15</v>
+        <v>220.7</v>
       </c>
       <c r="J38" t="n">
-        <v>20.9</v>
+        <v>36.8</v>
       </c>
       <c r="K38" t="n">
-        <v>-15.9</v>
+        <v>-19.9</v>
       </c>
       <c r="L38" t="n">
-        <v>1.31</v>
+        <v>1.85</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2151,86 +2151,86 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>971.2900000000001</v>
+        <v>101.36665072</v>
       </c>
       <c r="C39" t="n">
-        <v>1680</v>
+        <v>122.8038357</v>
       </c>
       <c r="D39" t="n">
-        <v>1280</v>
+        <v>109</v>
       </c>
       <c r="E39" t="n">
-        <v>943</v>
+        <v>98.414224</v>
       </c>
       <c r="F39" t="n">
-        <v>1600</v>
+        <v>116.956034</v>
       </c>
       <c r="G39" t="n">
-        <v>1680</v>
+        <v>122.8</v>
       </c>
       <c r="H39" t="n">
-        <v>971.29</v>
+        <v>101.37</v>
       </c>
       <c r="I39" t="n">
-        <v>1148.47</v>
+        <v>106.73</v>
       </c>
       <c r="J39" t="n">
-        <v>31.2</v>
+        <v>12.7</v>
       </c>
       <c r="K39" t="n">
-        <v>-24.1</v>
+        <v>-7</v>
       </c>
       <c r="L39" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>98.57100000000001</v>
+        <v>703.31864508</v>
       </c>
       <c r="C40" t="n">
-        <v>153.3</v>
+        <v>1826.16</v>
       </c>
       <c r="D40" t="n">
-        <v>122.5</v>
+        <v>1120</v>
       </c>
       <c r="E40" t="n">
-        <v>95.7</v>
+        <v>682.833636</v>
       </c>
       <c r="F40" t="n">
-        <v>146</v>
+        <v>1739.2</v>
       </c>
       <c r="G40" t="n">
-        <v>153.3</v>
+        <v>1826.16</v>
       </c>
       <c r="H40" t="n">
-        <v>98.56999999999999</v>
+        <v>703.3200000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>112.25</v>
+        <v>984.03</v>
       </c>
       <c r="J40" t="n">
-        <v>25.1</v>
+        <v>63.1</v>
       </c>
       <c r="K40" t="n">
-        <v>-19.5</v>
+        <v>-37.2</v>
       </c>
       <c r="L40" t="n">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2241,356 +2241,356 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>947.82327722</v>
+        <v>1142.476</v>
       </c>
       <c r="C41" t="n">
-        <v>2910.13596825</v>
+        <v>2700.13103115</v>
       </c>
       <c r="D41" t="n">
-        <v>1820</v>
+        <v>1740</v>
       </c>
       <c r="E41" t="n">
-        <v>920.216774</v>
+        <v>1109.2</v>
       </c>
       <c r="F41" t="n">
-        <v>2771.558065</v>
+        <v>2571.553363</v>
       </c>
       <c r="G41" t="n">
-        <v>2910.14</v>
+        <v>2700.13</v>
       </c>
       <c r="H41" t="n">
-        <v>947.8200000000001</v>
+        <v>1142.48</v>
       </c>
       <c r="I41" t="n">
-        <v>1438.4</v>
+        <v>1531.89</v>
       </c>
       <c r="J41" t="n">
-        <v>59.9</v>
+        <v>55.2</v>
       </c>
       <c r="K41" t="n">
-        <v>-47.9</v>
+        <v>-34.3</v>
       </c>
       <c r="L41" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>606.49914566</v>
+        <v>38.45982817</v>
       </c>
       <c r="C42" t="n">
-        <v>1647.3453759</v>
+        <v>90.1091205</v>
       </c>
       <c r="D42" t="n">
-        <v>1075</v>
+        <v>58.5</v>
       </c>
       <c r="E42" t="n">
-        <v>588.834122</v>
+        <v>37.339639</v>
       </c>
       <c r="F42" t="n">
-        <v>1568.900358</v>
+        <v>85.81820999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>1647.35</v>
+        <v>90.11</v>
       </c>
       <c r="H42" t="n">
-        <v>606.5</v>
+        <v>38.46</v>
       </c>
       <c r="I42" t="n">
-        <v>866.71</v>
+        <v>51.37</v>
       </c>
       <c r="J42" t="n">
-        <v>53.2</v>
+        <v>54</v>
       </c>
       <c r="K42" t="n">
-        <v>-43.6</v>
+        <v>-34.3</v>
       </c>
       <c r="L42" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>101.64987909</v>
+        <v>252.15184757</v>
       </c>
       <c r="C43" t="n">
-        <v>278.03973015</v>
+        <v>541.8000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>181</v>
+        <v>366.5</v>
       </c>
       <c r="E43" t="n">
-        <v>98.68920300000001</v>
+        <v>244.807619</v>
       </c>
       <c r="F43" t="n">
-        <v>264.799743</v>
+        <v>516</v>
       </c>
       <c r="G43" t="n">
-        <v>278.04</v>
+        <v>541.8</v>
       </c>
       <c r="H43" t="n">
-        <v>101.65</v>
+        <v>252.15</v>
       </c>
       <c r="I43" t="n">
-        <v>145.75</v>
+        <v>324.56</v>
       </c>
       <c r="J43" t="n">
-        <v>53.6</v>
+        <v>47.8</v>
       </c>
       <c r="K43" t="n">
-        <v>-43.8</v>
+        <v>-31.2</v>
       </c>
       <c r="L43" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>309.20523574</v>
+        <v>143.685</v>
       </c>
       <c r="C44" t="n">
-        <v>611.0052333000001</v>
+        <v>275.1</v>
       </c>
       <c r="D44" t="n">
-        <v>448.5</v>
+        <v>196.5</v>
       </c>
       <c r="E44" t="n">
-        <v>300.199258</v>
+        <v>139.5</v>
       </c>
       <c r="F44" t="n">
-        <v>581.909746</v>
+        <v>262</v>
       </c>
       <c r="G44" t="n">
-        <v>611.01</v>
+        <v>275.1</v>
       </c>
       <c r="H44" t="n">
-        <v>309.21</v>
+        <v>143.69</v>
       </c>
       <c r="I44" t="n">
-        <v>384.66</v>
+        <v>176.54</v>
       </c>
       <c r="J44" t="n">
-        <v>36.2</v>
+        <v>40</v>
       </c>
       <c r="K44" t="n">
-        <v>-31.1</v>
+        <v>-26.9</v>
       </c>
       <c r="L44" t="n">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>655.08</v>
+        <v>130.8919571</v>
       </c>
       <c r="C45" t="n">
-        <v>3470.25</v>
+        <v>148.5964515</v>
       </c>
       <c r="D45" t="n">
-        <v>2005</v>
+        <v>138</v>
       </c>
       <c r="E45" t="n">
-        <v>636</v>
+        <v>127.07957</v>
       </c>
       <c r="F45" t="n">
-        <v>3305</v>
+        <v>141.52043</v>
       </c>
       <c r="G45" t="n">
-        <v>3470.25</v>
+        <v>148.6</v>
       </c>
       <c r="H45" t="n">
-        <v>655.08</v>
+        <v>130.89</v>
       </c>
       <c r="I45" t="n">
-        <v>1358.87</v>
+        <v>135.32</v>
       </c>
       <c r="J45" t="n">
-        <v>73.09999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="K45" t="n">
-        <v>-67.3</v>
+        <v>-5.2</v>
       </c>
       <c r="L45" t="n">
-        <v>1.09</v>
+        <v>1.49</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>657.8355847500001</v>
+        <v>2194.20362855</v>
       </c>
       <c r="C46" t="n">
-        <v>833.75727225</v>
+        <v>6219.16666665</v>
       </c>
       <c r="D46" t="n">
-        <v>744</v>
+        <v>3835</v>
       </c>
       <c r="E46" t="n">
-        <v>638.675325</v>
+        <v>2130.294785</v>
       </c>
       <c r="F46" t="n">
-        <v>794.054545</v>
+        <v>5923.015873</v>
       </c>
       <c r="G46" t="n">
-        <v>833.76</v>
+        <v>6219.17</v>
       </c>
       <c r="H46" t="n">
-        <v>657.84</v>
+        <v>2194.2</v>
       </c>
       <c r="I46" t="n">
-        <v>701.8200000000001</v>
+        <v>3200.44</v>
       </c>
       <c r="J46" t="n">
-        <v>12.1</v>
+        <v>62.2</v>
       </c>
       <c r="K46" t="n">
-        <v>-11.6</v>
+        <v>-42.8</v>
       </c>
       <c r="L46" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2554.4</v>
+        <v>103.12004547</v>
       </c>
       <c r="C47" t="n">
-        <v>5922</v>
+        <v>122.22362355</v>
       </c>
       <c r="D47" t="n">
-        <v>4210</v>
+        <v>111</v>
       </c>
       <c r="E47" t="n">
-        <v>2480</v>
+        <v>100.116549</v>
       </c>
       <c r="F47" t="n">
-        <v>5640</v>
+        <v>116.403451</v>
       </c>
       <c r="G47" t="n">
-        <v>5922</v>
+        <v>122.22</v>
       </c>
       <c r="H47" t="n">
-        <v>2554.4</v>
+        <v>103.12</v>
       </c>
       <c r="I47" t="n">
-        <v>3396.3</v>
+        <v>107.9</v>
       </c>
       <c r="J47" t="n">
-        <v>40.7</v>
+        <v>10.1</v>
       </c>
       <c r="K47" t="n">
-        <v>-39.3</v>
+        <v>-7.1</v>
       </c>
       <c r="L47" t="n">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>181.795</v>
+        <v>971.2900000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>262.5</v>
+        <v>1680</v>
       </c>
       <c r="D48" t="n">
-        <v>221.5</v>
+        <v>1265</v>
       </c>
       <c r="E48" t="n">
-        <v>176.5</v>
+        <v>943</v>
       </c>
       <c r="F48" t="n">
-        <v>250</v>
+        <v>1600</v>
       </c>
       <c r="G48" t="n">
-        <v>262.5</v>
+        <v>1680</v>
       </c>
       <c r="H48" t="n">
-        <v>181.8</v>
+        <v>971.29</v>
       </c>
       <c r="I48" t="n">
-        <v>201.97</v>
+        <v>1148.47</v>
       </c>
       <c r="J48" t="n">
-        <v>18.5</v>
+        <v>32.8</v>
       </c>
       <c r="K48" t="n">
-        <v>-17.9</v>
+        <v>-23.2</v>
       </c>
       <c r="L48" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -2601,131 +2601,131 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3502</v>
+        <v>126.175</v>
       </c>
       <c r="C49" t="n">
-        <v>12064.5</v>
+        <v>208.95</v>
       </c>
       <c r="D49" t="n">
-        <v>7765</v>
+        <v>161</v>
       </c>
       <c r="E49" t="n">
-        <v>3400</v>
+        <v>122.5</v>
       </c>
       <c r="F49" t="n">
-        <v>11490</v>
+        <v>199</v>
       </c>
       <c r="G49" t="n">
-        <v>12064.5</v>
+        <v>208.95</v>
       </c>
       <c r="H49" t="n">
-        <v>3502</v>
+        <v>126.17</v>
       </c>
       <c r="I49" t="n">
-        <v>5642.62</v>
+        <v>146.87</v>
       </c>
       <c r="J49" t="n">
-        <v>55.4</v>
+        <v>29.8</v>
       </c>
       <c r="K49" t="n">
-        <v>-54.9</v>
+        <v>-21.6</v>
       </c>
       <c r="L49" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>115.875</v>
+        <v>86.31399999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>170.1</v>
+        <v>245.175</v>
       </c>
       <c r="D50" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E50" t="n">
-        <v>112.5</v>
+        <v>83.8</v>
       </c>
       <c r="F50" t="n">
-        <v>162</v>
+        <v>233.5</v>
       </c>
       <c r="G50" t="n">
-        <v>170.1</v>
+        <v>245.18</v>
       </c>
       <c r="H50" t="n">
-        <v>115.88</v>
+        <v>86.31</v>
       </c>
       <c r="I50" t="n">
-        <v>129.43</v>
+        <v>126.03</v>
       </c>
       <c r="J50" t="n">
-        <v>19</v>
+        <v>58.2</v>
       </c>
       <c r="K50" t="n">
-        <v>-19</v>
+        <v>-44.3</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1050.25820583</v>
+        <v>245.43847958</v>
       </c>
       <c r="C51" t="n">
-        <v>2700.13103115</v>
+        <v>1281</v>
       </c>
       <c r="D51" t="n">
-        <v>1880</v>
+        <v>699</v>
       </c>
       <c r="E51" t="n">
-        <v>1019.668161</v>
+        <v>238.289786</v>
       </c>
       <c r="F51" t="n">
-        <v>2571.553363</v>
+        <v>1220</v>
       </c>
       <c r="G51" t="n">
-        <v>2700.13</v>
+        <v>1281</v>
       </c>
       <c r="H51" t="n">
-        <v>1050.26</v>
+        <v>245.44</v>
       </c>
       <c r="I51" t="n">
-        <v>1462.73</v>
+        <v>504.33</v>
       </c>
       <c r="J51" t="n">
-        <v>43.6</v>
+        <v>83.3</v>
       </c>
       <c r="K51" t="n">
-        <v>-44.1</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>0.99</v>
+        <v>1.28</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -2736,131 +2736,131 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>691.49811788</v>
+        <v>156.56</v>
       </c>
       <c r="C52" t="n">
-        <v>1764</v>
+        <v>213.3067608</v>
       </c>
       <c r="D52" t="n">
-        <v>1230</v>
+        <v>181.5</v>
       </c>
       <c r="E52" t="n">
-        <v>671.357396</v>
+        <v>152</v>
       </c>
       <c r="F52" t="n">
-        <v>1680</v>
+        <v>203.149296</v>
       </c>
       <c r="G52" t="n">
-        <v>1764</v>
+        <v>213.31</v>
       </c>
       <c r="H52" t="n">
-        <v>691.5</v>
+        <v>156.56</v>
       </c>
       <c r="I52" t="n">
-        <v>959.62</v>
+        <v>170.75</v>
       </c>
       <c r="J52" t="n">
-        <v>43.4</v>
+        <v>17.5</v>
       </c>
       <c r="K52" t="n">
-        <v>-43.8</v>
+        <v>-13.7</v>
       </c>
       <c r="L52" t="n">
-        <v>0.99</v>
+        <v>1.28</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>40.38815194</v>
+        <v>104.545</v>
       </c>
       <c r="C53" t="n">
-        <v>60.31306155000001</v>
+        <v>512.4</v>
       </c>
       <c r="D53" t="n">
-        <v>50.4</v>
+        <v>288</v>
       </c>
       <c r="E53" t="n">
-        <v>39.211798</v>
+        <v>101.5</v>
       </c>
       <c r="F53" t="n">
-        <v>57.441011</v>
+        <v>488</v>
       </c>
       <c r="G53" t="n">
-        <v>60.31</v>
+        <v>512.4</v>
       </c>
       <c r="H53" t="n">
-        <v>40.39</v>
+        <v>104.55</v>
       </c>
       <c r="I53" t="n">
-        <v>45.37</v>
+        <v>206.51</v>
       </c>
       <c r="J53" t="n">
-        <v>19.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-19.9</v>
+        <v>-63.7</v>
       </c>
       <c r="L53" t="n">
-        <v>0.99</v>
+        <v>1.22</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>387.66964797</v>
+        <v>947.82327722</v>
       </c>
       <c r="C54" t="n">
-        <v>835.8000000000001</v>
+        <v>2910.13596825</v>
       </c>
       <c r="D54" t="n">
-        <v>616</v>
+        <v>1850</v>
       </c>
       <c r="E54" t="n">
-        <v>376.378299</v>
+        <v>920.216774</v>
       </c>
       <c r="F54" t="n">
-        <v>796</v>
+        <v>2771.558065</v>
       </c>
       <c r="G54" t="n">
-        <v>835.8</v>
+        <v>2910.14</v>
       </c>
       <c r="H54" t="n">
-        <v>387.67</v>
+        <v>947.8200000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>499.7</v>
+        <v>1438.4</v>
       </c>
       <c r="J54" t="n">
-        <v>35.7</v>
+        <v>57.3</v>
       </c>
       <c r="K54" t="n">
-        <v>-37.1</v>
+        <v>-48.8</v>
       </c>
       <c r="L54" t="n">
-        <v>0.96</v>
+        <v>1.18</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -2871,41 +2871,41 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2199.05</v>
+        <v>450.62400914</v>
       </c>
       <c r="C55" t="n">
-        <v>5628</v>
+        <v>2016</v>
       </c>
       <c r="D55" t="n">
-        <v>3950</v>
+        <v>1170</v>
       </c>
       <c r="E55" t="n">
-        <v>2135</v>
+        <v>437.499038</v>
       </c>
       <c r="F55" t="n">
-        <v>5360</v>
+        <v>1920</v>
       </c>
       <c r="G55" t="n">
-        <v>5628</v>
+        <v>2016</v>
       </c>
       <c r="H55" t="n">
-        <v>2199.05</v>
+        <v>450.62</v>
       </c>
       <c r="I55" t="n">
-        <v>3056.29</v>
+        <v>841.97</v>
       </c>
       <c r="J55" t="n">
-        <v>42.5</v>
+        <v>72.3</v>
       </c>
       <c r="K55" t="n">
-        <v>-44.3</v>
+        <v>-61.5</v>
       </c>
       <c r="L55" t="n">
-        <v>0.96</v>
+        <v>1.18</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -2916,41 +2916,41 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>136.92326733</v>
+        <v>113.85245492</v>
       </c>
       <c r="C56" t="n">
-        <v>209.37295785</v>
+        <v>196.35</v>
       </c>
       <c r="D56" t="n">
-        <v>174.5</v>
+        <v>152</v>
       </c>
       <c r="E56" t="n">
-        <v>132.935211</v>
+        <v>110.536364</v>
       </c>
       <c r="F56" t="n">
-        <v>199.402817</v>
+        <v>187</v>
       </c>
       <c r="G56" t="n">
-        <v>209.37</v>
+        <v>196.35</v>
       </c>
       <c r="H56" t="n">
-        <v>136.92</v>
+        <v>113.85</v>
       </c>
       <c r="I56" t="n">
-        <v>155.04</v>
+        <v>134.48</v>
       </c>
       <c r="J56" t="n">
-        <v>20</v>
+        <v>29.2</v>
       </c>
       <c r="K56" t="n">
-        <v>-21.5</v>
+        <v>-25.1</v>
       </c>
       <c r="L56" t="n">
-        <v>0.93</v>
+        <v>1.16</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -2961,41 +2961,41 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>276.555</v>
+        <v>7689.53418819</v>
       </c>
       <c r="C57" t="n">
-        <v>459.9</v>
+        <v>18889.24232475</v>
       </c>
       <c r="D57" t="n">
-        <v>373.5</v>
+        <v>12950</v>
       </c>
       <c r="E57" t="n">
-        <v>268.5</v>
+        <v>7465.567173</v>
       </c>
       <c r="F57" t="n">
-        <v>438</v>
+        <v>17989.754595</v>
       </c>
       <c r="G57" t="n">
-        <v>459.9</v>
+        <v>18889.24</v>
       </c>
       <c r="H57" t="n">
-        <v>276.56</v>
+        <v>7689.53</v>
       </c>
       <c r="I57" t="n">
-        <v>322.39</v>
+        <v>10489.46</v>
       </c>
       <c r="J57" t="n">
-        <v>23.1</v>
+        <v>45.9</v>
       </c>
       <c r="K57" t="n">
-        <v>-26</v>
+        <v>-40.6</v>
       </c>
       <c r="L57" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -3006,41 +3006,41 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2194.20362855</v>
+        <v>451.14</v>
       </c>
       <c r="C58" t="n">
-        <v>6219.16666665</v>
+        <v>1018.5</v>
       </c>
       <c r="D58" t="n">
-        <v>4340</v>
+        <v>718</v>
       </c>
       <c r="E58" t="n">
-        <v>2130.294785</v>
+        <v>438</v>
       </c>
       <c r="F58" t="n">
-        <v>5923.015873</v>
+        <v>970</v>
       </c>
       <c r="G58" t="n">
-        <v>6219.17</v>
+        <v>1018.5</v>
       </c>
       <c r="H58" t="n">
-        <v>2194.2</v>
+        <v>451.14</v>
       </c>
       <c r="I58" t="n">
-        <v>3200.44</v>
+        <v>592.98</v>
       </c>
       <c r="J58" t="n">
-        <v>43.3</v>
+        <v>41.9</v>
       </c>
       <c r="K58" t="n">
-        <v>-49.4</v>
+        <v>-37.2</v>
       </c>
       <c r="L58" t="n">
-        <v>0.88</v>
+        <v>1.13</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -3051,41 +3051,41 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>143.685</v>
+        <v>243.62129178</v>
       </c>
       <c r="C59" t="n">
-        <v>275.1</v>
+        <v>642.6</v>
       </c>
       <c r="D59" t="n">
-        <v>213.5</v>
+        <v>432</v>
       </c>
       <c r="E59" t="n">
-        <v>139.5</v>
+        <v>236.525526</v>
       </c>
       <c r="F59" t="n">
-        <v>262</v>
+        <v>612</v>
       </c>
       <c r="G59" t="n">
-        <v>275.1</v>
+        <v>642.6</v>
       </c>
       <c r="H59" t="n">
-        <v>143.69</v>
+        <v>243.62</v>
       </c>
       <c r="I59" t="n">
-        <v>176.54</v>
+        <v>343.37</v>
       </c>
       <c r="J59" t="n">
-        <v>28.9</v>
+        <v>48.8</v>
       </c>
       <c r="K59" t="n">
-        <v>-32.7</v>
+        <v>-43.6</v>
       </c>
       <c r="L59" t="n">
-        <v>0.88</v>
+        <v>1.12</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -3096,41 +3096,41 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7479.819619880001</v>
+        <v>129.65536794</v>
       </c>
       <c r="C60" t="n">
-        <v>18889.24232475</v>
+        <v>347.47028925</v>
       </c>
       <c r="D60" t="n">
-        <v>13665</v>
+        <v>234.5</v>
       </c>
       <c r="E60" t="n">
-        <v>7261.960796</v>
+        <v>125.878998</v>
       </c>
       <c r="F60" t="n">
-        <v>17989.754595</v>
+        <v>330.924085</v>
       </c>
       <c r="G60" t="n">
-        <v>18889.24</v>
+        <v>347.47</v>
       </c>
       <c r="H60" t="n">
-        <v>7479.82</v>
+        <v>129.66</v>
       </c>
       <c r="I60" t="n">
-        <v>10332.18</v>
+        <v>184.11</v>
       </c>
       <c r="J60" t="n">
-        <v>38.2</v>
+        <v>48.2</v>
       </c>
       <c r="K60" t="n">
-        <v>-45.3</v>
+        <v>-44.7</v>
       </c>
       <c r="L60" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -3141,41 +3141,41 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>252.15184757</v>
+        <v>1302.95</v>
       </c>
       <c r="C61" t="n">
-        <v>541.8000000000001</v>
+        <v>3160.5</v>
       </c>
       <c r="D61" t="n">
-        <v>410</v>
+        <v>2200</v>
       </c>
       <c r="E61" t="n">
-        <v>244.807619</v>
+        <v>1265</v>
       </c>
       <c r="F61" t="n">
-        <v>516</v>
+        <v>3010</v>
       </c>
       <c r="G61" t="n">
-        <v>541.8</v>
+        <v>3160.5</v>
       </c>
       <c r="H61" t="n">
-        <v>252.15</v>
+        <v>1302.95</v>
       </c>
       <c r="I61" t="n">
-        <v>324.56</v>
+        <v>1767.34</v>
       </c>
       <c r="J61" t="n">
-        <v>32.1</v>
+        <v>43.7</v>
       </c>
       <c r="K61" t="n">
-        <v>-38.5</v>
+        <v>-40.8</v>
       </c>
       <c r="L61" t="n">
-        <v>0.83</v>
+        <v>1.07</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -3186,86 +3186,86 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>30.8485</v>
+        <v>3293.32097618</v>
       </c>
       <c r="C62" t="n">
-        <v>37.3275</v>
+        <v>6000.22536855</v>
       </c>
       <c r="D62" t="n">
-        <v>34.45</v>
+        <v>4620</v>
       </c>
       <c r="E62" t="n">
-        <v>29.95</v>
+        <v>3197.399006</v>
       </c>
       <c r="F62" t="n">
-        <v>35.55</v>
+        <v>5714.500351</v>
       </c>
       <c r="G62" t="n">
-        <v>37.33</v>
+        <v>6000.23</v>
       </c>
       <c r="H62" t="n">
-        <v>30.85</v>
+        <v>3293.32</v>
       </c>
       <c r="I62" t="n">
-        <v>32.47</v>
+        <v>3970.05</v>
       </c>
       <c r="J62" t="n">
-        <v>8.4</v>
+        <v>29.9</v>
       </c>
       <c r="K62" t="n">
-        <v>-10.5</v>
+        <v>-28.7</v>
       </c>
       <c r="L62" t="n">
-        <v>0.8</v>
+        <v>1.04</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1302.95</v>
+        <v>101.64987909</v>
       </c>
       <c r="C63" t="n">
-        <v>3160.5</v>
+        <v>278.03973015</v>
       </c>
       <c r="D63" t="n">
-        <v>2350</v>
+        <v>190</v>
       </c>
       <c r="E63" t="n">
-        <v>1265</v>
+        <v>98.68920300000001</v>
       </c>
       <c r="F63" t="n">
-        <v>3010</v>
+        <v>264.799743</v>
       </c>
       <c r="G63" t="n">
-        <v>3160.5</v>
+        <v>278.04</v>
       </c>
       <c r="H63" t="n">
-        <v>1302.95</v>
+        <v>101.65</v>
       </c>
       <c r="I63" t="n">
-        <v>1767.34</v>
+        <v>145.75</v>
       </c>
       <c r="J63" t="n">
-        <v>34.5</v>
+        <v>46.3</v>
       </c>
       <c r="K63" t="n">
-        <v>-44.6</v>
+        <v>-46.5</v>
       </c>
       <c r="L63" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -3276,41 +3276,41 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>39.7065</v>
+        <v>370.8</v>
       </c>
       <c r="C64" t="n">
-        <v>93.03</v>
+        <v>1564.5</v>
       </c>
       <c r="D64" t="n">
-        <v>69.8</v>
+        <v>975</v>
       </c>
       <c r="E64" t="n">
-        <v>38.55</v>
+        <v>360</v>
       </c>
       <c r="F64" t="n">
-        <v>88.59999999999999</v>
+        <v>1490</v>
       </c>
       <c r="G64" t="n">
-        <v>93.03</v>
+        <v>1564.5</v>
       </c>
       <c r="H64" t="n">
-        <v>39.71</v>
+        <v>370.8</v>
       </c>
       <c r="I64" t="n">
-        <v>53.04</v>
+        <v>669.23</v>
       </c>
       <c r="J64" t="n">
-        <v>33.3</v>
+        <v>60.5</v>
       </c>
       <c r="K64" t="n">
-        <v>-43.1</v>
+        <v>-62</v>
       </c>
       <c r="L64" t="n">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -3321,41 +3321,41 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>86.31399999999999</v>
+        <v>1464.15186701</v>
       </c>
       <c r="C65" t="n">
-        <v>245.175</v>
+        <v>5187.505272599999</v>
       </c>
       <c r="D65" t="n">
-        <v>176.5</v>
+        <v>3370</v>
       </c>
       <c r="E65" t="n">
-        <v>83.8</v>
+        <v>1421.506667</v>
       </c>
       <c r="F65" t="n">
-        <v>233.5</v>
+        <v>4940.481212</v>
       </c>
       <c r="G65" t="n">
-        <v>245.18</v>
+        <v>5187.51</v>
       </c>
       <c r="H65" t="n">
-        <v>86.31</v>
+        <v>1464.15</v>
       </c>
       <c r="I65" t="n">
-        <v>126.03</v>
+        <v>2394.99</v>
       </c>
       <c r="J65" t="n">
-        <v>38.9</v>
+        <v>53.9</v>
       </c>
       <c r="K65" t="n">
-        <v>-51.1</v>
+        <v>-56.6</v>
       </c>
       <c r="L65" t="n">
-        <v>0.76</v>
+        <v>0.95</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -3366,86 +3366,86 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>370.8</v>
+        <v>113.3</v>
       </c>
       <c r="C66" t="n">
-        <v>1564.5</v>
+        <v>130.2</v>
       </c>
       <c r="D66" t="n">
-        <v>1050</v>
+        <v>122</v>
       </c>
       <c r="E66" t="n">
-        <v>360</v>
+        <v>110</v>
       </c>
       <c r="F66" t="n">
-        <v>1490</v>
+        <v>124</v>
       </c>
       <c r="G66" t="n">
-        <v>1564.5</v>
+        <v>130.2</v>
       </c>
       <c r="H66" t="n">
-        <v>370.8</v>
+        <v>113.3</v>
       </c>
       <c r="I66" t="n">
-        <v>669.23</v>
+        <v>117.53</v>
       </c>
       <c r="J66" t="n">
-        <v>49</v>
+        <v>6.7</v>
       </c>
       <c r="K66" t="n">
-        <v>-64.7</v>
+        <v>-7.1</v>
       </c>
       <c r="L66" t="n">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟡 接近門檻(&lt;5% 距離)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>31.55249573</v>
+        <v>136.92326733</v>
       </c>
       <c r="C67" t="n">
-        <v>45.6715329</v>
+        <v>209.37295785</v>
       </c>
       <c r="D67" t="n">
-        <v>39.6</v>
+        <v>174.5</v>
       </c>
       <c r="E67" t="n">
-        <v>30.633491</v>
+        <v>132.935211</v>
       </c>
       <c r="F67" t="n">
-        <v>43.496698</v>
+        <v>199.402817</v>
       </c>
       <c r="G67" t="n">
-        <v>45.67</v>
+        <v>209.37</v>
       </c>
       <c r="H67" t="n">
-        <v>31.55</v>
+        <v>136.92</v>
       </c>
       <c r="I67" t="n">
-        <v>35.08</v>
+        <v>155.04</v>
       </c>
       <c r="J67" t="n">
-        <v>15.3</v>
+        <v>20</v>
       </c>
       <c r="K67" t="n">
-        <v>-20.3</v>
+        <v>-21.5</v>
       </c>
       <c r="L67" t="n">
-        <v>0.75</v>
+        <v>0.93</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -3456,131 +3456,131 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>113.3</v>
+        <v>1122.7</v>
       </c>
       <c r="C68" t="n">
-        <v>130.2</v>
+        <v>2966.25</v>
       </c>
       <c r="D68" t="n">
-        <v>123</v>
+        <v>2090</v>
       </c>
       <c r="E68" t="n">
-        <v>110</v>
+        <v>1090</v>
       </c>
       <c r="F68" t="n">
-        <v>124</v>
+        <v>2825</v>
       </c>
       <c r="G68" t="n">
-        <v>130.2</v>
+        <v>2966.25</v>
       </c>
       <c r="H68" t="n">
-        <v>113.3</v>
+        <v>1122.7</v>
       </c>
       <c r="I68" t="n">
-        <v>117.53</v>
+        <v>1583.59</v>
       </c>
       <c r="J68" t="n">
-        <v>5.9</v>
+        <v>41.9</v>
       </c>
       <c r="K68" t="n">
-        <v>-7.9</v>
+        <v>-46.3</v>
       </c>
       <c r="L68" t="n">
-        <v>0.74</v>
+        <v>0.91</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>🟡 接近門檻(&lt;5% 距離)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>209.605</v>
+        <v>2199.05</v>
       </c>
       <c r="C69" t="n">
-        <v>262.5</v>
+        <v>5628</v>
       </c>
       <c r="D69" t="n">
-        <v>241</v>
+        <v>4010</v>
       </c>
       <c r="E69" t="n">
-        <v>203.5</v>
+        <v>2135</v>
       </c>
       <c r="F69" t="n">
-        <v>250</v>
+        <v>5360</v>
       </c>
       <c r="G69" t="n">
-        <v>262.5</v>
+        <v>5628</v>
       </c>
       <c r="H69" t="n">
-        <v>209.61</v>
+        <v>2199.05</v>
       </c>
       <c r="I69" t="n">
-        <v>222.83</v>
+        <v>3056.29</v>
       </c>
       <c r="J69" t="n">
-        <v>8.9</v>
+        <v>40.3</v>
       </c>
       <c r="K69" t="n">
-        <v>-13</v>
+        <v>-45.2</v>
       </c>
       <c r="L69" t="n">
-        <v>0.68</v>
+        <v>0.89</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1071.2</v>
+        <v>41.09844509000001</v>
       </c>
       <c r="C70" t="n">
-        <v>1743</v>
+        <v>86.52000000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>1480</v>
+        <v>65.5</v>
       </c>
       <c r="E70" t="n">
-        <v>1040</v>
+        <v>39.901403</v>
       </c>
       <c r="F70" t="n">
-        <v>1660</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>1743</v>
+        <v>86.52</v>
       </c>
       <c r="H70" t="n">
-        <v>1071.2</v>
+        <v>41.1</v>
       </c>
       <c r="I70" t="n">
-        <v>1239.15</v>
+        <v>52.45</v>
       </c>
       <c r="J70" t="n">
-        <v>17.8</v>
+        <v>32.1</v>
       </c>
       <c r="K70" t="n">
-        <v>-27.6</v>
+        <v>-37.3</v>
       </c>
       <c r="L70" t="n">
-        <v>0.64</v>
+        <v>0.86</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -3591,41 +3591,41 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>63.63683299</v>
+        <v>1071.2</v>
       </c>
       <c r="C71" t="n">
-        <v>103.53</v>
+        <v>1743</v>
       </c>
       <c r="D71" t="n">
-        <v>88.5</v>
+        <v>1435</v>
       </c>
       <c r="E71" t="n">
-        <v>61.783333</v>
+        <v>1040</v>
       </c>
       <c r="F71" t="n">
-        <v>98.59999999999999</v>
+        <v>1660</v>
       </c>
       <c r="G71" t="n">
-        <v>103.53</v>
+        <v>1743</v>
       </c>
       <c r="H71" t="n">
-        <v>63.64</v>
+        <v>1071.2</v>
       </c>
       <c r="I71" t="n">
-        <v>73.61</v>
+        <v>1239.15</v>
       </c>
       <c r="J71" t="n">
-        <v>17</v>
+        <v>21.5</v>
       </c>
       <c r="K71" t="n">
-        <v>-28.1</v>
+        <v>-25.4</v>
       </c>
       <c r="L71" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -3636,86 +3636,86 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>245.43847958</v>
+        <v>115.875</v>
       </c>
       <c r="C72" t="n">
-        <v>1281</v>
+        <v>170.1</v>
       </c>
       <c r="D72" t="n">
-        <v>900</v>
+        <v>145.5</v>
       </c>
       <c r="E72" t="n">
-        <v>238.289786</v>
+        <v>112.5</v>
       </c>
       <c r="F72" t="n">
-        <v>1220</v>
+        <v>162</v>
       </c>
       <c r="G72" t="n">
-        <v>1281</v>
+        <v>170.1</v>
       </c>
       <c r="H72" t="n">
-        <v>245.44</v>
+        <v>115.88</v>
       </c>
       <c r="I72" t="n">
-        <v>504.33</v>
+        <v>129.43</v>
       </c>
       <c r="J72" t="n">
-        <v>42.3</v>
+        <v>16.9</v>
       </c>
       <c r="K72" t="n">
-        <v>-72.7</v>
+        <v>-20.4</v>
       </c>
       <c r="L72" t="n">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>108.38378425</v>
+        <v>64.79386701</v>
       </c>
       <c r="C73" t="n">
-        <v>347.47028925</v>
+        <v>103.53</v>
       </c>
       <c r="D73" t="n">
-        <v>260.5</v>
+        <v>86.5</v>
       </c>
       <c r="E73" t="n">
-        <v>105.226975</v>
+        <v>62.906667</v>
       </c>
       <c r="F73" t="n">
-        <v>330.924085</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>347.47</v>
+        <v>103.53</v>
       </c>
       <c r="H73" t="n">
-        <v>108.38</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>168.16</v>
+        <v>74.48</v>
       </c>
       <c r="J73" t="n">
-        <v>33.4</v>
+        <v>19.7</v>
       </c>
       <c r="K73" t="n">
-        <v>-58.4</v>
+        <v>-25.1</v>
       </c>
       <c r="L73" t="n">
-        <v>0.57</v>
+        <v>0.78</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -3726,41 +3726,41 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>113.85245492</v>
+        <v>2427.6541946</v>
       </c>
       <c r="C74" t="n">
-        <v>196.35</v>
+        <v>8057.4659445</v>
       </c>
       <c r="D74" t="n">
-        <v>167</v>
+        <v>5600</v>
       </c>
       <c r="E74" t="n">
-        <v>110.536364</v>
+        <v>2356.94582</v>
       </c>
       <c r="F74" t="n">
-        <v>187</v>
+        <v>7673.77709</v>
       </c>
       <c r="G74" t="n">
-        <v>196.35</v>
+        <v>8057.47</v>
       </c>
       <c r="H74" t="n">
-        <v>113.85</v>
+        <v>2427.65</v>
       </c>
       <c r="I74" t="n">
-        <v>134.48</v>
+        <v>3835.11</v>
       </c>
       <c r="J74" t="n">
-        <v>17.6</v>
+        <v>43.9</v>
       </c>
       <c r="K74" t="n">
-        <v>-31.8</v>
+        <v>-56.6</v>
       </c>
       <c r="L74" t="n">
-        <v>0.55</v>
+        <v>0.77</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -3771,41 +3771,41 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3293.32097618</v>
+        <v>146.23854201</v>
       </c>
       <c r="C75" t="n">
-        <v>6000.22536855</v>
+        <v>270.9</v>
       </c>
       <c r="D75" t="n">
-        <v>5040</v>
+        <v>216.5</v>
       </c>
       <c r="E75" t="n">
-        <v>3197.399006</v>
+        <v>141.979167</v>
       </c>
       <c r="F75" t="n">
-        <v>5714.500351</v>
+        <v>258</v>
       </c>
       <c r="G75" t="n">
-        <v>6000.23</v>
+        <v>270.9</v>
       </c>
       <c r="H75" t="n">
-        <v>3293.32</v>
+        <v>146.24</v>
       </c>
       <c r="I75" t="n">
-        <v>3970.05</v>
+        <v>177.4</v>
       </c>
       <c r="J75" t="n">
-        <v>19.1</v>
+        <v>25.1</v>
       </c>
       <c r="K75" t="n">
-        <v>-34.7</v>
+        <v>-32.5</v>
       </c>
       <c r="L75" t="n">
-        <v>0.55</v>
+        <v>0.77</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -3816,41 +3816,41 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>243.62129178</v>
+        <v>491.825</v>
       </c>
       <c r="C76" t="n">
-        <v>642.6</v>
+        <v>1036.35</v>
       </c>
       <c r="D76" t="n">
-        <v>502</v>
+        <v>799</v>
       </c>
       <c r="E76" t="n">
-        <v>236.525526</v>
+        <v>477.5</v>
       </c>
       <c r="F76" t="n">
-        <v>612</v>
+        <v>987</v>
       </c>
       <c r="G76" t="n">
-        <v>642.6</v>
+        <v>1036.35</v>
       </c>
       <c r="H76" t="n">
-        <v>243.62</v>
+        <v>491.82</v>
       </c>
       <c r="I76" t="n">
-        <v>343.37</v>
+        <v>627.96</v>
       </c>
       <c r="J76" t="n">
-        <v>28</v>
+        <v>29.7</v>
       </c>
       <c r="K76" t="n">
-        <v>-51.5</v>
+        <v>-38.4</v>
       </c>
       <c r="L76" t="n">
-        <v>0.54</v>
+        <v>0.77</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -3861,176 +3861,176 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>311.575</v>
+        <v>87.38638965</v>
       </c>
       <c r="C77" t="n">
-        <v>616.35</v>
+        <v>114.7666821</v>
       </c>
       <c r="D77" t="n">
-        <v>509</v>
+        <v>103</v>
       </c>
       <c r="E77" t="n">
-        <v>302.5</v>
+        <v>84.841155</v>
       </c>
       <c r="F77" t="n">
-        <v>587</v>
+        <v>109.301602</v>
       </c>
       <c r="G77" t="n">
-        <v>616.35</v>
+        <v>114.77</v>
       </c>
       <c r="H77" t="n">
-        <v>311.57</v>
+        <v>87.39</v>
       </c>
       <c r="I77" t="n">
-        <v>387.77</v>
+        <v>94.23</v>
       </c>
       <c r="J77" t="n">
-        <v>21.1</v>
+        <v>11.4</v>
       </c>
       <c r="K77" t="n">
-        <v>-38.8</v>
+        <v>-15.2</v>
       </c>
       <c r="L77" t="n">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>156.56</v>
+        <v>139.8182976</v>
       </c>
       <c r="C78" t="n">
-        <v>213.3067608</v>
+        <v>425.25</v>
       </c>
       <c r="D78" t="n">
-        <v>194</v>
+        <v>304.5</v>
       </c>
       <c r="E78" t="n">
-        <v>152</v>
+        <v>135.74592</v>
       </c>
       <c r="F78" t="n">
-        <v>203.149296</v>
+        <v>405</v>
       </c>
       <c r="G78" t="n">
-        <v>213.31</v>
+        <v>425.25</v>
       </c>
       <c r="H78" t="n">
-        <v>156.56</v>
+        <v>139.82</v>
       </c>
       <c r="I78" t="n">
-        <v>170.75</v>
+        <v>211.18</v>
       </c>
       <c r="J78" t="n">
-        <v>10</v>
+        <v>39.7</v>
       </c>
       <c r="K78" t="n">
-        <v>-19.3</v>
+        <v>-54.1</v>
       </c>
       <c r="L78" t="n">
-        <v>0.52</v>
+        <v>0.73</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>🟠 稍高(等回檔 5-15%)</t>
+          <t>🔴 追高風險(掛限價單 Max Entry)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1464.15186701</v>
+        <v>1781.61861224</v>
       </c>
       <c r="C79" t="n">
-        <v>5187.505272599999</v>
+        <v>2661.75</v>
       </c>
       <c r="D79" t="n">
-        <v>3925</v>
+        <v>2290</v>
       </c>
       <c r="E79" t="n">
-        <v>1421.506667</v>
+        <v>1729.726808</v>
       </c>
       <c r="F79" t="n">
-        <v>4940.481212</v>
+        <v>2535</v>
       </c>
       <c r="G79" t="n">
-        <v>5187.51</v>
+        <v>2661.75</v>
       </c>
       <c r="H79" t="n">
-        <v>1464.15</v>
+        <v>1781.62</v>
       </c>
       <c r="I79" t="n">
-        <v>2394.99</v>
+        <v>2001.65</v>
       </c>
       <c r="J79" t="n">
-        <v>32.2</v>
+        <v>16.2</v>
       </c>
       <c r="K79" t="n">
-        <v>-62.7</v>
+        <v>-22.2</v>
       </c>
       <c r="L79" t="n">
-        <v>0.51</v>
+        <v>0.73</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>104.545</v>
+        <v>1606.8</v>
       </c>
       <c r="C80" t="n">
-        <v>512.4</v>
+        <v>6562.5</v>
       </c>
       <c r="D80" t="n">
-        <v>376</v>
+        <v>4495</v>
       </c>
       <c r="E80" t="n">
-        <v>101.5</v>
+        <v>1560</v>
       </c>
       <c r="F80" t="n">
-        <v>488</v>
+        <v>6250</v>
       </c>
       <c r="G80" t="n">
-        <v>512.4</v>
+        <v>6562.5</v>
       </c>
       <c r="H80" t="n">
-        <v>104.55</v>
+        <v>1606.8</v>
       </c>
       <c r="I80" t="n">
-        <v>206.51</v>
+        <v>2845.72</v>
       </c>
       <c r="J80" t="n">
-        <v>36.3</v>
+        <v>46</v>
       </c>
       <c r="K80" t="n">
-        <v>-72.2</v>
+        <v>-64.3</v>
       </c>
       <c r="L80" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>1060.5</v>
       </c>
       <c r="D81" t="n">
-        <v>817</v>
+        <v>747</v>
       </c>
       <c r="E81" t="n">
         <v>303</v>
@@ -4069,13 +4069,13 @@
         <v>499.19</v>
       </c>
       <c r="J81" t="n">
-        <v>29.8</v>
+        <v>42</v>
       </c>
       <c r="K81" t="n">
-        <v>-61.8</v>
+        <v>-58.2</v>
       </c>
       <c r="L81" t="n">
-        <v>0.48</v>
+        <v>0.72</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -4086,41 +4086,41 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>451.14</v>
+        <v>389.04750781</v>
       </c>
       <c r="C82" t="n">
-        <v>1018.5</v>
+        <v>775.0155462</v>
       </c>
       <c r="D82" t="n">
-        <v>840</v>
+        <v>615</v>
       </c>
       <c r="E82" t="n">
-        <v>438</v>
+        <v>377.716027</v>
       </c>
       <c r="F82" t="n">
-        <v>970</v>
+        <v>738.110044</v>
       </c>
       <c r="G82" t="n">
-        <v>1018.5</v>
+        <v>775.02</v>
       </c>
       <c r="H82" t="n">
-        <v>451.14</v>
+        <v>389.05</v>
       </c>
       <c r="I82" t="n">
-        <v>592.98</v>
+        <v>485.54</v>
       </c>
       <c r="J82" t="n">
-        <v>21.2</v>
+        <v>26</v>
       </c>
       <c r="K82" t="n">
-        <v>-46.3</v>
+        <v>-36.7</v>
       </c>
       <c r="L82" t="n">
-        <v>0.46</v>
+        <v>0.71</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -4131,41 +4131,41 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>491.825</v>
+        <v>203.79860469</v>
       </c>
       <c r="C83" t="n">
-        <v>1036.35</v>
+        <v>528.5476518</v>
       </c>
       <c r="D83" t="n">
-        <v>875</v>
+        <v>395.5</v>
       </c>
       <c r="E83" t="n">
-        <v>477.5</v>
+        <v>197.862723</v>
       </c>
       <c r="F83" t="n">
-        <v>987</v>
+        <v>503.378716</v>
       </c>
       <c r="G83" t="n">
-        <v>1036.35</v>
+        <v>528.55</v>
       </c>
       <c r="H83" t="n">
-        <v>491.82</v>
+        <v>203.8</v>
       </c>
       <c r="I83" t="n">
-        <v>627.96</v>
+        <v>284.99</v>
       </c>
       <c r="J83" t="n">
-        <v>18.4</v>
+        <v>33.6</v>
       </c>
       <c r="K83" t="n">
-        <v>-43.8</v>
+        <v>-48.5</v>
       </c>
       <c r="L83" t="n">
-        <v>0.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -4176,41 +4176,41 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>52.34033477000001</v>
+        <v>141.71465429</v>
       </c>
       <c r="C84" t="n">
-        <v>67.74120465</v>
+        <v>186.9</v>
       </c>
       <c r="D84" t="n">
-        <v>63.3</v>
+        <v>168.5</v>
       </c>
       <c r="E84" t="n">
-        <v>50.815859</v>
+        <v>137.587043</v>
       </c>
       <c r="F84" t="n">
-        <v>64.515433</v>
+        <v>178</v>
       </c>
       <c r="G84" t="n">
-        <v>67.73999999999999</v>
+        <v>186.9</v>
       </c>
       <c r="H84" t="n">
-        <v>52.34</v>
+        <v>141.71</v>
       </c>
       <c r="I84" t="n">
-        <v>56.19</v>
+        <v>153.01</v>
       </c>
       <c r="J84" t="n">
-        <v>7</v>
+        <v>10.9</v>
       </c>
       <c r="K84" t="n">
-        <v>-17.3</v>
+        <v>-15.9</v>
       </c>
       <c r="L84" t="n">
-        <v>0.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -4221,41 +4221,41 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>203.79860469</v>
+        <v>74.366</v>
       </c>
       <c r="C85" t="n">
-        <v>528.5476518</v>
+        <v>147</v>
       </c>
       <c r="D85" t="n">
-        <v>435.5</v>
+        <v>118.5</v>
       </c>
       <c r="E85" t="n">
-        <v>197.862723</v>
+        <v>72.2</v>
       </c>
       <c r="F85" t="n">
-        <v>503.378716</v>
+        <v>140</v>
       </c>
       <c r="G85" t="n">
-        <v>528.55</v>
+        <v>147</v>
       </c>
       <c r="H85" t="n">
-        <v>203.8</v>
+        <v>74.37</v>
       </c>
       <c r="I85" t="n">
-        <v>284.99</v>
+        <v>92.52</v>
       </c>
       <c r="J85" t="n">
-        <v>21.4</v>
+        <v>24.1</v>
       </c>
       <c r="K85" t="n">
-        <v>-53.2</v>
+        <v>-37.2</v>
       </c>
       <c r="L85" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -4266,41 +4266,41 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>450.62400914</v>
+        <v>394.93303905</v>
       </c>
       <c r="C86" t="n">
-        <v>2016</v>
+        <v>823.97745255</v>
       </c>
       <c r="D86" t="n">
-        <v>1570</v>
+        <v>656</v>
       </c>
       <c r="E86" t="n">
-        <v>437.499038</v>
+        <v>383.430135</v>
       </c>
       <c r="F86" t="n">
-        <v>1920</v>
+        <v>784.7404309999999</v>
       </c>
       <c r="G86" t="n">
-        <v>2016</v>
+        <v>823.98</v>
       </c>
       <c r="H86" t="n">
-        <v>450.62</v>
+        <v>394.93</v>
       </c>
       <c r="I86" t="n">
-        <v>841.97</v>
+        <v>502.19</v>
       </c>
       <c r="J86" t="n">
-        <v>28.4</v>
+        <v>25.6</v>
       </c>
       <c r="K86" t="n">
-        <v>-71.3</v>
+        <v>-39.8</v>
       </c>
       <c r="L86" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -4311,41 +4311,41 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>397.58</v>
+        <v>12.1025</v>
       </c>
       <c r="C87" t="n">
-        <v>829.5</v>
+        <v>44.7825</v>
       </c>
       <c r="D87" t="n">
-        <v>709</v>
+        <v>32.15</v>
       </c>
       <c r="E87" t="n">
-        <v>386</v>
+        <v>11.75</v>
       </c>
       <c r="F87" t="n">
-        <v>790</v>
+        <v>42.65</v>
       </c>
       <c r="G87" t="n">
-        <v>829.5</v>
+        <v>44.78</v>
       </c>
       <c r="H87" t="n">
-        <v>397.58</v>
+        <v>12.1</v>
       </c>
       <c r="I87" t="n">
-        <v>505.56</v>
+        <v>20.27</v>
       </c>
       <c r="J87" t="n">
-        <v>17</v>
+        <v>39.3</v>
       </c>
       <c r="K87" t="n">
-        <v>-43.9</v>
+        <v>-62.4</v>
       </c>
       <c r="L87" t="n">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -4356,86 +4356,86 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>12.1025</v>
+        <v>209.605</v>
       </c>
       <c r="C88" t="n">
-        <v>44.7825</v>
+        <v>262.5</v>
       </c>
       <c r="D88" t="n">
-        <v>36</v>
+        <v>243</v>
       </c>
       <c r="E88" t="n">
-        <v>11.75</v>
+        <v>203.5</v>
       </c>
       <c r="F88" t="n">
-        <v>42.65</v>
+        <v>250</v>
       </c>
       <c r="G88" t="n">
-        <v>44.78</v>
+        <v>262.5</v>
       </c>
       <c r="H88" t="n">
-        <v>12.1</v>
+        <v>209.61</v>
       </c>
       <c r="I88" t="n">
-        <v>20.27</v>
+        <v>222.83</v>
       </c>
       <c r="J88" t="n">
-        <v>24.4</v>
+        <v>8</v>
       </c>
       <c r="K88" t="n">
-        <v>-66.40000000000001</v>
+        <v>-13.7</v>
       </c>
       <c r="L88" t="n">
-        <v>0.37</v>
+        <v>0.58</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🟠 稍高(等回檔 5-15%)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1122.7</v>
+        <v>31.55249573</v>
       </c>
       <c r="C89" t="n">
-        <v>2966.25</v>
+        <v>45.6715329</v>
       </c>
       <c r="D89" t="n">
-        <v>2470</v>
+        <v>41.2</v>
       </c>
       <c r="E89" t="n">
-        <v>1090</v>
+        <v>30.633491</v>
       </c>
       <c r="F89" t="n">
-        <v>2825</v>
+        <v>43.496698</v>
       </c>
       <c r="G89" t="n">
-        <v>2966.25</v>
+        <v>45.67</v>
       </c>
       <c r="H89" t="n">
-        <v>1122.7</v>
+        <v>31.55</v>
       </c>
       <c r="I89" t="n">
-        <v>1583.59</v>
+        <v>35.08</v>
       </c>
       <c r="J89" t="n">
-        <v>20.1</v>
+        <v>10.9</v>
       </c>
       <c r="K89" t="n">
-        <v>-54.5</v>
+        <v>-23.4</v>
       </c>
       <c r="L89" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -4446,41 +4446,41 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1720.18348768</v>
+        <v>284.76904503</v>
       </c>
       <c r="C90" t="n">
-        <v>2661.75</v>
+        <v>758.5219929</v>
       </c>
       <c r="D90" t="n">
-        <v>2415</v>
+        <v>614</v>
       </c>
       <c r="E90" t="n">
-        <v>1670.081056</v>
+        <v>276.474801</v>
       </c>
       <c r="F90" t="n">
-        <v>2535</v>
+        <v>722.401898</v>
       </c>
       <c r="G90" t="n">
-        <v>2661.75</v>
+        <v>758.52</v>
       </c>
       <c r="H90" t="n">
-        <v>1720.18</v>
+        <v>284.77</v>
       </c>
       <c r="I90" t="n">
-        <v>1955.58</v>
+        <v>403.21</v>
       </c>
       <c r="J90" t="n">
-        <v>10.2</v>
+        <v>23.5</v>
       </c>
       <c r="K90" t="n">
-        <v>-28.8</v>
+        <v>-53.6</v>
       </c>
       <c r="L90" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -4491,41 +4491,41 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1591.35</v>
+        <v>509.26671718</v>
       </c>
       <c r="C91" t="n">
-        <v>6562.5</v>
+        <v>1484.6520297</v>
       </c>
       <c r="D91" t="n">
-        <v>5295</v>
+        <v>1195</v>
       </c>
       <c r="E91" t="n">
-        <v>1545</v>
+        <v>494.433706</v>
       </c>
       <c r="F91" t="n">
-        <v>6250</v>
+        <v>1413.954314</v>
       </c>
       <c r="G91" t="n">
-        <v>6562.5</v>
+        <v>1484.65</v>
       </c>
       <c r="H91" t="n">
-        <v>1591.35</v>
+        <v>509.27</v>
       </c>
       <c r="I91" t="n">
-        <v>2834.14</v>
+        <v>753.11</v>
       </c>
       <c r="J91" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="K91" t="n">
-        <v>-69.90000000000001</v>
+        <v>-57.4</v>
       </c>
       <c r="L91" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -4536,41 +4536,41 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>74.366</v>
+        <v>276.78156086</v>
       </c>
       <c r="C92" t="n">
-        <v>147</v>
+        <v>609.5391056999999</v>
       </c>
       <c r="D92" t="n">
-        <v>129</v>
+        <v>513</v>
       </c>
       <c r="E92" t="n">
-        <v>72.2</v>
+        <v>268.719962</v>
       </c>
       <c r="F92" t="n">
-        <v>140</v>
+        <v>580.513434</v>
       </c>
       <c r="G92" t="n">
-        <v>147</v>
+        <v>609.54</v>
       </c>
       <c r="H92" t="n">
-        <v>74.37</v>
+        <v>276.78</v>
       </c>
       <c r="I92" t="n">
-        <v>92.52</v>
+        <v>359.97</v>
       </c>
       <c r="J92" t="n">
-        <v>14</v>
+        <v>18.8</v>
       </c>
       <c r="K92" t="n">
-        <v>-42.4</v>
+        <v>-46</v>
       </c>
       <c r="L92" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -4581,41 +4581,41 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>149.35</v>
+        <v>255.95657075</v>
       </c>
       <c r="C93" t="n">
-        <v>269.325</v>
+        <v>637.35</v>
       </c>
       <c r="D93" t="n">
-        <v>240</v>
+        <v>542</v>
       </c>
       <c r="E93" t="n">
-        <v>145</v>
+        <v>248.501525</v>
       </c>
       <c r="F93" t="n">
-        <v>256.5</v>
+        <v>607</v>
       </c>
       <c r="G93" t="n">
-        <v>269.32</v>
+        <v>637.35</v>
       </c>
       <c r="H93" t="n">
-        <v>149.35</v>
+        <v>255.96</v>
       </c>
       <c r="I93" t="n">
-        <v>179.34</v>
+        <v>351.3</v>
       </c>
       <c r="J93" t="n">
-        <v>12.2</v>
+        <v>17.6</v>
       </c>
       <c r="K93" t="n">
-        <v>-37.8</v>
+        <v>-52.8</v>
       </c>
       <c r="L93" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -4626,41 +4626,41 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>139.8182976</v>
+        <v>52.34033477000001</v>
       </c>
       <c r="C94" t="n">
-        <v>425.25</v>
+        <v>73.08</v>
       </c>
       <c r="D94" t="n">
-        <v>358.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E94" t="n">
-        <v>135.74592</v>
+        <v>50.815859</v>
       </c>
       <c r="F94" t="n">
-        <v>405</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G94" t="n">
-        <v>425.25</v>
+        <v>73.08</v>
       </c>
       <c r="H94" t="n">
-        <v>139.82</v>
+        <v>52.34</v>
       </c>
       <c r="I94" t="n">
-        <v>211.18</v>
+        <v>57.53</v>
       </c>
       <c r="J94" t="n">
-        <v>18.6</v>
+        <v>7.6</v>
       </c>
       <c r="K94" t="n">
-        <v>-61</v>
+        <v>-22.9</v>
       </c>
       <c r="L94" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -4671,41 +4671,41 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>40.32664343</v>
+        <v>2961.25</v>
       </c>
       <c r="C95" t="n">
-        <v>86.52000000000001</v>
+        <v>9345</v>
       </c>
       <c r="D95" t="n">
-        <v>76</v>
+        <v>7890</v>
       </c>
       <c r="E95" t="n">
-        <v>39.152081</v>
+        <v>2875</v>
       </c>
       <c r="F95" t="n">
-        <v>82.40000000000001</v>
+        <v>8900</v>
       </c>
       <c r="G95" t="n">
-        <v>86.52</v>
+        <v>9345</v>
       </c>
       <c r="H95" t="n">
-        <v>40.33</v>
+        <v>2961.25</v>
       </c>
       <c r="I95" t="n">
-        <v>51.87</v>
+        <v>4557.19</v>
       </c>
       <c r="J95" t="n">
-        <v>13.8</v>
+        <v>18.4</v>
       </c>
       <c r="K95" t="n">
-        <v>-46.9</v>
+        <v>-62.5</v>
       </c>
       <c r="L95" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -4716,38 +4716,38 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>255.95657075</v>
+        <v>304.05461053</v>
       </c>
       <c r="C96" t="n">
-        <v>627.9</v>
+        <v>632.1</v>
       </c>
       <c r="D96" t="n">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E96" t="n">
-        <v>248.501525</v>
+        <v>295.198651</v>
       </c>
       <c r="F96" t="n">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="G96" t="n">
-        <v>627.9</v>
+        <v>632.1</v>
       </c>
       <c r="H96" t="n">
-        <v>255.96</v>
+        <v>304.05</v>
       </c>
       <c r="I96" t="n">
-        <v>348.94</v>
+        <v>386.07</v>
       </c>
       <c r="J96" t="n">
-        <v>14.4</v>
+        <v>12.5</v>
       </c>
       <c r="K96" t="n">
-        <v>-53.4</v>
+        <v>-45.9</v>
       </c>
       <c r="L96" t="n">
         <v>0.27</v>
@@ -4761,308 +4761,296 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>404.275</v>
+        <v>674.65</v>
       </c>
       <c r="C97" t="n">
-        <v>805.35</v>
+        <v>1170.75</v>
       </c>
       <c r="D97" t="n">
-        <v>720</v>
+        <v>655</v>
       </c>
       <c r="E97" t="n">
-        <v>392.5</v>
+        <v>655</v>
       </c>
       <c r="F97" t="n">
-        <v>767</v>
+        <v>1115</v>
       </c>
       <c r="G97" t="n">
-        <v>805.35</v>
+        <v>1170.75</v>
       </c>
       <c r="H97" t="n">
-        <v>404.28</v>
+        <v>674.65</v>
       </c>
       <c r="I97" t="n">
-        <v>504.54</v>
+        <v>798.67</v>
       </c>
       <c r="J97" t="n">
-        <v>11.9</v>
+        <v>78.7</v>
       </c>
       <c r="K97" t="n">
-        <v>-43.9</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0.27</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🚨 已破止損(SL 失守, 重新評估支撐)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>483.29318658</v>
+        <v>73.13</v>
       </c>
       <c r="C98" t="n">
-        <v>1484.6520297</v>
+        <v>142.9118481</v>
       </c>
       <c r="D98" t="n">
-        <v>1285</v>
+        <v>71</v>
       </c>
       <c r="E98" t="n">
-        <v>469.216686</v>
+        <v>71</v>
       </c>
       <c r="F98" t="n">
-        <v>1413.954314</v>
+        <v>136.106522</v>
       </c>
       <c r="G98" t="n">
-        <v>1484.65</v>
+        <v>142.91</v>
       </c>
       <c r="H98" t="n">
-        <v>483.29</v>
+        <v>73.13</v>
       </c>
       <c r="I98" t="n">
-        <v>733.63</v>
+        <v>90.58</v>
       </c>
       <c r="J98" t="n">
-        <v>15.5</v>
+        <v>101.3</v>
       </c>
       <c r="K98" t="n">
-        <v>-62.4</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0.25</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🚨 已破止損(SL 失守, 重新評估支撐)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>284.76904503</v>
+        <v>28.84</v>
       </c>
       <c r="C99" t="n">
-        <v>758.5219929</v>
+        <v>37.3275</v>
       </c>
       <c r="D99" t="n">
-        <v>677</v>
+        <v>28</v>
       </c>
       <c r="E99" t="n">
-        <v>276.474801</v>
+        <v>28</v>
       </c>
       <c r="F99" t="n">
-        <v>722.401898</v>
+        <v>35.55</v>
       </c>
       <c r="G99" t="n">
-        <v>758.52</v>
+        <v>37.33</v>
       </c>
       <c r="H99" t="n">
-        <v>284.77</v>
+        <v>28.84</v>
       </c>
       <c r="I99" t="n">
-        <v>403.21</v>
+        <v>30.96</v>
       </c>
       <c r="J99" t="n">
-        <v>12</v>
+        <v>33.3</v>
       </c>
       <c r="K99" t="n">
-        <v>-57.9</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0.21</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🚨 已破止損(SL 失守, 重新評估支撐)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2258.2829722</v>
+        <v>112.785</v>
       </c>
       <c r="C100" t="n">
-        <v>8057.4659445</v>
+        <v>163.24184205</v>
       </c>
       <c r="D100" t="n">
-        <v>7080</v>
+        <v>110.5</v>
       </c>
       <c r="E100" t="n">
-        <v>2192.50774</v>
+        <v>109.5</v>
       </c>
       <c r="F100" t="n">
-        <v>7673.77709</v>
+        <v>155.468421</v>
       </c>
       <c r="G100" t="n">
-        <v>8057.47</v>
+        <v>163.24</v>
       </c>
       <c r="H100" t="n">
-        <v>2258.28</v>
+        <v>112.78</v>
       </c>
       <c r="I100" t="n">
-        <v>3708.08</v>
+        <v>125.4</v>
       </c>
       <c r="J100" t="n">
-        <v>13.8</v>
+        <v>47.7</v>
       </c>
       <c r="K100" t="n">
-        <v>-68.09999999999999</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0.2</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🚨 已破止損(SL 失守, 重新評估支撐)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>282.735</v>
+        <v>38.3675</v>
       </c>
       <c r="C101" t="n">
-        <v>590.1</v>
+        <v>55.23</v>
       </c>
       <c r="D101" t="n">
-        <v>540</v>
+        <v>37.35</v>
       </c>
       <c r="E101" t="n">
-        <v>274.5</v>
+        <v>37.25</v>
       </c>
       <c r="F101" t="n">
-        <v>562</v>
+        <v>52.6</v>
       </c>
       <c r="G101" t="n">
-        <v>590.1</v>
+        <v>55.23</v>
       </c>
       <c r="H101" t="n">
-        <v>282.74</v>
+        <v>38.37</v>
       </c>
       <c r="I101" t="n">
-        <v>359.58</v>
+        <v>42.58</v>
       </c>
       <c r="J101" t="n">
-        <v>9.300000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="K101" t="n">
-        <v>-47.6</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0.19</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🚨 已破止損(SL 失守, 重新評估支撐)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2961.25</v>
+        <v>103</v>
       </c>
       <c r="C102" t="n">
-        <v>8988</v>
+        <v>156.975</v>
       </c>
       <c r="D102" t="n">
-        <v>8250</v>
+        <v>102.5</v>
       </c>
       <c r="E102" t="n">
-        <v>2875</v>
+        <v>100</v>
       </c>
       <c r="F102" t="n">
-        <v>8560</v>
+        <v>149.5</v>
       </c>
       <c r="G102" t="n">
-        <v>8988</v>
+        <v>156.97</v>
       </c>
       <c r="H102" t="n">
-        <v>2961.25</v>
+        <v>103</v>
       </c>
       <c r="I102" t="n">
-        <v>4467.94</v>
+        <v>116.49</v>
       </c>
       <c r="J102" t="n">
-        <v>8.9</v>
+        <v>53.1</v>
       </c>
       <c r="K102" t="n">
-        <v>-64.09999999999999</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0.14</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>🔴 追高風險(掛限價單 Max Entry)</t>
+          <t>🚨 已破止損(SL 失守, 重新評估支撐)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>742.63</v>
+        <v>43.466</v>
       </c>
       <c r="C103" t="n">
-        <v>1170.75</v>
+        <v>64.89</v>
       </c>
       <c r="D103" t="n">
-        <v>721</v>
+        <v>42.3</v>
       </c>
       <c r="E103" t="n">
-        <v>721</v>
+        <v>42.2</v>
       </c>
       <c r="F103" t="n">
-        <v>1115</v>
+        <v>61.8</v>
       </c>
       <c r="G103" t="n">
-        <v>1170.75</v>
+        <v>64.89</v>
       </c>
       <c r="H103" t="n">
-        <v>742.63</v>
+        <v>43.47</v>
       </c>
       <c r="I103" t="n">
-        <v>849.66</v>
+        <v>48.82</v>
       </c>
       <c r="J103" t="n">
-        <v>62.4</v>
+        <v>53.4</v>
       </c>
       <c r="K103" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
@@ -5074,38 +5062,38 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>38.934</v>
+        <v>2616.2</v>
       </c>
       <c r="C104" t="n">
-        <v>55.23</v>
+        <v>4673.55212625</v>
       </c>
       <c r="D104" t="n">
-        <v>38.8</v>
+        <v>2585</v>
       </c>
       <c r="E104" t="n">
-        <v>37.8</v>
+        <v>2540</v>
       </c>
       <c r="F104" t="n">
-        <v>52.6</v>
+        <v>4451.002025</v>
       </c>
       <c r="G104" t="n">
-        <v>55.23</v>
+        <v>4673.55</v>
       </c>
       <c r="H104" t="n">
-        <v>38.93</v>
+        <v>2616.2</v>
       </c>
       <c r="I104" t="n">
-        <v>43.01</v>
+        <v>3130.54</v>
       </c>
       <c r="J104" t="n">
-        <v>42.3</v>
+        <v>80.8</v>
       </c>
       <c r="K104" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
@@ -5117,38 +5105,38 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>112.785</v>
+        <v>71.07000000000001</v>
       </c>
       <c r="C105" t="n">
-        <v>163.24184205</v>
+        <v>111.0765831</v>
       </c>
       <c r="D105" t="n">
-        <v>112</v>
+        <v>69.5</v>
       </c>
       <c r="E105" t="n">
-        <v>109.5</v>
+        <v>69</v>
       </c>
       <c r="F105" t="n">
-        <v>155.468421</v>
+        <v>105.787222</v>
       </c>
       <c r="G105" t="n">
-        <v>163.24</v>
+        <v>111.08</v>
       </c>
       <c r="H105" t="n">
-        <v>112.78</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="I105" t="n">
-        <v>125.4</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="J105" t="n">
-        <v>45.8</v>
+        <v>59.8</v>
       </c>
       <c r="K105" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
